--- a/code/resultados/NWJSSP_OADG_NEH(SwapFirstANDMixedImprovement).xlsx
+++ b/code/resultados/NWJSSP_OADG_NEH(SwapFirstANDMixedImprovement).xlsx
@@ -17,6 +17,10 @@
     <sheet name="tai_j10_m10_1r" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="tai_j100_m10_1" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="tai_j100_m10_1r" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="tai_j100_m100_1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="tai_j100_m100_1r" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="tai_j1000_m10_1" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="tai_j1000_m10_1r" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +434,7 @@
         <v>309</v>
       </c>
       <c r="B1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2">
@@ -472,7 +476,4003 @@
         <v>6786530</v>
       </c>
       <c r="B1" t="n">
-        <v>309625</v>
+        <v>302435</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>53972</v>
+      </c>
+      <c r="B2" t="n">
+        <v>47051</v>
+      </c>
+      <c r="C2" t="n">
+        <v>48951</v>
+      </c>
+      <c r="D2" t="n">
+        <v>116251</v>
+      </c>
+      <c r="E2" t="n">
+        <v>105909</v>
+      </c>
+      <c r="F2" t="n">
+        <v>66654</v>
+      </c>
+      <c r="G2" t="n">
+        <v>107293</v>
+      </c>
+      <c r="H2" t="n">
+        <v>94577</v>
+      </c>
+      <c r="I2" t="n">
+        <v>72178</v>
+      </c>
+      <c r="J2" t="n">
+        <v>55681</v>
+      </c>
+      <c r="K2" t="n">
+        <v>33086</v>
+      </c>
+      <c r="L2" t="n">
+        <v>87548</v>
+      </c>
+      <c r="M2" t="n">
+        <v>9150</v>
+      </c>
+      <c r="N2" t="n">
+        <v>67940</v>
+      </c>
+      <c r="O2" t="n">
+        <v>44138</v>
+      </c>
+      <c r="P2" t="n">
+        <v>12255</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>49689</v>
+      </c>
+      <c r="R2" t="n">
+        <v>49230</v>
+      </c>
+      <c r="S2" t="n">
+        <v>39417</v>
+      </c>
+      <c r="T2" t="n">
+        <v>32233</v>
+      </c>
+      <c r="U2" t="n">
+        <v>128001</v>
+      </c>
+      <c r="V2" t="n">
+        <v>124714</v>
+      </c>
+      <c r="W2" t="n">
+        <v>95618</v>
+      </c>
+      <c r="X2" t="n">
+        <v>112164</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>131546</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>42226</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>36933</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>69810</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>12598</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>62818</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>3937</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>118482</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>104735</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>59353</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>28799</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>98504</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>80411</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>96381</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>116653</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>78516</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>6638</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>21308</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>110228</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>125430</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>44103</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>73059</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1641</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>23531</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>109252</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>56980</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>127987</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>76335</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>42755</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>35187</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>16947</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>27309</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>91940</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3139</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>38329</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>36533</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>30912</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>93</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>64975</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>74051</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>100434</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>80497</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>60044</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>83911</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>92892</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>20828</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>83481</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>93118</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>52584</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>54758</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>85057</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>110269</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>48010</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>122752</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>62176</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>65275</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>24971</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>32372</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>90234</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>15166</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>75812</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>12136</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>9256</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>119970</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>115007</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>101168</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>2142</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>5212</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>56071</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>28358</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>86651</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>116638</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>16327</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>102388</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>21675</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>44514186</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3619619</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>88754</v>
+      </c>
+      <c r="B2" t="n">
+        <v>550022</v>
+      </c>
+      <c r="C2" t="n">
+        <v>346151</v>
+      </c>
+      <c r="D2" t="n">
+        <v>353802</v>
+      </c>
+      <c r="E2" t="n">
+        <v>401994</v>
+      </c>
+      <c r="F2" t="n">
+        <v>662835</v>
+      </c>
+      <c r="G2" t="n">
+        <v>296995</v>
+      </c>
+      <c r="H2" t="n">
+        <v>210806</v>
+      </c>
+      <c r="I2" t="n">
+        <v>163667</v>
+      </c>
+      <c r="J2" t="n">
+        <v>146696</v>
+      </c>
+      <c r="K2" t="n">
+        <v>802453</v>
+      </c>
+      <c r="L2" t="n">
+        <v>137356</v>
+      </c>
+      <c r="M2" t="n">
+        <v>69214</v>
+      </c>
+      <c r="N2" t="n">
+        <v>528309</v>
+      </c>
+      <c r="O2" t="n">
+        <v>150214</v>
+      </c>
+      <c r="P2" t="n">
+        <v>66630</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>751156</v>
+      </c>
+      <c r="R2" t="n">
+        <v>675148</v>
+      </c>
+      <c r="S2" t="n">
+        <v>301790</v>
+      </c>
+      <c r="T2" t="n">
+        <v>649612</v>
+      </c>
+      <c r="U2" t="n">
+        <v>229313</v>
+      </c>
+      <c r="V2" t="n">
+        <v>576731</v>
+      </c>
+      <c r="W2" t="n">
+        <v>747132</v>
+      </c>
+      <c r="X2" t="n">
+        <v>408173</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>63332</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>584913</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>816306</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>134953</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>521955</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>714515</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>755</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>266840</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>721690</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>316505</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>342416</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>464508</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>823179</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>316788</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>602599</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>375081</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>210510</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>5206</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>633791</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>793370</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>734508</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>25666</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>85923</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>428456</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>41391</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>800063</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>280609</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>378364</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>652292</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>242976</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>769181</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>564342</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>172632</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>700825</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>17178</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>103620</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>784197</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>5170</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>238079</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>180590</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>762631</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>496784</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>553876</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>321053</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>197532</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>124229</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>176330</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>375874</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>499894</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>437933</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>695823</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>642324</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>672313</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>825336</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>486365</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>36974</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>621804</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>600248</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>102105</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>272634</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>510687</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>499880</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>363502</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>621948</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>191072</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>447502</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>462665</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>118470</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>57595</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>426453</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>396683</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>260341</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>434177</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>48453</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>543801</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>43942985</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3617084</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>83005</v>
+      </c>
+      <c r="B2" t="n">
+        <v>440018</v>
+      </c>
+      <c r="C2" t="n">
+        <v>462751</v>
+      </c>
+      <c r="D2" t="n">
+        <v>178019</v>
+      </c>
+      <c r="E2" t="n">
+        <v>274989</v>
+      </c>
+      <c r="F2" t="n">
+        <v>380541</v>
+      </c>
+      <c r="G2" t="n">
+        <v>705474</v>
+      </c>
+      <c r="H2" t="n">
+        <v>524463</v>
+      </c>
+      <c r="I2" t="n">
+        <v>123671</v>
+      </c>
+      <c r="J2" t="n">
+        <v>300078</v>
+      </c>
+      <c r="K2" t="n">
+        <v>802253</v>
+      </c>
+      <c r="L2" t="n">
+        <v>345205</v>
+      </c>
+      <c r="M2" t="n">
+        <v>742826</v>
+      </c>
+      <c r="N2" t="n">
+        <v>767974</v>
+      </c>
+      <c r="O2" t="n">
+        <v>787709</v>
+      </c>
+      <c r="P2" t="n">
+        <v>552052</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>312213</v>
+      </c>
+      <c r="R2" t="n">
+        <v>60417</v>
+      </c>
+      <c r="S2" t="n">
+        <v>375782</v>
+      </c>
+      <c r="T2" t="n">
+        <v>9485</v>
+      </c>
+      <c r="U2" t="n">
+        <v>43589</v>
+      </c>
+      <c r="V2" t="n">
+        <v>832262</v>
+      </c>
+      <c r="W2" t="n">
+        <v>190599</v>
+      </c>
+      <c r="X2" t="n">
+        <v>252871</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>554108</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>91292</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>650279</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>512477</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>419303</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>659055</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>583275</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>247735</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>389842</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>720765</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>448145</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>614106</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>311180</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>270849</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>338533</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>55546</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>742341</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>363737</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>302653</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>325946</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>694399</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>9253</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>359149</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>133239</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>160276</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>678617</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>620964</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>273628</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>467695</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>35559</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>227066</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>2115</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>735091</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>38429</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>676011</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>219050</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>826806</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>391065</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>198524</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>104950</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>138177</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>40469</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>167198</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>524410</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>650650</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>97987</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1657</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>708303</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>201723</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>782247</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>466187</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>48160</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>428205</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>173962</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>508824</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>124329</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>356745</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>583445</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>497427</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>215790</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>298176</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>503639</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>87696</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>599358</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>644373</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>405219</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>620077</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>253146</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>827322</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>550881</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>756069</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>447627</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>196134</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>472637</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>564769</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:ALL2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>583334031</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3771339</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1011998</v>
+      </c>
+      <c r="B2" t="n">
+        <v>455098</v>
+      </c>
+      <c r="C2" t="n">
+        <v>623325</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1174689</v>
+      </c>
+      <c r="E2" t="n">
+        <v>51721</v>
+      </c>
+      <c r="F2" t="n">
+        <v>617332</v>
+      </c>
+      <c r="G2" t="n">
+        <v>952664</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10672</v>
+      </c>
+      <c r="I2" t="n">
+        <v>281064</v>
+      </c>
+      <c r="J2" t="n">
+        <v>538253</v>
+      </c>
+      <c r="K2" t="n">
+        <v>560059</v>
+      </c>
+      <c r="L2" t="n">
+        <v>990724</v>
+      </c>
+      <c r="M2" t="n">
+        <v>450050</v>
+      </c>
+      <c r="N2" t="n">
+        <v>956419</v>
+      </c>
+      <c r="O2" t="n">
+        <v>937306</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1036887</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>660054</v>
+      </c>
+      <c r="R2" t="n">
+        <v>287655</v>
+      </c>
+      <c r="S2" t="n">
+        <v>142322</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1046982</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1001959</v>
+      </c>
+      <c r="V2" t="n">
+        <v>941532</v>
+      </c>
+      <c r="W2" t="n">
+        <v>203844</v>
+      </c>
+      <c r="X2" t="n">
+        <v>60246</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>258854</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>332559</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>594812</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1105019</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>629242</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>54451</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>77828</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>37489</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>121650</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>790711</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>163444</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1039973</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>406609</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>123168</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>841134</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>251102</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>70425</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>996984</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>606950</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>44648</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1021822</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>166160</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>899005</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>596144</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>694791</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>504431</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>692600</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>215593</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>503301</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>435999</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>130298</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>808679</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1167891</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>541370</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>890866</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>864429</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>490563</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>986639</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>135928</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1158950</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>895292</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>757964</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>739577</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>221834</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>838972</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>753596</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>424540</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>396245</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1009883</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>508575</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>119889</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>213171</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>664366</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>556103</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>1014058</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>812539</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>764521</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>40681</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>1012463</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>453440</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>611052</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>760699</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>1036041</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>457540</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>821361</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>303251</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>881568</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>242756</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>99789</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>963999</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>55660</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>415538</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>52561</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>914333</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>347486</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>656081</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>657803</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>802056</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>492459</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>179450</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>915585</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>573397</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>86471</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>1190658</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>379764</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>484758</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>103209</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>311825</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>391960</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>818414</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>462078</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>245359</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>677234</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>296557</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>129032</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>981020</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>408743</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>803230</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1117062</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>470735</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>927291</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>528546</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>282809</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>729750</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>201378</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>483820</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>584411</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>690447</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>23731</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>67931</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>44135</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>806412</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>1095881</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>1106836</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>251754</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>495848</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>15077</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>247801</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>652982</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>972791</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>920542</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>290047</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>875371</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>1141592</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>958120</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>1051351</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>546381</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>721186</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>869309</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>855352</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>823363</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>1138258</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>1117199</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>796255</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>1088452</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>1133135</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>647220</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>344069</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>229410</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>105589</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>433048</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>749196</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>35635</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>456589</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>1109444</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>13861</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>8551</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>33498</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>21352</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>1189699</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>1164975</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>137885</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>271695</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>1122575</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>1071438</v>
+      </c>
+      <c r="FX2" t="n">
+        <v>240772</v>
+      </c>
+      <c r="FY2" t="n">
+        <v>667596</v>
+      </c>
+      <c r="FZ2" t="n">
+        <v>637417</v>
+      </c>
+      <c r="GA2" t="n">
+        <v>702195</v>
+      </c>
+      <c r="GB2" t="n">
+        <v>413717</v>
+      </c>
+      <c r="GC2" t="n">
+        <v>702956</v>
+      </c>
+      <c r="GD2" t="n">
+        <v>969963</v>
+      </c>
+      <c r="GE2" t="n">
+        <v>72260</v>
+      </c>
+      <c r="GF2" t="n">
+        <v>135769</v>
+      </c>
+      <c r="GG2" t="n">
+        <v>894712</v>
+      </c>
+      <c r="GH2" t="n">
+        <v>438420</v>
+      </c>
+      <c r="GI2" t="n">
+        <v>168117</v>
+      </c>
+      <c r="GJ2" t="n">
+        <v>1085397</v>
+      </c>
+      <c r="GK2" t="n">
+        <v>901998</v>
+      </c>
+      <c r="GL2" t="n">
+        <v>272009</v>
+      </c>
+      <c r="GM2" t="n">
+        <v>829424</v>
+      </c>
+      <c r="GN2" t="n">
+        <v>1061633</v>
+      </c>
+      <c r="GO2" t="n">
+        <v>1156946</v>
+      </c>
+      <c r="GP2" t="n">
+        <v>373448</v>
+      </c>
+      <c r="GQ2" t="n">
+        <v>50998</v>
+      </c>
+      <c r="GR2" t="n">
+        <v>974658</v>
+      </c>
+      <c r="GS2" t="n">
+        <v>306278</v>
+      </c>
+      <c r="GT2" t="n">
+        <v>383613</v>
+      </c>
+      <c r="GU2" t="n">
+        <v>725572</v>
+      </c>
+      <c r="GV2" t="n">
+        <v>1169244</v>
+      </c>
+      <c r="GW2" t="n">
+        <v>605376</v>
+      </c>
+      <c r="GX2" t="n">
+        <v>1004119</v>
+      </c>
+      <c r="GY2" t="n">
+        <v>1006195</v>
+      </c>
+      <c r="GZ2" t="n">
+        <v>1189117</v>
+      </c>
+      <c r="HA2" t="n">
+        <v>345430</v>
+      </c>
+      <c r="HB2" t="n">
+        <v>490141</v>
+      </c>
+      <c r="HC2" t="n">
+        <v>475786</v>
+      </c>
+      <c r="HD2" t="n">
+        <v>990425</v>
+      </c>
+      <c r="HE2" t="n">
+        <v>756703</v>
+      </c>
+      <c r="HF2" t="n">
+        <v>266337</v>
+      </c>
+      <c r="HG2" t="n">
+        <v>97405</v>
+      </c>
+      <c r="HH2" t="n">
+        <v>98847</v>
+      </c>
+      <c r="HI2" t="n">
+        <v>311265</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>352173</v>
+      </c>
+      <c r="HK2" t="n">
+        <v>368781</v>
+      </c>
+      <c r="HL2" t="n">
+        <v>533873</v>
+      </c>
+      <c r="HM2" t="n">
+        <v>318487</v>
+      </c>
+      <c r="HN2" t="n">
+        <v>760214</v>
+      </c>
+      <c r="HO2" t="n">
+        <v>731471</v>
+      </c>
+      <c r="HP2" t="n">
+        <v>930911</v>
+      </c>
+      <c r="HQ2" t="n">
+        <v>352181</v>
+      </c>
+      <c r="HR2" t="n">
+        <v>294065</v>
+      </c>
+      <c r="HS2" t="n">
+        <v>110730</v>
+      </c>
+      <c r="HT2" t="n">
+        <v>776911</v>
+      </c>
+      <c r="HU2" t="n">
+        <v>929421</v>
+      </c>
+      <c r="HV2" t="n">
+        <v>754458</v>
+      </c>
+      <c r="HW2" t="n">
+        <v>597685</v>
+      </c>
+      <c r="HX2" t="n">
+        <v>377052</v>
+      </c>
+      <c r="HY2" t="n">
+        <v>933232</v>
+      </c>
+      <c r="HZ2" t="n">
+        <v>185683</v>
+      </c>
+      <c r="IA2" t="n">
+        <v>231043</v>
+      </c>
+      <c r="IB2" t="n">
+        <v>730416</v>
+      </c>
+      <c r="IC2" t="n">
+        <v>1069143</v>
+      </c>
+      <c r="ID2" t="n">
+        <v>830124</v>
+      </c>
+      <c r="IE2" t="n">
+        <v>1130167</v>
+      </c>
+      <c r="IF2" t="n">
+        <v>88179</v>
+      </c>
+      <c r="IG2" t="n">
+        <v>66827</v>
+      </c>
+      <c r="IH2" t="n">
+        <v>866226</v>
+      </c>
+      <c r="II2" t="n">
+        <v>349294</v>
+      </c>
+      <c r="IJ2" t="n">
+        <v>226634</v>
+      </c>
+      <c r="IK2" t="n">
+        <v>673257</v>
+      </c>
+      <c r="IL2" t="n">
+        <v>946814</v>
+      </c>
+      <c r="IM2" t="n">
+        <v>876566</v>
+      </c>
+      <c r="IN2" t="n">
+        <v>273624</v>
+      </c>
+      <c r="IO2" t="n">
+        <v>633775</v>
+      </c>
+      <c r="IP2" t="n">
+        <v>1026805</v>
+      </c>
+      <c r="IQ2" t="n">
+        <v>278704</v>
+      </c>
+      <c r="IR2" t="n">
+        <v>419221</v>
+      </c>
+      <c r="IS2" t="n">
+        <v>901587</v>
+      </c>
+      <c r="IT2" t="n">
+        <v>233261</v>
+      </c>
+      <c r="IU2" t="n">
+        <v>793541</v>
+      </c>
+      <c r="IV2" t="n">
+        <v>320571</v>
+      </c>
+      <c r="IW2" t="n">
+        <v>302082</v>
+      </c>
+      <c r="IX2" t="n">
+        <v>579518</v>
+      </c>
+      <c r="IY2" t="n">
+        <v>448890</v>
+      </c>
+      <c r="IZ2" t="n">
+        <v>1069679</v>
+      </c>
+      <c r="JA2" t="n">
+        <v>1154101</v>
+      </c>
+      <c r="JB2" t="n">
+        <v>966292</v>
+      </c>
+      <c r="JC2" t="n">
+        <v>879080</v>
+      </c>
+      <c r="JD2" t="n">
+        <v>746878</v>
+      </c>
+      <c r="JE2" t="n">
+        <v>45841</v>
+      </c>
+      <c r="JF2" t="n">
+        <v>211439</v>
+      </c>
+      <c r="JG2" t="n">
+        <v>1038680</v>
+      </c>
+      <c r="JH2" t="n">
+        <v>1079152</v>
+      </c>
+      <c r="JI2" t="n">
+        <v>363542</v>
+      </c>
+      <c r="JJ2" t="n">
+        <v>1075396</v>
+      </c>
+      <c r="JK2" t="n">
+        <v>1073625</v>
+      </c>
+      <c r="JL2" t="n">
+        <v>560237</v>
+      </c>
+      <c r="JM2" t="n">
+        <v>872119</v>
+      </c>
+      <c r="JN2" t="n">
+        <v>964371</v>
+      </c>
+      <c r="JO2" t="n">
+        <v>620925</v>
+      </c>
+      <c r="JP2" t="n">
+        <v>977246</v>
+      </c>
+      <c r="JQ2" t="n">
+        <v>1086447</v>
+      </c>
+      <c r="JR2" t="n">
+        <v>292339</v>
+      </c>
+      <c r="JS2" t="n">
+        <v>127459</v>
+      </c>
+      <c r="JT2" t="n">
+        <v>356563</v>
+      </c>
+      <c r="JU2" t="n">
+        <v>1161085</v>
+      </c>
+      <c r="JV2" t="n">
+        <v>678796</v>
+      </c>
+      <c r="JW2" t="n">
+        <v>776105</v>
+      </c>
+      <c r="JX2" t="n">
+        <v>1023922</v>
+      </c>
+      <c r="JY2" t="n">
+        <v>106827</v>
+      </c>
+      <c r="JZ2" t="n">
+        <v>1088952</v>
+      </c>
+      <c r="KA2" t="n">
+        <v>948962</v>
+      </c>
+      <c r="KB2" t="n">
+        <v>792556</v>
+      </c>
+      <c r="KC2" t="n">
+        <v>79325</v>
+      </c>
+      <c r="KD2" t="n">
+        <v>337474</v>
+      </c>
+      <c r="KE2" t="n">
+        <v>797374</v>
+      </c>
+      <c r="KF2" t="n">
+        <v>1185887</v>
+      </c>
+      <c r="KG2" t="n">
+        <v>253128</v>
+      </c>
+      <c r="KH2" t="n">
+        <v>29281</v>
+      </c>
+      <c r="KI2" t="n">
+        <v>861081</v>
+      </c>
+      <c r="KJ2" t="n">
+        <v>343555</v>
+      </c>
+      <c r="KK2" t="n">
+        <v>114015</v>
+      </c>
+      <c r="KL2" t="n">
+        <v>374504</v>
+      </c>
+      <c r="KM2" t="n">
+        <v>1059826</v>
+      </c>
+      <c r="KN2" t="n">
+        <v>1137624</v>
+      </c>
+      <c r="KO2" t="n">
+        <v>464861</v>
+      </c>
+      <c r="KP2" t="n">
+        <v>1195282</v>
+      </c>
+      <c r="KQ2" t="n">
+        <v>1042653</v>
+      </c>
+      <c r="KR2" t="n">
+        <v>646942</v>
+      </c>
+      <c r="KS2" t="n">
+        <v>417498</v>
+      </c>
+      <c r="KT2" t="n">
+        <v>1176815</v>
+      </c>
+      <c r="KU2" t="n">
+        <v>381764</v>
+      </c>
+      <c r="KV2" t="n">
+        <v>499349</v>
+      </c>
+      <c r="KW2" t="n">
+        <v>1165409</v>
+      </c>
+      <c r="KX2" t="n">
+        <v>358653</v>
+      </c>
+      <c r="KY2" t="n">
+        <v>809829</v>
+      </c>
+      <c r="KZ2" t="n">
+        <v>621885</v>
+      </c>
+      <c r="LA2" t="n">
+        <v>334128</v>
+      </c>
+      <c r="LB2" t="n">
+        <v>960910</v>
+      </c>
+      <c r="LC2" t="n">
+        <v>627474</v>
+      </c>
+      <c r="LD2" t="n">
+        <v>151141</v>
+      </c>
+      <c r="LE2" t="n">
+        <v>75506</v>
+      </c>
+      <c r="LF2" t="n">
+        <v>379052</v>
+      </c>
+      <c r="LG2" t="n">
+        <v>181968</v>
+      </c>
+      <c r="LH2" t="n">
+        <v>1059937</v>
+      </c>
+      <c r="LI2" t="n">
+        <v>910441</v>
+      </c>
+      <c r="LJ2" t="n">
+        <v>531103</v>
+      </c>
+      <c r="LK2" t="n">
+        <v>192014</v>
+      </c>
+      <c r="LL2" t="n">
+        <v>723244</v>
+      </c>
+      <c r="LM2" t="n">
+        <v>581337</v>
+      </c>
+      <c r="LN2" t="n">
+        <v>1202838</v>
+      </c>
+      <c r="LO2" t="n">
+        <v>509938</v>
+      </c>
+      <c r="LP2" t="n">
+        <v>986421</v>
+      </c>
+      <c r="LQ2" t="n">
+        <v>898067</v>
+      </c>
+      <c r="LR2" t="n">
+        <v>517167</v>
+      </c>
+      <c r="LS2" t="n">
+        <v>997590</v>
+      </c>
+      <c r="LT2" t="n">
+        <v>879813</v>
+      </c>
+      <c r="LU2" t="n">
+        <v>701851</v>
+      </c>
+      <c r="LV2" t="n">
+        <v>874620</v>
+      </c>
+      <c r="LW2" t="n">
+        <v>391055</v>
+      </c>
+      <c r="LX2" t="n">
+        <v>1030256</v>
+      </c>
+      <c r="LY2" t="n">
+        <v>951832</v>
+      </c>
+      <c r="LZ2" t="n">
+        <v>495841</v>
+      </c>
+      <c r="MA2" t="n">
+        <v>993742</v>
+      </c>
+      <c r="MB2" t="n">
+        <v>403032</v>
+      </c>
+      <c r="MC2" t="n">
+        <v>1113984</v>
+      </c>
+      <c r="MD2" t="n">
+        <v>326331</v>
+      </c>
+      <c r="ME2" t="n">
+        <v>339452</v>
+      </c>
+      <c r="MF2" t="n">
+        <v>339100</v>
+      </c>
+      <c r="MG2" t="n">
+        <v>401186</v>
+      </c>
+      <c r="MH2" t="n">
+        <v>689665</v>
+      </c>
+      <c r="MI2" t="n">
+        <v>739574</v>
+      </c>
+      <c r="MJ2" t="n">
+        <v>961076</v>
+      </c>
+      <c r="MK2" t="n">
+        <v>893014</v>
+      </c>
+      <c r="ML2" t="n">
+        <v>791666</v>
+      </c>
+      <c r="MM2" t="n">
+        <v>205941</v>
+      </c>
+      <c r="MN2" t="n">
+        <v>527103</v>
+      </c>
+      <c r="MO2" t="n">
+        <v>384053</v>
+      </c>
+      <c r="MP2" t="n">
+        <v>984754</v>
+      </c>
+      <c r="MQ2" t="n">
+        <v>1031894</v>
+      </c>
+      <c r="MR2" t="n">
+        <v>800944</v>
+      </c>
+      <c r="MS2" t="n">
+        <v>767588</v>
+      </c>
+      <c r="MT2" t="n">
+        <v>477358</v>
+      </c>
+      <c r="MU2" t="n">
+        <v>28090</v>
+      </c>
+      <c r="MV2" t="n">
+        <v>927004</v>
+      </c>
+      <c r="MW2" t="n">
+        <v>831037</v>
+      </c>
+      <c r="MX2" t="n">
+        <v>84459</v>
+      </c>
+      <c r="MY2" t="n">
+        <v>5031</v>
+      </c>
+      <c r="MZ2" t="n">
+        <v>84769</v>
+      </c>
+      <c r="NA2" t="n">
+        <v>191070</v>
+      </c>
+      <c r="NB2" t="n">
+        <v>283764</v>
+      </c>
+      <c r="NC2" t="n">
+        <v>898286</v>
+      </c>
+      <c r="ND2" t="n">
+        <v>748250</v>
+      </c>
+      <c r="NE2" t="n">
+        <v>921079</v>
+      </c>
+      <c r="NF2" t="n">
+        <v>546414</v>
+      </c>
+      <c r="NG2" t="n">
+        <v>772679</v>
+      </c>
+      <c r="NH2" t="n">
+        <v>212570</v>
+      </c>
+      <c r="NI2" t="n">
+        <v>476496</v>
+      </c>
+      <c r="NJ2" t="n">
+        <v>384940</v>
+      </c>
+      <c r="NK2" t="n">
+        <v>133898</v>
+      </c>
+      <c r="NL2" t="n">
+        <v>788179</v>
+      </c>
+      <c r="NM2" t="n">
+        <v>710713</v>
+      </c>
+      <c r="NN2" t="n">
+        <v>1131996</v>
+      </c>
+      <c r="NO2" t="n">
+        <v>505687</v>
+      </c>
+      <c r="NP2" t="n">
+        <v>727050</v>
+      </c>
+      <c r="NQ2" t="n">
+        <v>1008043</v>
+      </c>
+      <c r="NR2" t="n">
+        <v>236670</v>
+      </c>
+      <c r="NS2" t="n">
+        <v>1143552</v>
+      </c>
+      <c r="NT2" t="n">
+        <v>53441</v>
+      </c>
+      <c r="NU2" t="n">
+        <v>833257</v>
+      </c>
+      <c r="NV2" t="n">
+        <v>498252</v>
+      </c>
+      <c r="NW2" t="n">
+        <v>391179</v>
+      </c>
+      <c r="NX2" t="n">
+        <v>202687</v>
+      </c>
+      <c r="NY2" t="n">
+        <v>1140521</v>
+      </c>
+      <c r="NZ2" t="n">
+        <v>369677</v>
+      </c>
+      <c r="OA2" t="n">
+        <v>746041</v>
+      </c>
+      <c r="OB2" t="n">
+        <v>43171</v>
+      </c>
+      <c r="OC2" t="n">
+        <v>1154649</v>
+      </c>
+      <c r="OD2" t="n">
+        <v>1054877</v>
+      </c>
+      <c r="OE2" t="n">
+        <v>1171723</v>
+      </c>
+      <c r="OF2" t="n">
+        <v>661964</v>
+      </c>
+      <c r="OG2" t="n">
+        <v>189086</v>
+      </c>
+      <c r="OH2" t="n">
+        <v>127034</v>
+      </c>
+      <c r="OI2" t="n">
+        <v>826697</v>
+      </c>
+      <c r="OJ2" t="n">
+        <v>458831</v>
+      </c>
+      <c r="OK2" t="n">
+        <v>724671</v>
+      </c>
+      <c r="OL2" t="n">
+        <v>58915</v>
+      </c>
+      <c r="OM2" t="n">
+        <v>863195</v>
+      </c>
+      <c r="ON2" t="n">
+        <v>159043</v>
+      </c>
+      <c r="OO2" t="n">
+        <v>933389</v>
+      </c>
+      <c r="OP2" t="n">
+        <v>153083</v>
+      </c>
+      <c r="OQ2" t="n">
+        <v>367476</v>
+      </c>
+      <c r="OR2" t="n">
+        <v>157246</v>
+      </c>
+      <c r="OS2" t="n">
+        <v>240856</v>
+      </c>
+      <c r="OT2" t="n">
+        <v>868062</v>
+      </c>
+      <c r="OU2" t="n">
+        <v>687988</v>
+      </c>
+      <c r="OV2" t="n">
+        <v>355788</v>
+      </c>
+      <c r="OW2" t="n">
+        <v>1105187</v>
+      </c>
+      <c r="OX2" t="n">
+        <v>681798</v>
+      </c>
+      <c r="OY2" t="n">
+        <v>69083</v>
+      </c>
+      <c r="OZ2" t="n">
+        <v>649753</v>
+      </c>
+      <c r="PA2" t="n">
+        <v>47871</v>
+      </c>
+      <c r="PB2" t="n">
+        <v>858135</v>
+      </c>
+      <c r="PC2" t="n">
+        <v>1125847</v>
+      </c>
+      <c r="PD2" t="n">
+        <v>470054</v>
+      </c>
+      <c r="PE2" t="n">
+        <v>539207</v>
+      </c>
+      <c r="PF2" t="n">
+        <v>613323</v>
+      </c>
+      <c r="PG2" t="n">
+        <v>1185055</v>
+      </c>
+      <c r="PH2" t="n">
+        <v>1167624</v>
+      </c>
+      <c r="PI2" t="n">
+        <v>261940</v>
+      </c>
+      <c r="PJ2" t="n">
+        <v>610332</v>
+      </c>
+      <c r="PK2" t="n">
+        <v>440285</v>
+      </c>
+      <c r="PL2" t="n">
+        <v>1002029</v>
+      </c>
+      <c r="PM2" t="n">
+        <v>1004724</v>
+      </c>
+      <c r="PN2" t="n">
+        <v>5114</v>
+      </c>
+      <c r="PO2" t="n">
+        <v>736486</v>
+      </c>
+      <c r="PP2" t="n">
+        <v>967688</v>
+      </c>
+      <c r="PQ2" t="n">
+        <v>155101</v>
+      </c>
+      <c r="PR2" t="n">
+        <v>1109200</v>
+      </c>
+      <c r="PS2" t="n">
+        <v>895319</v>
+      </c>
+      <c r="PT2" t="n">
+        <v>1109117</v>
+      </c>
+      <c r="PU2" t="n">
+        <v>316958</v>
+      </c>
+      <c r="PV2" t="n">
+        <v>430113</v>
+      </c>
+      <c r="PW2" t="n">
+        <v>844615</v>
+      </c>
+      <c r="PX2" t="n">
+        <v>350149</v>
+      </c>
+      <c r="PY2" t="n">
+        <v>19861</v>
+      </c>
+      <c r="PZ2" t="n">
+        <v>965352</v>
+      </c>
+      <c r="QA2" t="n">
+        <v>614977</v>
+      </c>
+      <c r="QB2" t="n">
+        <v>1044234</v>
+      </c>
+      <c r="QC2" t="n">
+        <v>981021</v>
+      </c>
+      <c r="QD2" t="n">
+        <v>977157</v>
+      </c>
+      <c r="QE2" t="n">
+        <v>845969</v>
+      </c>
+      <c r="QF2" t="n">
+        <v>858193</v>
+      </c>
+      <c r="QG2" t="n">
+        <v>884353</v>
+      </c>
+      <c r="QH2" t="n">
+        <v>196488</v>
+      </c>
+      <c r="QI2" t="n">
+        <v>786821</v>
+      </c>
+      <c r="QJ2" t="n">
+        <v>640589</v>
+      </c>
+      <c r="QK2" t="n">
+        <v>391057</v>
+      </c>
+      <c r="QL2" t="n">
+        <v>568441</v>
+      </c>
+      <c r="QM2" t="n">
+        <v>762831</v>
+      </c>
+      <c r="QN2" t="n">
+        <v>177236</v>
+      </c>
+      <c r="QO2" t="n">
+        <v>241234</v>
+      </c>
+      <c r="QP2" t="n">
+        <v>707</v>
+      </c>
+      <c r="QQ2" t="n">
+        <v>1029659</v>
+      </c>
+      <c r="QR2" t="n">
+        <v>616881</v>
+      </c>
+      <c r="QS2" t="n">
+        <v>788947</v>
+      </c>
+      <c r="QT2" t="n">
+        <v>173015</v>
+      </c>
+      <c r="QU2" t="n">
+        <v>907235</v>
+      </c>
+      <c r="QV2" t="n">
+        <v>288419</v>
+      </c>
+      <c r="QW2" t="n">
+        <v>236791</v>
+      </c>
+      <c r="QX2" t="n">
+        <v>374458</v>
+      </c>
+      <c r="QY2" t="n">
+        <v>649601</v>
+      </c>
+      <c r="QZ2" t="n">
+        <v>490196</v>
+      </c>
+      <c r="RA2" t="n">
+        <v>426194</v>
+      </c>
+      <c r="RB2" t="n">
+        <v>88675</v>
+      </c>
+      <c r="RC2" t="n">
+        <v>523317</v>
+      </c>
+      <c r="RD2" t="n">
+        <v>91872</v>
+      </c>
+      <c r="RE2" t="n">
+        <v>769597</v>
+      </c>
+      <c r="RF2" t="n">
+        <v>218490</v>
+      </c>
+      <c r="RG2" t="n">
+        <v>285575</v>
+      </c>
+      <c r="RH2" t="n">
+        <v>82770</v>
+      </c>
+      <c r="RI2" t="n">
+        <v>215145</v>
+      </c>
+      <c r="RJ2" t="n">
+        <v>817087</v>
+      </c>
+      <c r="RK2" t="n">
+        <v>319726</v>
+      </c>
+      <c r="RL2" t="n">
+        <v>185977</v>
+      </c>
+      <c r="RM2" t="n">
+        <v>838464</v>
+      </c>
+      <c r="RN2" t="n">
+        <v>665233</v>
+      </c>
+      <c r="RO2" t="n">
+        <v>77564</v>
+      </c>
+      <c r="RP2" t="n">
+        <v>210377</v>
+      </c>
+      <c r="RQ2" t="n">
+        <v>974852</v>
+      </c>
+      <c r="RR2" t="n">
+        <v>958319</v>
+      </c>
+      <c r="RS2" t="n">
+        <v>389163</v>
+      </c>
+      <c r="RT2" t="n">
+        <v>269225</v>
+      </c>
+      <c r="RU2" t="n">
+        <v>275390</v>
+      </c>
+      <c r="RV2" t="n">
+        <v>732502</v>
+      </c>
+      <c r="RW2" t="n">
+        <v>1135784</v>
+      </c>
+      <c r="RX2" t="n">
+        <v>1066845</v>
+      </c>
+      <c r="RY2" t="n">
+        <v>486623</v>
+      </c>
+      <c r="RZ2" t="n">
+        <v>143775</v>
+      </c>
+      <c r="SA2" t="n">
+        <v>1049784</v>
+      </c>
+      <c r="SB2" t="n">
+        <v>154110</v>
+      </c>
+      <c r="SC2" t="n">
+        <v>1046061</v>
+      </c>
+      <c r="SD2" t="n">
+        <v>223535</v>
+      </c>
+      <c r="SE2" t="n">
+        <v>915899</v>
+      </c>
+      <c r="SF2" t="n">
+        <v>183426</v>
+      </c>
+      <c r="SG2" t="n">
+        <v>329501</v>
+      </c>
+      <c r="SH2" t="n">
+        <v>1157685</v>
+      </c>
+      <c r="SI2" t="n">
+        <v>527590</v>
+      </c>
+      <c r="SJ2" t="n">
+        <v>1080452</v>
+      </c>
+      <c r="SK2" t="n">
+        <v>435778</v>
+      </c>
+      <c r="SL2" t="n">
+        <v>1115453</v>
+      </c>
+      <c r="SM2" t="n">
+        <v>906290</v>
+      </c>
+      <c r="SN2" t="n">
+        <v>1082075</v>
+      </c>
+      <c r="SO2" t="n">
+        <v>31225</v>
+      </c>
+      <c r="SP2" t="n">
+        <v>394530</v>
+      </c>
+      <c r="SQ2" t="n">
+        <v>652091</v>
+      </c>
+      <c r="SR2" t="n">
+        <v>8975</v>
+      </c>
+      <c r="SS2" t="n">
+        <v>1016788</v>
+      </c>
+      <c r="ST2" t="n">
+        <v>365339</v>
+      </c>
+      <c r="SU2" t="n">
+        <v>785406</v>
+      </c>
+      <c r="SV2" t="n">
+        <v>139273</v>
+      </c>
+      <c r="SW2" t="n">
+        <v>218760</v>
+      </c>
+      <c r="SX2" t="n">
+        <v>430987</v>
+      </c>
+      <c r="SY2" t="n">
+        <v>527367</v>
+      </c>
+      <c r="SZ2" t="n">
+        <v>663932</v>
+      </c>
+      <c r="TA2" t="n">
+        <v>408927</v>
+      </c>
+      <c r="TB2" t="n">
+        <v>125320</v>
+      </c>
+      <c r="TC2" t="n">
+        <v>1176050</v>
+      </c>
+      <c r="TD2" t="n">
+        <v>766022</v>
+      </c>
+      <c r="TE2" t="n">
+        <v>758538</v>
+      </c>
+      <c r="TF2" t="n">
+        <v>642475</v>
+      </c>
+      <c r="TG2" t="n">
+        <v>885322</v>
+      </c>
+      <c r="TH2" t="n">
+        <v>1049839</v>
+      </c>
+      <c r="TI2" t="n">
+        <v>1057171</v>
+      </c>
+      <c r="TJ2" t="n">
+        <v>24881</v>
+      </c>
+      <c r="TK2" t="n">
+        <v>1182964</v>
+      </c>
+      <c r="TL2" t="n">
+        <v>838170</v>
+      </c>
+      <c r="TM2" t="n">
+        <v>149957</v>
+      </c>
+      <c r="TN2" t="n">
+        <v>589887</v>
+      </c>
+      <c r="TO2" t="n">
+        <v>109228</v>
+      </c>
+      <c r="TP2" t="n">
+        <v>590494</v>
+      </c>
+      <c r="TQ2" t="n">
+        <v>480314</v>
+      </c>
+      <c r="TR2" t="n">
+        <v>566381</v>
+      </c>
+      <c r="TS2" t="n">
+        <v>535716</v>
+      </c>
+      <c r="TT2" t="n">
+        <v>850368</v>
+      </c>
+      <c r="TU2" t="n">
+        <v>713147</v>
+      </c>
+      <c r="TV2" t="n">
+        <v>818010</v>
+      </c>
+      <c r="TW2" t="n">
+        <v>680198</v>
+      </c>
+      <c r="TX2" t="n">
+        <v>165213</v>
+      </c>
+      <c r="TY2" t="n">
+        <v>336738</v>
+      </c>
+      <c r="TZ2" t="n">
+        <v>276506</v>
+      </c>
+      <c r="UA2" t="n">
+        <v>293702</v>
+      </c>
+      <c r="UB2" t="n">
+        <v>627125</v>
+      </c>
+      <c r="UC2" t="n">
+        <v>565829</v>
+      </c>
+      <c r="UD2" t="n">
+        <v>301021</v>
+      </c>
+      <c r="UE2" t="n">
+        <v>289894</v>
+      </c>
+      <c r="UF2" t="n">
+        <v>64976</v>
+      </c>
+      <c r="UG2" t="n">
+        <v>400985</v>
+      </c>
+      <c r="UH2" t="n">
+        <v>28278</v>
+      </c>
+      <c r="UI2" t="n">
+        <v>749185</v>
+      </c>
+      <c r="UJ2" t="n">
+        <v>972431</v>
+      </c>
+      <c r="UK2" t="n">
+        <v>260161</v>
+      </c>
+      <c r="UL2" t="n">
+        <v>62779</v>
+      </c>
+      <c r="UM2" t="n">
+        <v>727676</v>
+      </c>
+      <c r="UN2" t="n">
+        <v>78270</v>
+      </c>
+      <c r="UO2" t="n">
+        <v>1082871</v>
+      </c>
+      <c r="UP2" t="n">
+        <v>101695</v>
+      </c>
+      <c r="UQ2" t="n">
+        <v>682638</v>
+      </c>
+      <c r="UR2" t="n">
+        <v>944245</v>
+      </c>
+      <c r="US2" t="n">
+        <v>303641</v>
+      </c>
+      <c r="UT2" t="n">
+        <v>836225</v>
+      </c>
+      <c r="UU2" t="n">
+        <v>340346</v>
+      </c>
+      <c r="UV2" t="n">
+        <v>517345</v>
+      </c>
+      <c r="UW2" t="n">
+        <v>671240</v>
+      </c>
+      <c r="UX2" t="n">
+        <v>99164</v>
+      </c>
+      <c r="UY2" t="n">
+        <v>912794</v>
+      </c>
+      <c r="UZ2" t="n">
+        <v>778166</v>
+      </c>
+      <c r="VA2" t="n">
+        <v>587207</v>
+      </c>
+      <c r="VB2" t="n">
+        <v>454423</v>
+      </c>
+      <c r="VC2" t="n">
+        <v>1104364</v>
+      </c>
+      <c r="VD2" t="n">
+        <v>398438</v>
+      </c>
+      <c r="VE2" t="n">
+        <v>614846</v>
+      </c>
+      <c r="VF2" t="n">
+        <v>910492</v>
+      </c>
+      <c r="VG2" t="n">
+        <v>584642</v>
+      </c>
+      <c r="VH2" t="n">
+        <v>479945</v>
+      </c>
+      <c r="VI2" t="n">
+        <v>810122</v>
+      </c>
+      <c r="VJ2" t="n">
+        <v>522396</v>
+      </c>
+      <c r="VK2" t="n">
+        <v>476217</v>
+      </c>
+      <c r="VL2" t="n">
+        <v>1120410</v>
+      </c>
+      <c r="VM2" t="n">
+        <v>53620</v>
+      </c>
+      <c r="VN2" t="n">
+        <v>77357</v>
+      </c>
+      <c r="VO2" t="n">
+        <v>717726</v>
+      </c>
+      <c r="VP2" t="n">
+        <v>1156422</v>
+      </c>
+      <c r="VQ2" t="n">
+        <v>635223</v>
+      </c>
+      <c r="VR2" t="n">
+        <v>571129</v>
+      </c>
+      <c r="VS2" t="n">
+        <v>159232</v>
+      </c>
+      <c r="VT2" t="n">
+        <v>569479</v>
+      </c>
+      <c r="VU2" t="n">
+        <v>515914</v>
+      </c>
+      <c r="VV2" t="n">
+        <v>835573</v>
+      </c>
+      <c r="VW2" t="n">
+        <v>716713</v>
+      </c>
+      <c r="VX2" t="n">
+        <v>287300</v>
+      </c>
+      <c r="VY2" t="n">
+        <v>176142</v>
+      </c>
+      <c r="VZ2" t="n">
+        <v>405868</v>
+      </c>
+      <c r="WA2" t="n">
+        <v>686275</v>
+      </c>
+      <c r="WB2" t="n">
+        <v>145305</v>
+      </c>
+      <c r="WC2" t="n">
+        <v>307060</v>
+      </c>
+      <c r="WD2" t="n">
+        <v>847850</v>
+      </c>
+      <c r="WE2" t="n">
+        <v>548345</v>
+      </c>
+      <c r="WF2" t="n">
+        <v>512504</v>
+      </c>
+      <c r="WG2" t="n">
+        <v>996962</v>
+      </c>
+      <c r="WH2" t="n">
+        <v>36807</v>
+      </c>
+      <c r="WI2" t="n">
+        <v>123621</v>
+      </c>
+      <c r="WJ2" t="n">
+        <v>209030</v>
+      </c>
+      <c r="WK2" t="n">
+        <v>563649</v>
+      </c>
+      <c r="WL2" t="n">
+        <v>324188</v>
+      </c>
+      <c r="WM2" t="n">
+        <v>26319</v>
+      </c>
+      <c r="WN2" t="n">
+        <v>940776</v>
+      </c>
+      <c r="WO2" t="n">
+        <v>322491</v>
+      </c>
+      <c r="WP2" t="n">
+        <v>2373</v>
+      </c>
+      <c r="WQ2" t="n">
+        <v>715072</v>
+      </c>
+      <c r="WR2" t="n">
+        <v>772960</v>
+      </c>
+      <c r="WS2" t="n">
+        <v>368574</v>
+      </c>
+      <c r="WT2" t="n">
+        <v>932265</v>
+      </c>
+      <c r="WU2" t="n">
+        <v>328029</v>
+      </c>
+      <c r="WV2" t="n">
+        <v>208160</v>
+      </c>
+      <c r="WW2" t="n">
+        <v>225397</v>
+      </c>
+      <c r="WX2" t="n">
+        <v>325604</v>
+      </c>
+      <c r="WY2" t="n">
+        <v>1089722</v>
+      </c>
+      <c r="WZ2" t="n">
+        <v>798061</v>
+      </c>
+      <c r="XA2" t="n">
+        <v>784598</v>
+      </c>
+      <c r="XB2" t="n">
+        <v>156159</v>
+      </c>
+      <c r="XC2" t="n">
+        <v>734876</v>
+      </c>
+      <c r="XD2" t="n">
+        <v>699749</v>
+      </c>
+      <c r="XE2" t="n">
+        <v>861564</v>
+      </c>
+      <c r="XF2" t="n">
+        <v>471119</v>
+      </c>
+      <c r="XG2" t="n">
+        <v>553101</v>
+      </c>
+      <c r="XH2" t="n">
+        <v>275614</v>
+      </c>
+      <c r="XI2" t="n">
+        <v>161390</v>
+      </c>
+      <c r="XJ2" t="n">
+        <v>619473</v>
+      </c>
+      <c r="XK2" t="n">
+        <v>654396</v>
+      </c>
+      <c r="XL2" t="n">
+        <v>215967</v>
+      </c>
+      <c r="XM2" t="n">
+        <v>150407</v>
+      </c>
+      <c r="XN2" t="n">
+        <v>608601</v>
+      </c>
+      <c r="XO2" t="n">
+        <v>842068</v>
+      </c>
+      <c r="XP2" t="n">
+        <v>66851</v>
+      </c>
+      <c r="XQ2" t="n">
+        <v>918223</v>
+      </c>
+      <c r="XR2" t="n">
+        <v>186593</v>
+      </c>
+      <c r="XS2" t="n">
+        <v>175614</v>
+      </c>
+      <c r="XT2" t="n">
+        <v>525060</v>
+      </c>
+      <c r="XU2" t="n">
+        <v>501400</v>
+      </c>
+      <c r="XV2" t="n">
+        <v>887469</v>
+      </c>
+      <c r="XW2" t="n">
+        <v>1174511</v>
+      </c>
+      <c r="XX2" t="n">
+        <v>138566</v>
+      </c>
+      <c r="XY2" t="n">
+        <v>576076</v>
+      </c>
+      <c r="XZ2" t="n">
+        <v>703820</v>
+      </c>
+      <c r="YA2" t="n">
+        <v>419603</v>
+      </c>
+      <c r="YB2" t="n">
+        <v>541563</v>
+      </c>
+      <c r="YC2" t="n">
+        <v>330613</v>
+      </c>
+      <c r="YD2" t="n">
+        <v>1139751</v>
+      </c>
+      <c r="YE2" t="n">
+        <v>6382</v>
+      </c>
+      <c r="YF2" t="n">
+        <v>802834</v>
+      </c>
+      <c r="YG2" t="n">
+        <v>95912</v>
+      </c>
+      <c r="YH2" t="n">
+        <v>707836</v>
+      </c>
+      <c r="YI2" t="n">
+        <v>575915</v>
+      </c>
+      <c r="YJ2" t="n">
+        <v>845656</v>
+      </c>
+      <c r="YK2" t="n">
+        <v>27502</v>
+      </c>
+      <c r="YL2" t="n">
+        <v>1101472</v>
+      </c>
+      <c r="YM2" t="n">
+        <v>883714</v>
+      </c>
+      <c r="YN2" t="n">
+        <v>17000</v>
+      </c>
+      <c r="YO2" t="n">
+        <v>117620</v>
+      </c>
+      <c r="YP2" t="n">
+        <v>1041207</v>
+      </c>
+      <c r="YQ2" t="n">
+        <v>267119</v>
+      </c>
+      <c r="YR2" t="n">
+        <v>1201591</v>
+      </c>
+      <c r="YS2" t="n">
+        <v>1063002</v>
+      </c>
+      <c r="YT2" t="n">
+        <v>1018808</v>
+      </c>
+      <c r="YU2" t="n">
+        <v>426362</v>
+      </c>
+      <c r="YV2" t="n">
+        <v>592037</v>
+      </c>
+      <c r="YW2" t="n">
+        <v>1150849</v>
+      </c>
+      <c r="YX2" t="n">
+        <v>710708</v>
+      </c>
+      <c r="YY2" t="n">
+        <v>407573</v>
+      </c>
+      <c r="YZ2" t="n">
+        <v>977642</v>
+      </c>
+      <c r="ZA2" t="n">
+        <v>147688</v>
+      </c>
+      <c r="ZB2" t="n">
+        <v>665999</v>
+      </c>
+      <c r="ZC2" t="n">
+        <v>604730</v>
+      </c>
+      <c r="ZD2" t="n">
+        <v>515985</v>
+      </c>
+      <c r="ZE2" t="n">
+        <v>634521</v>
+      </c>
+      <c r="ZF2" t="n">
+        <v>1161859</v>
+      </c>
+      <c r="ZG2" t="n">
+        <v>196042</v>
+      </c>
+      <c r="ZH2" t="n">
+        <v>108248</v>
+      </c>
+      <c r="ZI2" t="n">
+        <v>93002</v>
+      </c>
+      <c r="ZJ2" t="n">
+        <v>656639</v>
+      </c>
+      <c r="ZK2" t="n">
+        <v>609512</v>
+      </c>
+      <c r="ZL2" t="n">
+        <v>403803</v>
+      </c>
+      <c r="ZM2" t="n">
+        <v>72778</v>
+      </c>
+      <c r="ZN2" t="n">
+        <v>199579</v>
+      </c>
+      <c r="ZO2" t="n">
+        <v>550566</v>
+      </c>
+      <c r="ZP2" t="n">
+        <v>332231</v>
+      </c>
+      <c r="ZQ2" t="n">
+        <v>532517</v>
+      </c>
+      <c r="ZR2" t="n">
+        <v>1045536</v>
+      </c>
+      <c r="ZS2" t="n">
+        <v>376214</v>
+      </c>
+      <c r="ZT2" t="n">
+        <v>481918</v>
+      </c>
+      <c r="ZU2" t="n">
+        <v>744107</v>
+      </c>
+      <c r="ZV2" t="n">
+        <v>246166</v>
+      </c>
+      <c r="ZW2" t="n">
+        <v>938023</v>
+      </c>
+      <c r="ZX2" t="n">
+        <v>387284</v>
+      </c>
+      <c r="ZY2" t="n">
+        <v>134247</v>
+      </c>
+      <c r="ZZ2" t="n">
+        <v>234796</v>
+      </c>
+      <c r="AAA2" t="n">
+        <v>1052948</v>
+      </c>
+      <c r="AAB2" t="n">
+        <v>509708</v>
+      </c>
+      <c r="AAC2" t="n">
+        <v>886796</v>
+      </c>
+      <c r="AAD2" t="n">
+        <v>451558</v>
+      </c>
+      <c r="AAE2" t="n">
+        <v>914921</v>
+      </c>
+      <c r="AAF2" t="n">
+        <v>820261</v>
+      </c>
+      <c r="AAG2" t="n">
+        <v>783487</v>
+      </c>
+      <c r="AAH2" t="n">
+        <v>430025</v>
+      </c>
+      <c r="AAI2" t="n">
+        <v>238384</v>
+      </c>
+      <c r="AAJ2" t="n">
+        <v>1124667</v>
+      </c>
+      <c r="AAK2" t="n">
+        <v>1020478</v>
+      </c>
+      <c r="AAL2" t="n">
+        <v>312331</v>
+      </c>
+      <c r="AAM2" t="n">
+        <v>233625</v>
+      </c>
+      <c r="AAN2" t="n">
+        <v>218934</v>
+      </c>
+      <c r="AAO2" t="n">
+        <v>918637</v>
+      </c>
+      <c r="AAP2" t="n">
+        <v>431712</v>
+      </c>
+      <c r="AAQ2" t="n">
+        <v>446440</v>
+      </c>
+      <c r="AAR2" t="n">
+        <v>32436</v>
+      </c>
+      <c r="AAS2" t="n">
+        <v>1101072</v>
+      </c>
+      <c r="AAT2" t="n">
+        <v>772787</v>
+      </c>
+      <c r="AAU2" t="n">
+        <v>712109</v>
+      </c>
+      <c r="AAV2" t="n">
+        <v>256504</v>
+      </c>
+      <c r="AAW2" t="n">
+        <v>202338</v>
+      </c>
+      <c r="AAX2" t="n">
+        <v>1178145</v>
+      </c>
+      <c r="AAY2" t="n">
+        <v>1025570</v>
+      </c>
+      <c r="AAZ2" t="n">
+        <v>1066057</v>
+      </c>
+      <c r="ABA2" t="n">
+        <v>7937</v>
+      </c>
+      <c r="ABB2" t="n">
+        <v>434585</v>
+      </c>
+      <c r="ABC2" t="n">
+        <v>189021</v>
+      </c>
+      <c r="ABD2" t="n">
+        <v>450977</v>
+      </c>
+      <c r="ABE2" t="n">
+        <v>812977</v>
+      </c>
+      <c r="ABF2" t="n">
+        <v>763648</v>
+      </c>
+      <c r="ABG2" t="n">
+        <v>698057</v>
+      </c>
+      <c r="ABH2" t="n">
+        <v>1101077</v>
+      </c>
+      <c r="ABI2" t="n">
+        <v>15703</v>
+      </c>
+      <c r="ABJ2" t="n">
+        <v>1460</v>
+      </c>
+      <c r="ABK2" t="n">
+        <v>1097221</v>
+      </c>
+      <c r="ABL2" t="n">
+        <v>751608</v>
+      </c>
+      <c r="ABM2" t="n">
+        <v>596942</v>
+      </c>
+      <c r="ABN2" t="n">
+        <v>382982</v>
+      </c>
+      <c r="ABO2" t="n">
+        <v>24520</v>
+      </c>
+      <c r="ABP2" t="n">
+        <v>672307</v>
+      </c>
+      <c r="ABQ2" t="n">
+        <v>675893</v>
+      </c>
+      <c r="ABR2" t="n">
+        <v>220410</v>
+      </c>
+      <c r="ABS2" t="n">
+        <v>131740</v>
+      </c>
+      <c r="ABT2" t="n">
+        <v>296330</v>
+      </c>
+      <c r="ABU2" t="n">
+        <v>148657</v>
+      </c>
+      <c r="ABV2" t="n">
+        <v>487500</v>
+      </c>
+      <c r="ABW2" t="n">
+        <v>167725</v>
+      </c>
+      <c r="ABX2" t="n">
+        <v>587746</v>
+      </c>
+      <c r="ABY2" t="n">
+        <v>224428</v>
+      </c>
+      <c r="ABZ2" t="n">
+        <v>804836</v>
+      </c>
+      <c r="ACA2" t="n">
+        <v>226301</v>
+      </c>
+      <c r="ACB2" t="n">
+        <v>334869</v>
+      </c>
+      <c r="ACC2" t="n">
+        <v>193853</v>
+      </c>
+      <c r="ACD2" t="n">
+        <v>423661</v>
+      </c>
+      <c r="ACE2" t="n">
+        <v>58034</v>
+      </c>
+      <c r="ACF2" t="n">
+        <v>180192</v>
+      </c>
+      <c r="ACG2" t="n">
+        <v>445715</v>
+      </c>
+      <c r="ACH2" t="n">
+        <v>990091</v>
+      </c>
+      <c r="ACI2" t="n">
+        <v>226578</v>
+      </c>
+      <c r="ACJ2" t="n">
+        <v>471025</v>
+      </c>
+      <c r="ACK2" t="n">
+        <v>263884</v>
+      </c>
+      <c r="ACL2" t="n">
+        <v>705231</v>
+      </c>
+      <c r="ACM2" t="n">
+        <v>968967</v>
+      </c>
+      <c r="ACN2" t="n">
+        <v>719358</v>
+      </c>
+      <c r="ACO2" t="n">
+        <v>868461</v>
+      </c>
+      <c r="ACP2" t="n">
+        <v>4165</v>
+      </c>
+      <c r="ACQ2" t="n">
+        <v>480384</v>
+      </c>
+      <c r="ACR2" t="n">
+        <v>669355</v>
+      </c>
+      <c r="ACS2" t="n">
+        <v>306277</v>
+      </c>
+      <c r="ACT2" t="n">
+        <v>10729</v>
+      </c>
+      <c r="ACU2" t="n">
+        <v>1054175</v>
+      </c>
+      <c r="ACV2" t="n">
+        <v>624250</v>
+      </c>
+      <c r="ACW2" t="n">
+        <v>182008</v>
+      </c>
+      <c r="ACX2" t="n">
+        <v>952060</v>
+      </c>
+      <c r="ACY2" t="n">
+        <v>299393</v>
+      </c>
+      <c r="ACZ2" t="n">
+        <v>131435</v>
+      </c>
+      <c r="ADA2" t="n">
+        <v>172087</v>
+      </c>
+      <c r="ADB2" t="n">
+        <v>38672</v>
+      </c>
+      <c r="ADC2" t="n">
+        <v>1023895</v>
+      </c>
+      <c r="ADD2" t="n">
+        <v>268363</v>
+      </c>
+      <c r="ADE2" t="n">
+        <v>798442</v>
+      </c>
+      <c r="ADF2" t="n">
+        <v>853244</v>
+      </c>
+      <c r="ADG2" t="n">
+        <v>660192</v>
+      </c>
+      <c r="ADH2" t="n">
+        <v>439557</v>
+      </c>
+      <c r="ADI2" t="n">
+        <v>17854</v>
+      </c>
+      <c r="ADJ2" t="n">
+        <v>81171</v>
+      </c>
+      <c r="ADK2" t="n">
+        <v>668614</v>
+      </c>
+      <c r="ADL2" t="n">
+        <v>908430</v>
+      </c>
+      <c r="ADM2" t="n">
+        <v>161031</v>
+      </c>
+      <c r="ADN2" t="n">
+        <v>498909</v>
+      </c>
+      <c r="ADO2" t="n">
+        <v>982719</v>
+      </c>
+      <c r="ADP2" t="n">
+        <v>361728</v>
+      </c>
+      <c r="ADQ2" t="n">
+        <v>245911</v>
+      </c>
+      <c r="ADR2" t="n">
+        <v>775270</v>
+      </c>
+      <c r="ADS2" t="n">
+        <v>278313</v>
+      </c>
+      <c r="ADT2" t="n">
+        <v>544235</v>
+      </c>
+      <c r="ADU2" t="n">
+        <v>170413</v>
+      </c>
+      <c r="ADV2" t="n">
+        <v>232016</v>
+      </c>
+      <c r="ADW2" t="n">
+        <v>465843</v>
+      </c>
+      <c r="ADX2" t="n">
+        <v>1126965</v>
+      </c>
+      <c r="ADY2" t="n">
+        <v>48389</v>
+      </c>
+      <c r="ADZ2" t="n">
+        <v>360488</v>
+      </c>
+      <c r="AEA2" t="n">
+        <v>600658</v>
+      </c>
+      <c r="AEB2" t="n">
+        <v>742073</v>
+      </c>
+      <c r="AEC2" t="n">
+        <v>572906</v>
+      </c>
+      <c r="AED2" t="n">
+        <v>935257</v>
+      </c>
+      <c r="AEE2" t="n">
+        <v>466818</v>
+      </c>
+      <c r="AEF2" t="n">
+        <v>805850</v>
+      </c>
+      <c r="AEG2" t="n">
+        <v>828154</v>
+      </c>
+      <c r="AEH2" t="n">
+        <v>411109</v>
+      </c>
+      <c r="AEI2" t="n">
+        <v>637726</v>
+      </c>
+      <c r="AEJ2" t="n">
+        <v>521972</v>
+      </c>
+      <c r="AEK2" t="n">
+        <v>347683</v>
+      </c>
+      <c r="AEL2" t="n">
+        <v>444796</v>
+      </c>
+      <c r="AEM2" t="n">
+        <v>782305</v>
+      </c>
+      <c r="AEN2" t="n">
+        <v>889431</v>
+      </c>
+      <c r="AEO2" t="n">
+        <v>463614</v>
+      </c>
+      <c r="AEP2" t="n">
+        <v>254816</v>
+      </c>
+      <c r="AEQ2" t="n">
+        <v>146056</v>
+      </c>
+      <c r="AER2" t="n">
+        <v>82270</v>
+      </c>
+      <c r="AES2" t="n">
+        <v>1204992</v>
+      </c>
+      <c r="AET2" t="n">
+        <v>979763</v>
+      </c>
+      <c r="AEU2" t="n">
+        <v>371928</v>
+      </c>
+      <c r="AEV2" t="n">
+        <v>60429</v>
+      </c>
+      <c r="AEW2" t="n">
+        <v>462878</v>
+      </c>
+      <c r="AEX2" t="n">
+        <v>644119</v>
+      </c>
+      <c r="AEY2" t="n">
+        <v>198758</v>
+      </c>
+      <c r="AEZ2" t="n">
+        <v>1181149</v>
+      </c>
+      <c r="AFA2" t="n">
+        <v>711039</v>
+      </c>
+      <c r="AFB2" t="n">
+        <v>378489</v>
+      </c>
+      <c r="AFC2" t="n">
+        <v>118990</v>
+      </c>
+      <c r="AFD2" t="n">
+        <v>684738</v>
+      </c>
+      <c r="AFE2" t="n">
+        <v>162652</v>
+      </c>
+      <c r="AFF2" t="n">
+        <v>642311</v>
+      </c>
+      <c r="AFG2" t="n">
+        <v>69843</v>
+      </c>
+      <c r="AFH2" t="n">
+        <v>825764</v>
+      </c>
+      <c r="AFI2" t="n">
+        <v>421122</v>
+      </c>
+      <c r="AFJ2" t="n">
+        <v>572713</v>
+      </c>
+      <c r="AFK2" t="n">
+        <v>1021902</v>
+      </c>
+      <c r="AFL2" t="n">
+        <v>443674</v>
+      </c>
+      <c r="AFM2" t="n">
+        <v>904108</v>
+      </c>
+      <c r="AFN2" t="n">
+        <v>538015</v>
+      </c>
+      <c r="AFO2" t="n">
+        <v>1128887</v>
+      </c>
+      <c r="AFP2" t="n">
+        <v>270147</v>
+      </c>
+      <c r="AFQ2" t="n">
+        <v>551279</v>
+      </c>
+      <c r="AFR2" t="n">
+        <v>780876</v>
+      </c>
+      <c r="AFS2" t="n">
+        <v>769947</v>
+      </c>
+      <c r="AFT2" t="n">
+        <v>357540</v>
+      </c>
+      <c r="AFU2" t="n">
+        <v>843813</v>
+      </c>
+      <c r="AFV2" t="n">
+        <v>1180215</v>
+      </c>
+      <c r="AFW2" t="n">
+        <v>850919</v>
+      </c>
+      <c r="AFX2" t="n">
+        <v>411134</v>
+      </c>
+      <c r="AFY2" t="n">
+        <v>641252</v>
+      </c>
+      <c r="AFZ2" t="n">
+        <v>256143</v>
+      </c>
+      <c r="AGA2" t="n">
+        <v>367440</v>
+      </c>
+      <c r="AGB2" t="n">
+        <v>632637</v>
+      </c>
+      <c r="AGC2" t="n">
+        <v>581345</v>
+      </c>
+      <c r="AGD2" t="n">
+        <v>1171947</v>
+      </c>
+      <c r="AGE2" t="n">
+        <v>1066233</v>
+      </c>
+      <c r="AGF2" t="n">
+        <v>1076699</v>
+      </c>
+      <c r="AGG2" t="n">
+        <v>519119</v>
+      </c>
+      <c r="AGH2" t="n">
+        <v>1033784</v>
+      </c>
+      <c r="AGI2" t="n">
+        <v>631780</v>
+      </c>
+      <c r="AGJ2" t="n">
+        <v>249954</v>
+      </c>
+      <c r="AGK2" t="n">
+        <v>1114033</v>
+      </c>
+      <c r="AGL2" t="n">
+        <v>418972</v>
+      </c>
+      <c r="AGM2" t="n">
+        <v>704564</v>
+      </c>
+      <c r="AGN2" t="n">
+        <v>1010667</v>
+      </c>
+      <c r="AGO2" t="n">
+        <v>1057774</v>
+      </c>
+      <c r="AGP2" t="n">
+        <v>308771</v>
+      </c>
+      <c r="AGQ2" t="n">
+        <v>250494</v>
+      </c>
+      <c r="AGR2" t="n">
+        <v>602418</v>
+      </c>
+      <c r="AGS2" t="n">
+        <v>1091360</v>
+      </c>
+      <c r="AGT2" t="n">
+        <v>675502</v>
+      </c>
+      <c r="AGU2" t="n">
+        <v>428349</v>
+      </c>
+      <c r="AGV2" t="n">
+        <v>1184992</v>
+      </c>
+      <c r="AGW2" t="n">
+        <v>1195985</v>
+      </c>
+      <c r="AGX2" t="n">
+        <v>856446</v>
+      </c>
+      <c r="AGY2" t="n">
+        <v>352894</v>
+      </c>
+      <c r="AGZ2" t="n">
+        <v>111552</v>
+      </c>
+      <c r="AHA2" t="n">
+        <v>40640</v>
+      </c>
+      <c r="AHB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AHC2" t="n">
+        <v>94063</v>
+      </c>
+      <c r="AHD2" t="n">
+        <v>1150821</v>
+      </c>
+      <c r="AHE2" t="n">
+        <v>208437</v>
+      </c>
+      <c r="AHF2" t="n">
+        <v>257584</v>
+      </c>
+      <c r="AHG2" t="n">
+        <v>21396</v>
+      </c>
+      <c r="AHH2" t="n">
+        <v>56181</v>
+      </c>
+      <c r="AHI2" t="n">
+        <v>563994</v>
+      </c>
+      <c r="AHJ2" t="n">
+        <v>47105</v>
+      </c>
+      <c r="AHK2" t="n">
+        <v>890170</v>
+      </c>
+      <c r="AHL2" t="n">
+        <v>64682</v>
+      </c>
+      <c r="AHM2" t="n">
+        <v>1065223</v>
+      </c>
+      <c r="AHN2" t="n">
+        <v>442031</v>
+      </c>
+      <c r="AHO2" t="n">
+        <v>1131466</v>
+      </c>
+      <c r="AHP2" t="n">
+        <v>1094184</v>
+      </c>
+      <c r="AHQ2" t="n">
+        <v>852849</v>
+      </c>
+      <c r="AHR2" t="n">
+        <v>141351</v>
+      </c>
+      <c r="AHS2" t="n">
+        <v>513068</v>
+      </c>
+      <c r="AHT2" t="n">
+        <v>115811</v>
+      </c>
+      <c r="AHU2" t="n">
+        <v>12436</v>
+      </c>
+      <c r="AHV2" t="n">
+        <v>460335</v>
+      </c>
+      <c r="AHW2" t="n">
+        <v>446507</v>
+      </c>
+      <c r="AHX2" t="n">
+        <v>6415</v>
+      </c>
+      <c r="AHY2" t="n">
+        <v>689185</v>
+      </c>
+      <c r="AHZ2" t="n">
+        <v>474042</v>
+      </c>
+      <c r="AIA2" t="n">
+        <v>1000287</v>
+      </c>
+      <c r="AIB2" t="n">
+        <v>1191782</v>
+      </c>
+      <c r="AIC2" t="n">
+        <v>264074</v>
+      </c>
+      <c r="AID2" t="n">
+        <v>1198543</v>
+      </c>
+      <c r="AIE2" t="n">
+        <v>872023</v>
+      </c>
+      <c r="AIF2" t="n">
+        <v>1144859</v>
+      </c>
+      <c r="AIG2" t="n">
+        <v>100620</v>
+      </c>
+      <c r="AIH2" t="n">
+        <v>1111900</v>
+      </c>
+      <c r="AII2" t="n">
+        <v>1120740</v>
+      </c>
+      <c r="AIJ2" t="n">
+        <v>190136</v>
+      </c>
+      <c r="AIK2" t="n">
+        <v>504755</v>
+      </c>
+      <c r="AIL2" t="n">
+        <v>601285</v>
+      </c>
+      <c r="AIM2" t="n">
+        <v>738783</v>
+      </c>
+      <c r="AIN2" t="n">
+        <v>598289</v>
+      </c>
+      <c r="AIO2" t="n">
+        <v>504856</v>
+      </c>
+      <c r="AIP2" t="n">
+        <v>314931</v>
+      </c>
+      <c r="AIQ2" t="n">
+        <v>865142</v>
+      </c>
+      <c r="AIR2" t="n">
+        <v>556234</v>
+      </c>
+      <c r="AIS2" t="n">
+        <v>1073669</v>
+      </c>
+      <c r="AIT2" t="n">
+        <v>926549</v>
+      </c>
+      <c r="AIU2" t="n">
+        <v>743500</v>
+      </c>
+      <c r="AIV2" t="n">
+        <v>947757</v>
+      </c>
+      <c r="AIW2" t="n">
+        <v>105373</v>
+      </c>
+      <c r="AIX2" t="n">
+        <v>1017562</v>
+      </c>
+      <c r="AIY2" t="n">
+        <v>1028287</v>
+      </c>
+      <c r="AIZ2" t="n">
+        <v>1018314</v>
+      </c>
+      <c r="AJA2" t="n">
+        <v>386600</v>
+      </c>
+      <c r="AJB2" t="n">
+        <v>168563</v>
+      </c>
+      <c r="AJC2" t="n">
+        <v>552370</v>
+      </c>
+      <c r="AJD2" t="n">
+        <v>1121424</v>
+      </c>
+      <c r="AJE2" t="n">
+        <v>315841</v>
+      </c>
+      <c r="AJF2" t="n">
+        <v>816323</v>
+      </c>
+      <c r="AJG2" t="n">
+        <v>988261</v>
+      </c>
+      <c r="AJH2" t="n">
+        <v>117326</v>
+      </c>
+      <c r="AJI2" t="n">
+        <v>808310</v>
+      </c>
+      <c r="AJJ2" t="n">
+        <v>511321</v>
+      </c>
+      <c r="AJK2" t="n">
+        <v>591721</v>
+      </c>
+      <c r="AJL2" t="n">
+        <v>13956</v>
+      </c>
+      <c r="AJM2" t="n">
+        <v>177230</v>
+      </c>
+      <c r="AJN2" t="n">
+        <v>173317</v>
+      </c>
+      <c r="AJO2" t="n">
+        <v>923561</v>
+      </c>
+      <c r="AJP2" t="n">
+        <v>1035111</v>
+      </c>
+      <c r="AJQ2" t="n">
+        <v>779598</v>
+      </c>
+      <c r="AJR2" t="n">
+        <v>1096959</v>
+      </c>
+      <c r="AJS2" t="n">
+        <v>49172</v>
+      </c>
+      <c r="AJT2" t="n">
+        <v>875243</v>
+      </c>
+      <c r="AJU2" t="n">
+        <v>682538</v>
+      </c>
+      <c r="AJV2" t="n">
+        <v>1097947</v>
+      </c>
+      <c r="AJW2" t="n">
+        <v>588771</v>
+      </c>
+      <c r="AJX2" t="n">
+        <v>924349</v>
+      </c>
+      <c r="AJY2" t="n">
+        <v>955697</v>
+      </c>
+      <c r="AJZ2" t="n">
+        <v>708089</v>
+      </c>
+      <c r="AKA2" t="n">
+        <v>18716</v>
+      </c>
+      <c r="AKB2" t="n">
+        <v>396514</v>
+      </c>
+      <c r="AKC2" t="n">
+        <v>90857</v>
+      </c>
+      <c r="AKD2" t="n">
+        <v>439</v>
+      </c>
+      <c r="AKE2" t="n">
+        <v>326527</v>
+      </c>
+      <c r="AKF2" t="n">
+        <v>544461</v>
+      </c>
+      <c r="AKG2" t="n">
+        <v>631552</v>
+      </c>
+      <c r="AKH2" t="n">
+        <v>585032</v>
+      </c>
+      <c r="AKI2" t="n">
+        <v>628789</v>
+      </c>
+      <c r="AKJ2" t="n">
+        <v>1146880</v>
+      </c>
+      <c r="AKK2" t="n">
+        <v>698670</v>
+      </c>
+      <c r="AKL2" t="n">
+        <v>853854</v>
+      </c>
+      <c r="AKM2" t="n">
+        <v>869556</v>
+      </c>
+      <c r="AKN2" t="n">
+        <v>577290</v>
+      </c>
+      <c r="AKO2" t="n">
+        <v>558847</v>
+      </c>
+      <c r="AKP2" t="n">
+        <v>194873</v>
+      </c>
+      <c r="AKQ2" t="n">
+        <v>494908</v>
+      </c>
+      <c r="AKR2" t="n">
+        <v>945668</v>
+      </c>
+      <c r="AKS2" t="n">
+        <v>270805</v>
+      </c>
+      <c r="AKT2" t="n">
+        <v>1147891</v>
+      </c>
+      <c r="AKU2" t="n">
+        <v>312192</v>
+      </c>
+      <c r="AKV2" t="n">
+        <v>697289</v>
+      </c>
+      <c r="AKW2" t="n">
+        <v>9760</v>
+      </c>
+      <c r="AKX2" t="n">
+        <v>1030015</v>
+      </c>
+      <c r="AKY2" t="n">
+        <v>994235</v>
+      </c>
+      <c r="AKZ2" t="n">
+        <v>639076</v>
+      </c>
+      <c r="ALA2" t="n">
+        <v>363766</v>
+      </c>
+      <c r="ALB2" t="n">
+        <v>697178</v>
+      </c>
+      <c r="ALC2" t="n">
+        <v>112179</v>
+      </c>
+      <c r="ALD2" t="n">
+        <v>721725</v>
+      </c>
+      <c r="ALE2" t="n">
+        <v>552439</v>
+      </c>
+      <c r="ALF2" t="n">
+        <v>207035</v>
+      </c>
+      <c r="ALG2" t="n">
+        <v>281989</v>
+      </c>
+      <c r="ALH2" t="n">
+        <v>32623</v>
+      </c>
+      <c r="ALI2" t="n">
+        <v>943160</v>
+      </c>
+      <c r="ALJ2" t="n">
+        <v>414745</v>
+      </c>
+      <c r="ALK2" t="n">
+        <v>484150</v>
+      </c>
+      <c r="ALL2" t="n">
+        <v>1170741</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:ALL2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>581273641</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3822253</v>
       </c>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>
@@ -572,307 +4572,3907 @@
       <c r="CT1" t="inlineStr"/>
       <c r="CU1" t="inlineStr"/>
       <c r="CV1" t="inlineStr"/>
+      <c r="CW1" t="inlineStr"/>
+      <c r="CX1" t="inlineStr"/>
+      <c r="CY1" t="inlineStr"/>
+      <c r="CZ1" t="inlineStr"/>
+      <c r="DA1" t="inlineStr"/>
+      <c r="DB1" t="inlineStr"/>
+      <c r="DC1" t="inlineStr"/>
+      <c r="DD1" t="inlineStr"/>
+      <c r="DE1" t="inlineStr"/>
+      <c r="DF1" t="inlineStr"/>
+      <c r="DG1" t="inlineStr"/>
+      <c r="DH1" t="inlineStr"/>
+      <c r="DI1" t="inlineStr"/>
+      <c r="DJ1" t="inlineStr"/>
+      <c r="DK1" t="inlineStr"/>
+      <c r="DL1" t="inlineStr"/>
+      <c r="DM1" t="inlineStr"/>
+      <c r="DN1" t="inlineStr"/>
+      <c r="DO1" t="inlineStr"/>
+      <c r="DP1" t="inlineStr"/>
+      <c r="DQ1" t="inlineStr"/>
+      <c r="DR1" t="inlineStr"/>
+      <c r="DS1" t="inlineStr"/>
+      <c r="DT1" t="inlineStr"/>
+      <c r="DU1" t="inlineStr"/>
+      <c r="DV1" t="inlineStr"/>
+      <c r="DW1" t="inlineStr"/>
+      <c r="DX1" t="inlineStr"/>
+      <c r="DY1" t="inlineStr"/>
+      <c r="DZ1" t="inlineStr"/>
+      <c r="EA1" t="inlineStr"/>
+      <c r="EB1" t="inlineStr"/>
+      <c r="EC1" t="inlineStr"/>
+      <c r="ED1" t="inlineStr"/>
+      <c r="EE1" t="inlineStr"/>
+      <c r="EF1" t="inlineStr"/>
+      <c r="EG1" t="inlineStr"/>
+      <c r="EH1" t="inlineStr"/>
+      <c r="EI1" t="inlineStr"/>
+      <c r="EJ1" t="inlineStr"/>
+      <c r="EK1" t="inlineStr"/>
+      <c r="EL1" t="inlineStr"/>
+      <c r="EM1" t="inlineStr"/>
+      <c r="EN1" t="inlineStr"/>
+      <c r="EO1" t="inlineStr"/>
+      <c r="EP1" t="inlineStr"/>
+      <c r="EQ1" t="inlineStr"/>
+      <c r="ER1" t="inlineStr"/>
+      <c r="ES1" t="inlineStr"/>
+      <c r="ET1" t="inlineStr"/>
+      <c r="EU1" t="inlineStr"/>
+      <c r="EV1" t="inlineStr"/>
+      <c r="EW1" t="inlineStr"/>
+      <c r="EX1" t="inlineStr"/>
+      <c r="EY1" t="inlineStr"/>
+      <c r="EZ1" t="inlineStr"/>
+      <c r="FA1" t="inlineStr"/>
+      <c r="FB1" t="inlineStr"/>
+      <c r="FC1" t="inlineStr"/>
+      <c r="FD1" t="inlineStr"/>
+      <c r="FE1" t="inlineStr"/>
+      <c r="FF1" t="inlineStr"/>
+      <c r="FG1" t="inlineStr"/>
+      <c r="FH1" t="inlineStr"/>
+      <c r="FI1" t="inlineStr"/>
+      <c r="FJ1" t="inlineStr"/>
+      <c r="FK1" t="inlineStr"/>
+      <c r="FL1" t="inlineStr"/>
+      <c r="FM1" t="inlineStr"/>
+      <c r="FN1" t="inlineStr"/>
+      <c r="FO1" t="inlineStr"/>
+      <c r="FP1" t="inlineStr"/>
+      <c r="FQ1" t="inlineStr"/>
+      <c r="FR1" t="inlineStr"/>
+      <c r="FS1" t="inlineStr"/>
+      <c r="FT1" t="inlineStr"/>
+      <c r="FU1" t="inlineStr"/>
+      <c r="FV1" t="inlineStr"/>
+      <c r="FW1" t="inlineStr"/>
+      <c r="FX1" t="inlineStr"/>
+      <c r="FY1" t="inlineStr"/>
+      <c r="FZ1" t="inlineStr"/>
+      <c r="GA1" t="inlineStr"/>
+      <c r="GB1" t="inlineStr"/>
+      <c r="GC1" t="inlineStr"/>
+      <c r="GD1" t="inlineStr"/>
+      <c r="GE1" t="inlineStr"/>
+      <c r="GF1" t="inlineStr"/>
+      <c r="GG1" t="inlineStr"/>
+      <c r="GH1" t="inlineStr"/>
+      <c r="GI1" t="inlineStr"/>
+      <c r="GJ1" t="inlineStr"/>
+      <c r="GK1" t="inlineStr"/>
+      <c r="GL1" t="inlineStr"/>
+      <c r="GM1" t="inlineStr"/>
+      <c r="GN1" t="inlineStr"/>
+      <c r="GO1" t="inlineStr"/>
+      <c r="GP1" t="inlineStr"/>
+      <c r="GQ1" t="inlineStr"/>
+      <c r="GR1" t="inlineStr"/>
+      <c r="GS1" t="inlineStr"/>
+      <c r="GT1" t="inlineStr"/>
+      <c r="GU1" t="inlineStr"/>
+      <c r="GV1" t="inlineStr"/>
+      <c r="GW1" t="inlineStr"/>
+      <c r="GX1" t="inlineStr"/>
+      <c r="GY1" t="inlineStr"/>
+      <c r="GZ1" t="inlineStr"/>
+      <c r="HA1" t="inlineStr"/>
+      <c r="HB1" t="inlineStr"/>
+      <c r="HC1" t="inlineStr"/>
+      <c r="HD1" t="inlineStr"/>
+      <c r="HE1" t="inlineStr"/>
+      <c r="HF1" t="inlineStr"/>
+      <c r="HG1" t="inlineStr"/>
+      <c r="HH1" t="inlineStr"/>
+      <c r="HI1" t="inlineStr"/>
+      <c r="HJ1" t="inlineStr"/>
+      <c r="HK1" t="inlineStr"/>
+      <c r="HL1" t="inlineStr"/>
+      <c r="HM1" t="inlineStr"/>
+      <c r="HN1" t="inlineStr"/>
+      <c r="HO1" t="inlineStr"/>
+      <c r="HP1" t="inlineStr"/>
+      <c r="HQ1" t="inlineStr"/>
+      <c r="HR1" t="inlineStr"/>
+      <c r="HS1" t="inlineStr"/>
+      <c r="HT1" t="inlineStr"/>
+      <c r="HU1" t="inlineStr"/>
+      <c r="HV1" t="inlineStr"/>
+      <c r="HW1" t="inlineStr"/>
+      <c r="HX1" t="inlineStr"/>
+      <c r="HY1" t="inlineStr"/>
+      <c r="HZ1" t="inlineStr"/>
+      <c r="IA1" t="inlineStr"/>
+      <c r="IB1" t="inlineStr"/>
+      <c r="IC1" t="inlineStr"/>
+      <c r="ID1" t="inlineStr"/>
+      <c r="IE1" t="inlineStr"/>
+      <c r="IF1" t="inlineStr"/>
+      <c r="IG1" t="inlineStr"/>
+      <c r="IH1" t="inlineStr"/>
+      <c r="II1" t="inlineStr"/>
+      <c r="IJ1" t="inlineStr"/>
+      <c r="IK1" t="inlineStr"/>
+      <c r="IL1" t="inlineStr"/>
+      <c r="IM1" t="inlineStr"/>
+      <c r="IN1" t="inlineStr"/>
+      <c r="IO1" t="inlineStr"/>
+      <c r="IP1" t="inlineStr"/>
+      <c r="IQ1" t="inlineStr"/>
+      <c r="IR1" t="inlineStr"/>
+      <c r="IS1" t="inlineStr"/>
+      <c r="IT1" t="inlineStr"/>
+      <c r="IU1" t="inlineStr"/>
+      <c r="IV1" t="inlineStr"/>
+      <c r="IW1" t="inlineStr"/>
+      <c r="IX1" t="inlineStr"/>
+      <c r="IY1" t="inlineStr"/>
+      <c r="IZ1" t="inlineStr"/>
+      <c r="JA1" t="inlineStr"/>
+      <c r="JB1" t="inlineStr"/>
+      <c r="JC1" t="inlineStr"/>
+      <c r="JD1" t="inlineStr"/>
+      <c r="JE1" t="inlineStr"/>
+      <c r="JF1" t="inlineStr"/>
+      <c r="JG1" t="inlineStr"/>
+      <c r="JH1" t="inlineStr"/>
+      <c r="JI1" t="inlineStr"/>
+      <c r="JJ1" t="inlineStr"/>
+      <c r="JK1" t="inlineStr"/>
+      <c r="JL1" t="inlineStr"/>
+      <c r="JM1" t="inlineStr"/>
+      <c r="JN1" t="inlineStr"/>
+      <c r="JO1" t="inlineStr"/>
+      <c r="JP1" t="inlineStr"/>
+      <c r="JQ1" t="inlineStr"/>
+      <c r="JR1" t="inlineStr"/>
+      <c r="JS1" t="inlineStr"/>
+      <c r="JT1" t="inlineStr"/>
+      <c r="JU1" t="inlineStr"/>
+      <c r="JV1" t="inlineStr"/>
+      <c r="JW1" t="inlineStr"/>
+      <c r="JX1" t="inlineStr"/>
+      <c r="JY1" t="inlineStr"/>
+      <c r="JZ1" t="inlineStr"/>
+      <c r="KA1" t="inlineStr"/>
+      <c r="KB1" t="inlineStr"/>
+      <c r="KC1" t="inlineStr"/>
+      <c r="KD1" t="inlineStr"/>
+      <c r="KE1" t="inlineStr"/>
+      <c r="KF1" t="inlineStr"/>
+      <c r="KG1" t="inlineStr"/>
+      <c r="KH1" t="inlineStr"/>
+      <c r="KI1" t="inlineStr"/>
+      <c r="KJ1" t="inlineStr"/>
+      <c r="KK1" t="inlineStr"/>
+      <c r="KL1" t="inlineStr"/>
+      <c r="KM1" t="inlineStr"/>
+      <c r="KN1" t="inlineStr"/>
+      <c r="KO1" t="inlineStr"/>
+      <c r="KP1" t="inlineStr"/>
+      <c r="KQ1" t="inlineStr"/>
+      <c r="KR1" t="inlineStr"/>
+      <c r="KS1" t="inlineStr"/>
+      <c r="KT1" t="inlineStr"/>
+      <c r="KU1" t="inlineStr"/>
+      <c r="KV1" t="inlineStr"/>
+      <c r="KW1" t="inlineStr"/>
+      <c r="KX1" t="inlineStr"/>
+      <c r="KY1" t="inlineStr"/>
+      <c r="KZ1" t="inlineStr"/>
+      <c r="LA1" t="inlineStr"/>
+      <c r="LB1" t="inlineStr"/>
+      <c r="LC1" t="inlineStr"/>
+      <c r="LD1" t="inlineStr"/>
+      <c r="LE1" t="inlineStr"/>
+      <c r="LF1" t="inlineStr"/>
+      <c r="LG1" t="inlineStr"/>
+      <c r="LH1" t="inlineStr"/>
+      <c r="LI1" t="inlineStr"/>
+      <c r="LJ1" t="inlineStr"/>
+      <c r="LK1" t="inlineStr"/>
+      <c r="LL1" t="inlineStr"/>
+      <c r="LM1" t="inlineStr"/>
+      <c r="LN1" t="inlineStr"/>
+      <c r="LO1" t="inlineStr"/>
+      <c r="LP1" t="inlineStr"/>
+      <c r="LQ1" t="inlineStr"/>
+      <c r="LR1" t="inlineStr"/>
+      <c r="LS1" t="inlineStr"/>
+      <c r="LT1" t="inlineStr"/>
+      <c r="LU1" t="inlineStr"/>
+      <c r="LV1" t="inlineStr"/>
+      <c r="LW1" t="inlineStr"/>
+      <c r="LX1" t="inlineStr"/>
+      <c r="LY1" t="inlineStr"/>
+      <c r="LZ1" t="inlineStr"/>
+      <c r="MA1" t="inlineStr"/>
+      <c r="MB1" t="inlineStr"/>
+      <c r="MC1" t="inlineStr"/>
+      <c r="MD1" t="inlineStr"/>
+      <c r="ME1" t="inlineStr"/>
+      <c r="MF1" t="inlineStr"/>
+      <c r="MG1" t="inlineStr"/>
+      <c r="MH1" t="inlineStr"/>
+      <c r="MI1" t="inlineStr"/>
+      <c r="MJ1" t="inlineStr"/>
+      <c r="MK1" t="inlineStr"/>
+      <c r="ML1" t="inlineStr"/>
+      <c r="MM1" t="inlineStr"/>
+      <c r="MN1" t="inlineStr"/>
+      <c r="MO1" t="inlineStr"/>
+      <c r="MP1" t="inlineStr"/>
+      <c r="MQ1" t="inlineStr"/>
+      <c r="MR1" t="inlineStr"/>
+      <c r="MS1" t="inlineStr"/>
+      <c r="MT1" t="inlineStr"/>
+      <c r="MU1" t="inlineStr"/>
+      <c r="MV1" t="inlineStr"/>
+      <c r="MW1" t="inlineStr"/>
+      <c r="MX1" t="inlineStr"/>
+      <c r="MY1" t="inlineStr"/>
+      <c r="MZ1" t="inlineStr"/>
+      <c r="NA1" t="inlineStr"/>
+      <c r="NB1" t="inlineStr"/>
+      <c r="NC1" t="inlineStr"/>
+      <c r="ND1" t="inlineStr"/>
+      <c r="NE1" t="inlineStr"/>
+      <c r="NF1" t="inlineStr"/>
+      <c r="NG1" t="inlineStr"/>
+      <c r="NH1" t="inlineStr"/>
+      <c r="NI1" t="inlineStr"/>
+      <c r="NJ1" t="inlineStr"/>
+      <c r="NK1" t="inlineStr"/>
+      <c r="NL1" t="inlineStr"/>
+      <c r="NM1" t="inlineStr"/>
+      <c r="NN1" t="inlineStr"/>
+      <c r="NO1" t="inlineStr"/>
+      <c r="NP1" t="inlineStr"/>
+      <c r="NQ1" t="inlineStr"/>
+      <c r="NR1" t="inlineStr"/>
+      <c r="NS1" t="inlineStr"/>
+      <c r="NT1" t="inlineStr"/>
+      <c r="NU1" t="inlineStr"/>
+      <c r="NV1" t="inlineStr"/>
+      <c r="NW1" t="inlineStr"/>
+      <c r="NX1" t="inlineStr"/>
+      <c r="NY1" t="inlineStr"/>
+      <c r="NZ1" t="inlineStr"/>
+      <c r="OA1" t="inlineStr"/>
+      <c r="OB1" t="inlineStr"/>
+      <c r="OC1" t="inlineStr"/>
+      <c r="OD1" t="inlineStr"/>
+      <c r="OE1" t="inlineStr"/>
+      <c r="OF1" t="inlineStr"/>
+      <c r="OG1" t="inlineStr"/>
+      <c r="OH1" t="inlineStr"/>
+      <c r="OI1" t="inlineStr"/>
+      <c r="OJ1" t="inlineStr"/>
+      <c r="OK1" t="inlineStr"/>
+      <c r="OL1" t="inlineStr"/>
+      <c r="OM1" t="inlineStr"/>
+      <c r="ON1" t="inlineStr"/>
+      <c r="OO1" t="inlineStr"/>
+      <c r="OP1" t="inlineStr"/>
+      <c r="OQ1" t="inlineStr"/>
+      <c r="OR1" t="inlineStr"/>
+      <c r="OS1" t="inlineStr"/>
+      <c r="OT1" t="inlineStr"/>
+      <c r="OU1" t="inlineStr"/>
+      <c r="OV1" t="inlineStr"/>
+      <c r="OW1" t="inlineStr"/>
+      <c r="OX1" t="inlineStr"/>
+      <c r="OY1" t="inlineStr"/>
+      <c r="OZ1" t="inlineStr"/>
+      <c r="PA1" t="inlineStr"/>
+      <c r="PB1" t="inlineStr"/>
+      <c r="PC1" t="inlineStr"/>
+      <c r="PD1" t="inlineStr"/>
+      <c r="PE1" t="inlineStr"/>
+      <c r="PF1" t="inlineStr"/>
+      <c r="PG1" t="inlineStr"/>
+      <c r="PH1" t="inlineStr"/>
+      <c r="PI1" t="inlineStr"/>
+      <c r="PJ1" t="inlineStr"/>
+      <c r="PK1" t="inlineStr"/>
+      <c r="PL1" t="inlineStr"/>
+      <c r="PM1" t="inlineStr"/>
+      <c r="PN1" t="inlineStr"/>
+      <c r="PO1" t="inlineStr"/>
+      <c r="PP1" t="inlineStr"/>
+      <c r="PQ1" t="inlineStr"/>
+      <c r="PR1" t="inlineStr"/>
+      <c r="PS1" t="inlineStr"/>
+      <c r="PT1" t="inlineStr"/>
+      <c r="PU1" t="inlineStr"/>
+      <c r="PV1" t="inlineStr"/>
+      <c r="PW1" t="inlineStr"/>
+      <c r="PX1" t="inlineStr"/>
+      <c r="PY1" t="inlineStr"/>
+      <c r="PZ1" t="inlineStr"/>
+      <c r="QA1" t="inlineStr"/>
+      <c r="QB1" t="inlineStr"/>
+      <c r="QC1" t="inlineStr"/>
+      <c r="QD1" t="inlineStr"/>
+      <c r="QE1" t="inlineStr"/>
+      <c r="QF1" t="inlineStr"/>
+      <c r="QG1" t="inlineStr"/>
+      <c r="QH1" t="inlineStr"/>
+      <c r="QI1" t="inlineStr"/>
+      <c r="QJ1" t="inlineStr"/>
+      <c r="QK1" t="inlineStr"/>
+      <c r="QL1" t="inlineStr"/>
+      <c r="QM1" t="inlineStr"/>
+      <c r="QN1" t="inlineStr"/>
+      <c r="QO1" t="inlineStr"/>
+      <c r="QP1" t="inlineStr"/>
+      <c r="QQ1" t="inlineStr"/>
+      <c r="QR1" t="inlineStr"/>
+      <c r="QS1" t="inlineStr"/>
+      <c r="QT1" t="inlineStr"/>
+      <c r="QU1" t="inlineStr"/>
+      <c r="QV1" t="inlineStr"/>
+      <c r="QW1" t="inlineStr"/>
+      <c r="QX1" t="inlineStr"/>
+      <c r="QY1" t="inlineStr"/>
+      <c r="QZ1" t="inlineStr"/>
+      <c r="RA1" t="inlineStr"/>
+      <c r="RB1" t="inlineStr"/>
+      <c r="RC1" t="inlineStr"/>
+      <c r="RD1" t="inlineStr"/>
+      <c r="RE1" t="inlineStr"/>
+      <c r="RF1" t="inlineStr"/>
+      <c r="RG1" t="inlineStr"/>
+      <c r="RH1" t="inlineStr"/>
+      <c r="RI1" t="inlineStr"/>
+      <c r="RJ1" t="inlineStr"/>
+      <c r="RK1" t="inlineStr"/>
+      <c r="RL1" t="inlineStr"/>
+      <c r="RM1" t="inlineStr"/>
+      <c r="RN1" t="inlineStr"/>
+      <c r="RO1" t="inlineStr"/>
+      <c r="RP1" t="inlineStr"/>
+      <c r="RQ1" t="inlineStr"/>
+      <c r="RR1" t="inlineStr"/>
+      <c r="RS1" t="inlineStr"/>
+      <c r="RT1" t="inlineStr"/>
+      <c r="RU1" t="inlineStr"/>
+      <c r="RV1" t="inlineStr"/>
+      <c r="RW1" t="inlineStr"/>
+      <c r="RX1" t="inlineStr"/>
+      <c r="RY1" t="inlineStr"/>
+      <c r="RZ1" t="inlineStr"/>
+      <c r="SA1" t="inlineStr"/>
+      <c r="SB1" t="inlineStr"/>
+      <c r="SC1" t="inlineStr"/>
+      <c r="SD1" t="inlineStr"/>
+      <c r="SE1" t="inlineStr"/>
+      <c r="SF1" t="inlineStr"/>
+      <c r="SG1" t="inlineStr"/>
+      <c r="SH1" t="inlineStr"/>
+      <c r="SI1" t="inlineStr"/>
+      <c r="SJ1" t="inlineStr"/>
+      <c r="SK1" t="inlineStr"/>
+      <c r="SL1" t="inlineStr"/>
+      <c r="SM1" t="inlineStr"/>
+      <c r="SN1" t="inlineStr"/>
+      <c r="SO1" t="inlineStr"/>
+      <c r="SP1" t="inlineStr"/>
+      <c r="SQ1" t="inlineStr"/>
+      <c r="SR1" t="inlineStr"/>
+      <c r="SS1" t="inlineStr"/>
+      <c r="ST1" t="inlineStr"/>
+      <c r="SU1" t="inlineStr"/>
+      <c r="SV1" t="inlineStr"/>
+      <c r="SW1" t="inlineStr"/>
+      <c r="SX1" t="inlineStr"/>
+      <c r="SY1" t="inlineStr"/>
+      <c r="SZ1" t="inlineStr"/>
+      <c r="TA1" t="inlineStr"/>
+      <c r="TB1" t="inlineStr"/>
+      <c r="TC1" t="inlineStr"/>
+      <c r="TD1" t="inlineStr"/>
+      <c r="TE1" t="inlineStr"/>
+      <c r="TF1" t="inlineStr"/>
+      <c r="TG1" t="inlineStr"/>
+      <c r="TH1" t="inlineStr"/>
+      <c r="TI1" t="inlineStr"/>
+      <c r="TJ1" t="inlineStr"/>
+      <c r="TK1" t="inlineStr"/>
+      <c r="TL1" t="inlineStr"/>
+      <c r="TM1" t="inlineStr"/>
+      <c r="TN1" t="inlineStr"/>
+      <c r="TO1" t="inlineStr"/>
+      <c r="TP1" t="inlineStr"/>
+      <c r="TQ1" t="inlineStr"/>
+      <c r="TR1" t="inlineStr"/>
+      <c r="TS1" t="inlineStr"/>
+      <c r="TT1" t="inlineStr"/>
+      <c r="TU1" t="inlineStr"/>
+      <c r="TV1" t="inlineStr"/>
+      <c r="TW1" t="inlineStr"/>
+      <c r="TX1" t="inlineStr"/>
+      <c r="TY1" t="inlineStr"/>
+      <c r="TZ1" t="inlineStr"/>
+      <c r="UA1" t="inlineStr"/>
+      <c r="UB1" t="inlineStr"/>
+      <c r="UC1" t="inlineStr"/>
+      <c r="UD1" t="inlineStr"/>
+      <c r="UE1" t="inlineStr"/>
+      <c r="UF1" t="inlineStr"/>
+      <c r="UG1" t="inlineStr"/>
+      <c r="UH1" t="inlineStr"/>
+      <c r="UI1" t="inlineStr"/>
+      <c r="UJ1" t="inlineStr"/>
+      <c r="UK1" t="inlineStr"/>
+      <c r="UL1" t="inlineStr"/>
+      <c r="UM1" t="inlineStr"/>
+      <c r="UN1" t="inlineStr"/>
+      <c r="UO1" t="inlineStr"/>
+      <c r="UP1" t="inlineStr"/>
+      <c r="UQ1" t="inlineStr"/>
+      <c r="UR1" t="inlineStr"/>
+      <c r="US1" t="inlineStr"/>
+      <c r="UT1" t="inlineStr"/>
+      <c r="UU1" t="inlineStr"/>
+      <c r="UV1" t="inlineStr"/>
+      <c r="UW1" t="inlineStr"/>
+      <c r="UX1" t="inlineStr"/>
+      <c r="UY1" t="inlineStr"/>
+      <c r="UZ1" t="inlineStr"/>
+      <c r="VA1" t="inlineStr"/>
+      <c r="VB1" t="inlineStr"/>
+      <c r="VC1" t="inlineStr"/>
+      <c r="VD1" t="inlineStr"/>
+      <c r="VE1" t="inlineStr"/>
+      <c r="VF1" t="inlineStr"/>
+      <c r="VG1" t="inlineStr"/>
+      <c r="VH1" t="inlineStr"/>
+      <c r="VI1" t="inlineStr"/>
+      <c r="VJ1" t="inlineStr"/>
+      <c r="VK1" t="inlineStr"/>
+      <c r="VL1" t="inlineStr"/>
+      <c r="VM1" t="inlineStr"/>
+      <c r="VN1" t="inlineStr"/>
+      <c r="VO1" t="inlineStr"/>
+      <c r="VP1" t="inlineStr"/>
+      <c r="VQ1" t="inlineStr"/>
+      <c r="VR1" t="inlineStr"/>
+      <c r="VS1" t="inlineStr"/>
+      <c r="VT1" t="inlineStr"/>
+      <c r="VU1" t="inlineStr"/>
+      <c r="VV1" t="inlineStr"/>
+      <c r="VW1" t="inlineStr"/>
+      <c r="VX1" t="inlineStr"/>
+      <c r="VY1" t="inlineStr"/>
+      <c r="VZ1" t="inlineStr"/>
+      <c r="WA1" t="inlineStr"/>
+      <c r="WB1" t="inlineStr"/>
+      <c r="WC1" t="inlineStr"/>
+      <c r="WD1" t="inlineStr"/>
+      <c r="WE1" t="inlineStr"/>
+      <c r="WF1" t="inlineStr"/>
+      <c r="WG1" t="inlineStr"/>
+      <c r="WH1" t="inlineStr"/>
+      <c r="WI1" t="inlineStr"/>
+      <c r="WJ1" t="inlineStr"/>
+      <c r="WK1" t="inlineStr"/>
+      <c r="WL1" t="inlineStr"/>
+      <c r="WM1" t="inlineStr"/>
+      <c r="WN1" t="inlineStr"/>
+      <c r="WO1" t="inlineStr"/>
+      <c r="WP1" t="inlineStr"/>
+      <c r="WQ1" t="inlineStr"/>
+      <c r="WR1" t="inlineStr"/>
+      <c r="WS1" t="inlineStr"/>
+      <c r="WT1" t="inlineStr"/>
+      <c r="WU1" t="inlineStr"/>
+      <c r="WV1" t="inlineStr"/>
+      <c r="WW1" t="inlineStr"/>
+      <c r="WX1" t="inlineStr"/>
+      <c r="WY1" t="inlineStr"/>
+      <c r="WZ1" t="inlineStr"/>
+      <c r="XA1" t="inlineStr"/>
+      <c r="XB1" t="inlineStr"/>
+      <c r="XC1" t="inlineStr"/>
+      <c r="XD1" t="inlineStr"/>
+      <c r="XE1" t="inlineStr"/>
+      <c r="XF1" t="inlineStr"/>
+      <c r="XG1" t="inlineStr"/>
+      <c r="XH1" t="inlineStr"/>
+      <c r="XI1" t="inlineStr"/>
+      <c r="XJ1" t="inlineStr"/>
+      <c r="XK1" t="inlineStr"/>
+      <c r="XL1" t="inlineStr"/>
+      <c r="XM1" t="inlineStr"/>
+      <c r="XN1" t="inlineStr"/>
+      <c r="XO1" t="inlineStr"/>
+      <c r="XP1" t="inlineStr"/>
+      <c r="XQ1" t="inlineStr"/>
+      <c r="XR1" t="inlineStr"/>
+      <c r="XS1" t="inlineStr"/>
+      <c r="XT1" t="inlineStr"/>
+      <c r="XU1" t="inlineStr"/>
+      <c r="XV1" t="inlineStr"/>
+      <c r="XW1" t="inlineStr"/>
+      <c r="XX1" t="inlineStr"/>
+      <c r="XY1" t="inlineStr"/>
+      <c r="XZ1" t="inlineStr"/>
+      <c r="YA1" t="inlineStr"/>
+      <c r="YB1" t="inlineStr"/>
+      <c r="YC1" t="inlineStr"/>
+      <c r="YD1" t="inlineStr"/>
+      <c r="YE1" t="inlineStr"/>
+      <c r="YF1" t="inlineStr"/>
+      <c r="YG1" t="inlineStr"/>
+      <c r="YH1" t="inlineStr"/>
+      <c r="YI1" t="inlineStr"/>
+      <c r="YJ1" t="inlineStr"/>
+      <c r="YK1" t="inlineStr"/>
+      <c r="YL1" t="inlineStr"/>
+      <c r="YM1" t="inlineStr"/>
+      <c r="YN1" t="inlineStr"/>
+      <c r="YO1" t="inlineStr"/>
+      <c r="YP1" t="inlineStr"/>
+      <c r="YQ1" t="inlineStr"/>
+      <c r="YR1" t="inlineStr"/>
+      <c r="YS1" t="inlineStr"/>
+      <c r="YT1" t="inlineStr"/>
+      <c r="YU1" t="inlineStr"/>
+      <c r="YV1" t="inlineStr"/>
+      <c r="YW1" t="inlineStr"/>
+      <c r="YX1" t="inlineStr"/>
+      <c r="YY1" t="inlineStr"/>
+      <c r="YZ1" t="inlineStr"/>
+      <c r="ZA1" t="inlineStr"/>
+      <c r="ZB1" t="inlineStr"/>
+      <c r="ZC1" t="inlineStr"/>
+      <c r="ZD1" t="inlineStr"/>
+      <c r="ZE1" t="inlineStr"/>
+      <c r="ZF1" t="inlineStr"/>
+      <c r="ZG1" t="inlineStr"/>
+      <c r="ZH1" t="inlineStr"/>
+      <c r="ZI1" t="inlineStr"/>
+      <c r="ZJ1" t="inlineStr"/>
+      <c r="ZK1" t="inlineStr"/>
+      <c r="ZL1" t="inlineStr"/>
+      <c r="ZM1" t="inlineStr"/>
+      <c r="ZN1" t="inlineStr"/>
+      <c r="ZO1" t="inlineStr"/>
+      <c r="ZP1" t="inlineStr"/>
+      <c r="ZQ1" t="inlineStr"/>
+      <c r="ZR1" t="inlineStr"/>
+      <c r="ZS1" t="inlineStr"/>
+      <c r="ZT1" t="inlineStr"/>
+      <c r="ZU1" t="inlineStr"/>
+      <c r="ZV1" t="inlineStr"/>
+      <c r="ZW1" t="inlineStr"/>
+      <c r="ZX1" t="inlineStr"/>
+      <c r="ZY1" t="inlineStr"/>
+      <c r="ZZ1" t="inlineStr"/>
+      <c r="AAA1" t="inlineStr"/>
+      <c r="AAB1" t="inlineStr"/>
+      <c r="AAC1" t="inlineStr"/>
+      <c r="AAD1" t="inlineStr"/>
+      <c r="AAE1" t="inlineStr"/>
+      <c r="AAF1" t="inlineStr"/>
+      <c r="AAG1" t="inlineStr"/>
+      <c r="AAH1" t="inlineStr"/>
+      <c r="AAI1" t="inlineStr"/>
+      <c r="AAJ1" t="inlineStr"/>
+      <c r="AAK1" t="inlineStr"/>
+      <c r="AAL1" t="inlineStr"/>
+      <c r="AAM1" t="inlineStr"/>
+      <c r="AAN1" t="inlineStr"/>
+      <c r="AAO1" t="inlineStr"/>
+      <c r="AAP1" t="inlineStr"/>
+      <c r="AAQ1" t="inlineStr"/>
+      <c r="AAR1" t="inlineStr"/>
+      <c r="AAS1" t="inlineStr"/>
+      <c r="AAT1" t="inlineStr"/>
+      <c r="AAU1" t="inlineStr"/>
+      <c r="AAV1" t="inlineStr"/>
+      <c r="AAW1" t="inlineStr"/>
+      <c r="AAX1" t="inlineStr"/>
+      <c r="AAY1" t="inlineStr"/>
+      <c r="AAZ1" t="inlineStr"/>
+      <c r="ABA1" t="inlineStr"/>
+      <c r="ABB1" t="inlineStr"/>
+      <c r="ABC1" t="inlineStr"/>
+      <c r="ABD1" t="inlineStr"/>
+      <c r="ABE1" t="inlineStr"/>
+      <c r="ABF1" t="inlineStr"/>
+      <c r="ABG1" t="inlineStr"/>
+      <c r="ABH1" t="inlineStr"/>
+      <c r="ABI1" t="inlineStr"/>
+      <c r="ABJ1" t="inlineStr"/>
+      <c r="ABK1" t="inlineStr"/>
+      <c r="ABL1" t="inlineStr"/>
+      <c r="ABM1" t="inlineStr"/>
+      <c r="ABN1" t="inlineStr"/>
+      <c r="ABO1" t="inlineStr"/>
+      <c r="ABP1" t="inlineStr"/>
+      <c r="ABQ1" t="inlineStr"/>
+      <c r="ABR1" t="inlineStr"/>
+      <c r="ABS1" t="inlineStr"/>
+      <c r="ABT1" t="inlineStr"/>
+      <c r="ABU1" t="inlineStr"/>
+      <c r="ABV1" t="inlineStr"/>
+      <c r="ABW1" t="inlineStr"/>
+      <c r="ABX1" t="inlineStr"/>
+      <c r="ABY1" t="inlineStr"/>
+      <c r="ABZ1" t="inlineStr"/>
+      <c r="ACA1" t="inlineStr"/>
+      <c r="ACB1" t="inlineStr"/>
+      <c r="ACC1" t="inlineStr"/>
+      <c r="ACD1" t="inlineStr"/>
+      <c r="ACE1" t="inlineStr"/>
+      <c r="ACF1" t="inlineStr"/>
+      <c r="ACG1" t="inlineStr"/>
+      <c r="ACH1" t="inlineStr"/>
+      <c r="ACI1" t="inlineStr"/>
+      <c r="ACJ1" t="inlineStr"/>
+      <c r="ACK1" t="inlineStr"/>
+      <c r="ACL1" t="inlineStr"/>
+      <c r="ACM1" t="inlineStr"/>
+      <c r="ACN1" t="inlineStr"/>
+      <c r="ACO1" t="inlineStr"/>
+      <c r="ACP1" t="inlineStr"/>
+      <c r="ACQ1" t="inlineStr"/>
+      <c r="ACR1" t="inlineStr"/>
+      <c r="ACS1" t="inlineStr"/>
+      <c r="ACT1" t="inlineStr"/>
+      <c r="ACU1" t="inlineStr"/>
+      <c r="ACV1" t="inlineStr"/>
+      <c r="ACW1" t="inlineStr"/>
+      <c r="ACX1" t="inlineStr"/>
+      <c r="ACY1" t="inlineStr"/>
+      <c r="ACZ1" t="inlineStr"/>
+      <c r="ADA1" t="inlineStr"/>
+      <c r="ADB1" t="inlineStr"/>
+      <c r="ADC1" t="inlineStr"/>
+      <c r="ADD1" t="inlineStr"/>
+      <c r="ADE1" t="inlineStr"/>
+      <c r="ADF1" t="inlineStr"/>
+      <c r="ADG1" t="inlineStr"/>
+      <c r="ADH1" t="inlineStr"/>
+      <c r="ADI1" t="inlineStr"/>
+      <c r="ADJ1" t="inlineStr"/>
+      <c r="ADK1" t="inlineStr"/>
+      <c r="ADL1" t="inlineStr"/>
+      <c r="ADM1" t="inlineStr"/>
+      <c r="ADN1" t="inlineStr"/>
+      <c r="ADO1" t="inlineStr"/>
+      <c r="ADP1" t="inlineStr"/>
+      <c r="ADQ1" t="inlineStr"/>
+      <c r="ADR1" t="inlineStr"/>
+      <c r="ADS1" t="inlineStr"/>
+      <c r="ADT1" t="inlineStr"/>
+      <c r="ADU1" t="inlineStr"/>
+      <c r="ADV1" t="inlineStr"/>
+      <c r="ADW1" t="inlineStr"/>
+      <c r="ADX1" t="inlineStr"/>
+      <c r="ADY1" t="inlineStr"/>
+      <c r="ADZ1" t="inlineStr"/>
+      <c r="AEA1" t="inlineStr"/>
+      <c r="AEB1" t="inlineStr"/>
+      <c r="AEC1" t="inlineStr"/>
+      <c r="AED1" t="inlineStr"/>
+      <c r="AEE1" t="inlineStr"/>
+      <c r="AEF1" t="inlineStr"/>
+      <c r="AEG1" t="inlineStr"/>
+      <c r="AEH1" t="inlineStr"/>
+      <c r="AEI1" t="inlineStr"/>
+      <c r="AEJ1" t="inlineStr"/>
+      <c r="AEK1" t="inlineStr"/>
+      <c r="AEL1" t="inlineStr"/>
+      <c r="AEM1" t="inlineStr"/>
+      <c r="AEN1" t="inlineStr"/>
+      <c r="AEO1" t="inlineStr"/>
+      <c r="AEP1" t="inlineStr"/>
+      <c r="AEQ1" t="inlineStr"/>
+      <c r="AER1" t="inlineStr"/>
+      <c r="AES1" t="inlineStr"/>
+      <c r="AET1" t="inlineStr"/>
+      <c r="AEU1" t="inlineStr"/>
+      <c r="AEV1" t="inlineStr"/>
+      <c r="AEW1" t="inlineStr"/>
+      <c r="AEX1" t="inlineStr"/>
+      <c r="AEY1" t="inlineStr"/>
+      <c r="AEZ1" t="inlineStr"/>
+      <c r="AFA1" t="inlineStr"/>
+      <c r="AFB1" t="inlineStr"/>
+      <c r="AFC1" t="inlineStr"/>
+      <c r="AFD1" t="inlineStr"/>
+      <c r="AFE1" t="inlineStr"/>
+      <c r="AFF1" t="inlineStr"/>
+      <c r="AFG1" t="inlineStr"/>
+      <c r="AFH1" t="inlineStr"/>
+      <c r="AFI1" t="inlineStr"/>
+      <c r="AFJ1" t="inlineStr"/>
+      <c r="AFK1" t="inlineStr"/>
+      <c r="AFL1" t="inlineStr"/>
+      <c r="AFM1" t="inlineStr"/>
+      <c r="AFN1" t="inlineStr"/>
+      <c r="AFO1" t="inlineStr"/>
+      <c r="AFP1" t="inlineStr"/>
+      <c r="AFQ1" t="inlineStr"/>
+      <c r="AFR1" t="inlineStr"/>
+      <c r="AFS1" t="inlineStr"/>
+      <c r="AFT1" t="inlineStr"/>
+      <c r="AFU1" t="inlineStr"/>
+      <c r="AFV1" t="inlineStr"/>
+      <c r="AFW1" t="inlineStr"/>
+      <c r="AFX1" t="inlineStr"/>
+      <c r="AFY1" t="inlineStr"/>
+      <c r="AFZ1" t="inlineStr"/>
+      <c r="AGA1" t="inlineStr"/>
+      <c r="AGB1" t="inlineStr"/>
+      <c r="AGC1" t="inlineStr"/>
+      <c r="AGD1" t="inlineStr"/>
+      <c r="AGE1" t="inlineStr"/>
+      <c r="AGF1" t="inlineStr"/>
+      <c r="AGG1" t="inlineStr"/>
+      <c r="AGH1" t="inlineStr"/>
+      <c r="AGI1" t="inlineStr"/>
+      <c r="AGJ1" t="inlineStr"/>
+      <c r="AGK1" t="inlineStr"/>
+      <c r="AGL1" t="inlineStr"/>
+      <c r="AGM1" t="inlineStr"/>
+      <c r="AGN1" t="inlineStr"/>
+      <c r="AGO1" t="inlineStr"/>
+      <c r="AGP1" t="inlineStr"/>
+      <c r="AGQ1" t="inlineStr"/>
+      <c r="AGR1" t="inlineStr"/>
+      <c r="AGS1" t="inlineStr"/>
+      <c r="AGT1" t="inlineStr"/>
+      <c r="AGU1" t="inlineStr"/>
+      <c r="AGV1" t="inlineStr"/>
+      <c r="AGW1" t="inlineStr"/>
+      <c r="AGX1" t="inlineStr"/>
+      <c r="AGY1" t="inlineStr"/>
+      <c r="AGZ1" t="inlineStr"/>
+      <c r="AHA1" t="inlineStr"/>
+      <c r="AHB1" t="inlineStr"/>
+      <c r="AHC1" t="inlineStr"/>
+      <c r="AHD1" t="inlineStr"/>
+      <c r="AHE1" t="inlineStr"/>
+      <c r="AHF1" t="inlineStr"/>
+      <c r="AHG1" t="inlineStr"/>
+      <c r="AHH1" t="inlineStr"/>
+      <c r="AHI1" t="inlineStr"/>
+      <c r="AHJ1" t="inlineStr"/>
+      <c r="AHK1" t="inlineStr"/>
+      <c r="AHL1" t="inlineStr"/>
+      <c r="AHM1" t="inlineStr"/>
+      <c r="AHN1" t="inlineStr"/>
+      <c r="AHO1" t="inlineStr"/>
+      <c r="AHP1" t="inlineStr"/>
+      <c r="AHQ1" t="inlineStr"/>
+      <c r="AHR1" t="inlineStr"/>
+      <c r="AHS1" t="inlineStr"/>
+      <c r="AHT1" t="inlineStr"/>
+      <c r="AHU1" t="inlineStr"/>
+      <c r="AHV1" t="inlineStr"/>
+      <c r="AHW1" t="inlineStr"/>
+      <c r="AHX1" t="inlineStr"/>
+      <c r="AHY1" t="inlineStr"/>
+      <c r="AHZ1" t="inlineStr"/>
+      <c r="AIA1" t="inlineStr"/>
+      <c r="AIB1" t="inlineStr"/>
+      <c r="AIC1" t="inlineStr"/>
+      <c r="AID1" t="inlineStr"/>
+      <c r="AIE1" t="inlineStr"/>
+      <c r="AIF1" t="inlineStr"/>
+      <c r="AIG1" t="inlineStr"/>
+      <c r="AIH1" t="inlineStr"/>
+      <c r="AII1" t="inlineStr"/>
+      <c r="AIJ1" t="inlineStr"/>
+      <c r="AIK1" t="inlineStr"/>
+      <c r="AIL1" t="inlineStr"/>
+      <c r="AIM1" t="inlineStr"/>
+      <c r="AIN1" t="inlineStr"/>
+      <c r="AIO1" t="inlineStr"/>
+      <c r="AIP1" t="inlineStr"/>
+      <c r="AIQ1" t="inlineStr"/>
+      <c r="AIR1" t="inlineStr"/>
+      <c r="AIS1" t="inlineStr"/>
+      <c r="AIT1" t="inlineStr"/>
+      <c r="AIU1" t="inlineStr"/>
+      <c r="AIV1" t="inlineStr"/>
+      <c r="AIW1" t="inlineStr"/>
+      <c r="AIX1" t="inlineStr"/>
+      <c r="AIY1" t="inlineStr"/>
+      <c r="AIZ1" t="inlineStr"/>
+      <c r="AJA1" t="inlineStr"/>
+      <c r="AJB1" t="inlineStr"/>
+      <c r="AJC1" t="inlineStr"/>
+      <c r="AJD1" t="inlineStr"/>
+      <c r="AJE1" t="inlineStr"/>
+      <c r="AJF1" t="inlineStr"/>
+      <c r="AJG1" t="inlineStr"/>
+      <c r="AJH1" t="inlineStr"/>
+      <c r="AJI1" t="inlineStr"/>
+      <c r="AJJ1" t="inlineStr"/>
+      <c r="AJK1" t="inlineStr"/>
+      <c r="AJL1" t="inlineStr"/>
+      <c r="AJM1" t="inlineStr"/>
+      <c r="AJN1" t="inlineStr"/>
+      <c r="AJO1" t="inlineStr"/>
+      <c r="AJP1" t="inlineStr"/>
+      <c r="AJQ1" t="inlineStr"/>
+      <c r="AJR1" t="inlineStr"/>
+      <c r="AJS1" t="inlineStr"/>
+      <c r="AJT1" t="inlineStr"/>
+      <c r="AJU1" t="inlineStr"/>
+      <c r="AJV1" t="inlineStr"/>
+      <c r="AJW1" t="inlineStr"/>
+      <c r="AJX1" t="inlineStr"/>
+      <c r="AJY1" t="inlineStr"/>
+      <c r="AJZ1" t="inlineStr"/>
+      <c r="AKA1" t="inlineStr"/>
+      <c r="AKB1" t="inlineStr"/>
+      <c r="AKC1" t="inlineStr"/>
+      <c r="AKD1" t="inlineStr"/>
+      <c r="AKE1" t="inlineStr"/>
+      <c r="AKF1" t="inlineStr"/>
+      <c r="AKG1" t="inlineStr"/>
+      <c r="AKH1" t="inlineStr"/>
+      <c r="AKI1" t="inlineStr"/>
+      <c r="AKJ1" t="inlineStr"/>
+      <c r="AKK1" t="inlineStr"/>
+      <c r="AKL1" t="inlineStr"/>
+      <c r="AKM1" t="inlineStr"/>
+      <c r="AKN1" t="inlineStr"/>
+      <c r="AKO1" t="inlineStr"/>
+      <c r="AKP1" t="inlineStr"/>
+      <c r="AKQ1" t="inlineStr"/>
+      <c r="AKR1" t="inlineStr"/>
+      <c r="AKS1" t="inlineStr"/>
+      <c r="AKT1" t="inlineStr"/>
+      <c r="AKU1" t="inlineStr"/>
+      <c r="AKV1" t="inlineStr"/>
+      <c r="AKW1" t="inlineStr"/>
+      <c r="AKX1" t="inlineStr"/>
+      <c r="AKY1" t="inlineStr"/>
+      <c r="AKZ1" t="inlineStr"/>
+      <c r="ALA1" t="inlineStr"/>
+      <c r="ALB1" t="inlineStr"/>
+      <c r="ALC1" t="inlineStr"/>
+      <c r="ALD1" t="inlineStr"/>
+      <c r="ALE1" t="inlineStr"/>
+      <c r="ALF1" t="inlineStr"/>
+      <c r="ALG1" t="inlineStr"/>
+      <c r="ALH1" t="inlineStr"/>
+      <c r="ALI1" t="inlineStr"/>
+      <c r="ALJ1" t="inlineStr"/>
+      <c r="ALK1" t="inlineStr"/>
+      <c r="ALL1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53972</v>
+        <v>1084716</v>
       </c>
       <c r="B2" t="n">
-        <v>47051</v>
+        <v>431034</v>
       </c>
       <c r="C2" t="n">
-        <v>48951</v>
+        <v>757678</v>
       </c>
       <c r="D2" t="n">
-        <v>116251</v>
+        <v>1161050</v>
       </c>
       <c r="E2" t="n">
-        <v>105909</v>
+        <v>1037735</v>
       </c>
       <c r="F2" t="n">
-        <v>66654</v>
+        <v>652443</v>
       </c>
       <c r="G2" t="n">
-        <v>107293</v>
+        <v>1172186</v>
       </c>
       <c r="H2" t="n">
-        <v>94577</v>
+        <v>1644</v>
       </c>
       <c r="I2" t="n">
-        <v>72178</v>
+        <v>1117596</v>
       </c>
       <c r="J2" t="n">
-        <v>55681</v>
+        <v>566986</v>
       </c>
       <c r="K2" t="n">
-        <v>33086</v>
+        <v>591524</v>
       </c>
       <c r="L2" t="n">
-        <v>87548</v>
+        <v>931747</v>
       </c>
       <c r="M2" t="n">
-        <v>9150</v>
+        <v>1009722</v>
       </c>
       <c r="N2" t="n">
-        <v>67940</v>
+        <v>687469</v>
       </c>
       <c r="O2" t="n">
-        <v>44138</v>
+        <v>353511</v>
       </c>
       <c r="P2" t="n">
-        <v>12255</v>
+        <v>387691</v>
       </c>
       <c r="Q2" t="n">
-        <v>49689</v>
+        <v>681009</v>
       </c>
       <c r="R2" t="n">
-        <v>49230</v>
+        <v>309797</v>
       </c>
       <c r="S2" t="n">
-        <v>39417</v>
+        <v>524678</v>
       </c>
       <c r="T2" t="n">
-        <v>32233</v>
+        <v>1060182</v>
       </c>
       <c r="U2" t="n">
-        <v>128001</v>
+        <v>314578</v>
       </c>
       <c r="V2" t="n">
-        <v>124714</v>
+        <v>1153689</v>
       </c>
       <c r="W2" t="n">
-        <v>95618</v>
+        <v>510611</v>
       </c>
       <c r="X2" t="n">
-        <v>112164</v>
+        <v>1186739</v>
       </c>
       <c r="Y2" t="n">
-        <v>131546</v>
+        <v>830904</v>
       </c>
       <c r="Z2" t="n">
-        <v>42226</v>
+        <v>892423</v>
       </c>
       <c r="AA2" t="n">
-        <v>36933</v>
+        <v>317034</v>
       </c>
       <c r="AB2" t="n">
-        <v>69810</v>
+        <v>1012288</v>
       </c>
       <c r="AC2" t="n">
-        <v>12598</v>
+        <v>122205</v>
       </c>
       <c r="AD2" t="n">
-        <v>62818</v>
+        <v>680099</v>
       </c>
       <c r="AE2" t="n">
-        <v>3937</v>
+        <v>451039</v>
       </c>
       <c r="AF2" t="n">
-        <v>118482</v>
+        <v>713376</v>
       </c>
       <c r="AG2" t="n">
-        <v>104735</v>
+        <v>414737</v>
       </c>
       <c r="AH2" t="n">
-        <v>59353</v>
+        <v>868285</v>
       </c>
       <c r="AI2" t="n">
-        <v>28799</v>
+        <v>383158</v>
       </c>
       <c r="AJ2" t="n">
-        <v>98504</v>
+        <v>1051908</v>
       </c>
       <c r="AK2" t="n">
-        <v>80411</v>
+        <v>226406</v>
       </c>
       <c r="AL2" t="n">
-        <v>96381</v>
+        <v>1226112</v>
       </c>
       <c r="AM2" t="n">
-        <v>116653</v>
+        <v>284496</v>
       </c>
       <c r="AN2" t="n">
-        <v>78516</v>
+        <v>157100</v>
       </c>
       <c r="AO2" t="n">
-        <v>6638</v>
+        <v>856999</v>
       </c>
       <c r="AP2" t="n">
-        <v>21308</v>
+        <v>152992</v>
       </c>
       <c r="AQ2" t="n">
-        <v>110228</v>
+        <v>873394</v>
       </c>
       <c r="AR2" t="n">
-        <v>125430</v>
+        <v>2030</v>
       </c>
       <c r="AS2" t="n">
-        <v>44103</v>
+        <v>1142114</v>
       </c>
       <c r="AT2" t="n">
-        <v>73059</v>
+        <v>807568</v>
       </c>
       <c r="AU2" t="n">
-        <v>1641</v>
+        <v>1033529</v>
       </c>
       <c r="AV2" t="n">
-        <v>23531</v>
+        <v>71895</v>
       </c>
       <c r="AW2" t="n">
-        <v>109252</v>
+        <v>460710</v>
       </c>
       <c r="AX2" t="n">
-        <v>56980</v>
+        <v>528527</v>
       </c>
       <c r="AY2" t="n">
-        <v>127987</v>
+        <v>464506</v>
       </c>
       <c r="AZ2" t="n">
-        <v>76335</v>
+        <v>12704</v>
       </c>
       <c r="BA2" t="n">
-        <v>42755</v>
+        <v>1125254</v>
       </c>
       <c r="BB2" t="n">
-        <v>35187</v>
+        <v>86451</v>
       </c>
       <c r="BC2" t="n">
-        <v>16947</v>
+        <v>369024</v>
       </c>
       <c r="BD2" t="n">
-        <v>27309</v>
+        <v>306101</v>
       </c>
       <c r="BE2" t="n">
-        <v>91940</v>
+        <v>477641</v>
       </c>
       <c r="BF2" t="n">
-        <v>3139</v>
+        <v>1139727</v>
       </c>
       <c r="BG2" t="n">
-        <v>38329</v>
+        <v>563210</v>
       </c>
       <c r="BH2" t="n">
-        <v>36533</v>
+        <v>581942</v>
       </c>
       <c r="BI2" t="n">
-        <v>30912</v>
+        <v>73726</v>
       </c>
       <c r="BJ2" t="n">
-        <v>93</v>
+        <v>131078</v>
       </c>
       <c r="BK2" t="n">
-        <v>64975</v>
+        <v>1065874</v>
       </c>
       <c r="BL2" t="n">
-        <v>74051</v>
+        <v>58266</v>
       </c>
       <c r="BM2" t="n">
-        <v>100434</v>
+        <v>733003</v>
       </c>
       <c r="BN2" t="n">
-        <v>80497</v>
+        <v>159095</v>
       </c>
       <c r="BO2" t="n">
-        <v>60044</v>
+        <v>387219</v>
       </c>
       <c r="BP2" t="n">
-        <v>83911</v>
+        <v>591248</v>
       </c>
       <c r="BQ2" t="n">
-        <v>92892</v>
+        <v>190176</v>
       </c>
       <c r="BR2" t="n">
-        <v>20828</v>
+        <v>958066</v>
       </c>
       <c r="BS2" t="n">
-        <v>83481</v>
+        <v>214965</v>
       </c>
       <c r="BT2" t="n">
-        <v>93118</v>
+        <v>886407</v>
       </c>
       <c r="BU2" t="n">
-        <v>52584</v>
+        <v>456483</v>
       </c>
       <c r="BV2" t="n">
-        <v>54758</v>
+        <v>210515</v>
       </c>
       <c r="BW2" t="n">
-        <v>85057</v>
+        <v>819759</v>
       </c>
       <c r="BX2" t="n">
+        <v>916485</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>450094</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>891522</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>178867</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>713622</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>766396</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>65555</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>451846</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>432720</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>593047</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>612194</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>49588</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>800616</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>991947</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>879995</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>519118</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>323364</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>762947</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>1143835</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>1000298</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>1172426</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>283779</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>1006658</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>901881</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>1216460</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>819670</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>710279</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>606928</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>1114858</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>371295</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>102560</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>243191</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>319183</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>881438</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>660051</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1017750</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>817569</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>427721</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>615835</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>27969</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>839184</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>1103591</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>780899</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>922061</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>637382</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1112162</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>379205</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>694297</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>579115</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>812919</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1166109</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>858410</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>402893</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>624733</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1067769</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>348256</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>775615</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>1081843</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>114211</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>669659</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>131160</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>215711</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>742707</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>829117</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>1029090</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>24500</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>322116</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>976683</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>377301</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>630943</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>121640</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>32807</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>400111</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>251616</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>741766</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>234640</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>292860</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>563927</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>1123325</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>754766</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>757235</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>303236</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>1102570</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>734131</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>694084</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>876095</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>152051</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>452924</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>520901</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>959533</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>39531</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>909428</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>45537</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>360138</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>9609</v>
+      </c>
+      <c r="FO2" t="n">
+        <v>13231</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>544179</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>231514</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>1213492</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>482821</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>1198184</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>736709</v>
+      </c>
+      <c r="FV2" t="n">
+        <v>296871</v>
+      </c>
+      <c r="FW2" t="n">
+        <v>1214405</v>
+      </c>
+      <c r="FX2" t="n">
+        <v>823637</v>
+      </c>
+      <c r="FY2" t="n">
+        <v>683015</v>
+      </c>
+      <c r="FZ2" t="n">
+        <v>796842</v>
+      </c>
+      <c r="GA2" t="n">
+        <v>234137</v>
+      </c>
+      <c r="GB2" t="n">
+        <v>721698</v>
+      </c>
+      <c r="GC2" t="n">
+        <v>197228</v>
+      </c>
+      <c r="GD2" t="n">
+        <v>532297</v>
+      </c>
+      <c r="GE2" t="n">
+        <v>309230</v>
+      </c>
+      <c r="GF2" t="n">
+        <v>280388</v>
+      </c>
+      <c r="GG2" t="n">
+        <v>928394</v>
+      </c>
+      <c r="GH2" t="n">
+        <v>36825</v>
+      </c>
+      <c r="GI2" t="n">
+        <v>1057565</v>
+      </c>
+      <c r="GJ2" t="n">
+        <v>93526</v>
+      </c>
+      <c r="GK2" t="n">
+        <v>609977</v>
+      </c>
+      <c r="GL2" t="n">
+        <v>981102</v>
+      </c>
+      <c r="GM2" t="n">
+        <v>550032</v>
+      </c>
+      <c r="GN2" t="n">
+        <v>1057303</v>
+      </c>
+      <c r="GO2" t="n">
+        <v>510017</v>
+      </c>
+      <c r="GP2" t="n">
+        <v>110907</v>
+      </c>
+      <c r="GQ2" t="n">
+        <v>56238</v>
+      </c>
+      <c r="GR2" t="n">
+        <v>130137</v>
+      </c>
+      <c r="GS2" t="n">
+        <v>549450</v>
+      </c>
+      <c r="GT2" t="n">
+        <v>100082</v>
+      </c>
+      <c r="GU2" t="n">
+        <v>263564</v>
+      </c>
+      <c r="GV2" t="n">
+        <v>134502</v>
+      </c>
+      <c r="GW2" t="n">
+        <v>408061</v>
+      </c>
+      <c r="GX2" t="n">
+        <v>658235</v>
+      </c>
+      <c r="GY2" t="n">
+        <v>138160</v>
+      </c>
+      <c r="GZ2" t="n">
+        <v>15783</v>
+      </c>
+      <c r="HA2" t="n">
+        <v>904082</v>
+      </c>
+      <c r="HB2" t="n">
+        <v>1046322</v>
+      </c>
+      <c r="HC2" t="n">
+        <v>240293</v>
+      </c>
+      <c r="HD2" t="n">
+        <v>365588</v>
+      </c>
+      <c r="HE2" t="n">
+        <v>688920</v>
+      </c>
+      <c r="HF2" t="n">
+        <v>356945</v>
+      </c>
+      <c r="HG2" t="n">
+        <v>618860</v>
+      </c>
+      <c r="HH2" t="n">
+        <v>65411</v>
+      </c>
+      <c r="HI2" t="n">
+        <v>863038</v>
+      </c>
+      <c r="HJ2" t="n">
+        <v>826674</v>
+      </c>
+      <c r="HK2" t="n">
+        <v>1181507</v>
+      </c>
+      <c r="HL2" t="n">
+        <v>453409</v>
+      </c>
+      <c r="HM2" t="n">
+        <v>696686</v>
+      </c>
+      <c r="HN2" t="n">
+        <v>668193</v>
+      </c>
+      <c r="HO2" t="n">
+        <v>661195</v>
+      </c>
+      <c r="HP2" t="n">
+        <v>225642</v>
+      </c>
+      <c r="HQ2" t="n">
+        <v>1093389</v>
+      </c>
+      <c r="HR2" t="n">
+        <v>1208281</v>
+      </c>
+      <c r="HS2" t="n">
+        <v>663816</v>
+      </c>
+      <c r="HT2" t="n">
+        <v>900796</v>
+      </c>
+      <c r="HU2" t="n">
+        <v>939721</v>
+      </c>
+      <c r="HV2" t="n">
+        <v>262690</v>
+      </c>
+      <c r="HW2" t="n">
+        <v>14071</v>
+      </c>
+      <c r="HX2" t="n">
+        <v>1071396</v>
+      </c>
+      <c r="HY2" t="n">
+        <v>274375</v>
+      </c>
+      <c r="HZ2" t="n">
+        <v>165335</v>
+      </c>
+      <c r="IA2" t="n">
+        <v>940926</v>
+      </c>
+      <c r="IB2" t="n">
+        <v>1014488</v>
+      </c>
+      <c r="IC2" t="n">
+        <v>332368</v>
+      </c>
+      <c r="ID2" t="n">
+        <v>394925</v>
+      </c>
+      <c r="IE2" t="n">
+        <v>604746</v>
+      </c>
+      <c r="IF2" t="n">
+        <v>493762</v>
+      </c>
+      <c r="IG2" t="n">
+        <v>5421</v>
+      </c>
+      <c r="IH2" t="n">
+        <v>1224138</v>
+      </c>
+      <c r="II2" t="n">
+        <v>15088</v>
+      </c>
+      <c r="IJ2" t="n">
+        <v>1088032</v>
+      </c>
+      <c r="IK2" t="n">
+        <v>835813</v>
+      </c>
+      <c r="IL2" t="n">
+        <v>1152213</v>
+      </c>
+      <c r="IM2" t="n">
+        <v>82437</v>
+      </c>
+      <c r="IN2" t="n">
+        <v>961587</v>
+      </c>
+      <c r="IO2" t="n">
+        <v>784204</v>
+      </c>
+      <c r="IP2" t="n">
+        <v>530284</v>
+      </c>
+      <c r="IQ2" t="n">
+        <v>271548</v>
+      </c>
+      <c r="IR2" t="n">
+        <v>1240200</v>
+      </c>
+      <c r="IS2" t="n">
+        <v>1184334</v>
+      </c>
+      <c r="IT2" t="n">
+        <v>479604</v>
+      </c>
+      <c r="IU2" t="n">
+        <v>627420</v>
+      </c>
+      <c r="IV2" t="n">
+        <v>1096438</v>
+      </c>
+      <c r="IW2" t="n">
+        <v>74324</v>
+      </c>
+      <c r="IX2" t="n">
+        <v>725464</v>
+      </c>
+      <c r="IY2" t="n">
+        <v>794635</v>
+      </c>
+      <c r="IZ2" t="n">
+        <v>281482</v>
+      </c>
+      <c r="JA2" t="n">
+        <v>534813</v>
+      </c>
+      <c r="JB2" t="n">
+        <v>168990</v>
+      </c>
+      <c r="JC2" t="n">
+        <v>1054148</v>
+      </c>
+      <c r="JD2" t="n">
+        <v>260615</v>
+      </c>
+      <c r="JE2" t="n">
+        <v>1004946</v>
+      </c>
+      <c r="JF2" t="n">
+        <v>500571</v>
+      </c>
+      <c r="JG2" t="n">
+        <v>162454</v>
+      </c>
+      <c r="JH2" t="n">
+        <v>673315</v>
+      </c>
+      <c r="JI2" t="n">
+        <v>107986</v>
+      </c>
+      <c r="JJ2" t="n">
+        <v>760371</v>
+      </c>
+      <c r="JK2" t="n">
+        <v>1169124</v>
+      </c>
+      <c r="JL2" t="n">
+        <v>327343</v>
+      </c>
+      <c r="JM2" t="n">
+        <v>151183</v>
+      </c>
+      <c r="JN2" t="n">
+        <v>919991</v>
+      </c>
+      <c r="JO2" t="n">
+        <v>650005</v>
+      </c>
+      <c r="JP2" t="n">
+        <v>1230195</v>
+      </c>
+      <c r="JQ2" t="n">
+        <v>968930</v>
+      </c>
+      <c r="JR2" t="n">
+        <v>192048</v>
+      </c>
+      <c r="JS2" t="n">
+        <v>571694</v>
+      </c>
+      <c r="JT2" t="n">
+        <v>986773</v>
+      </c>
+      <c r="JU2" t="n">
+        <v>605612</v>
+      </c>
+      <c r="JV2" t="n">
+        <v>517161</v>
+      </c>
+      <c r="JW2" t="n">
+        <v>347156</v>
+      </c>
+      <c r="JX2" t="n">
+        <v>805838</v>
+      </c>
+      <c r="JY2" t="n">
+        <v>1021866</v>
+      </c>
+      <c r="JZ2" t="n">
+        <v>727325</v>
+      </c>
+      <c r="KA2" t="n">
+        <v>1036297</v>
+      </c>
+      <c r="KB2" t="n">
+        <v>78610</v>
+      </c>
+      <c r="KC2" t="n">
+        <v>373977</v>
+      </c>
+      <c r="KD2" t="n">
+        <v>184617</v>
+      </c>
+      <c r="KE2" t="n">
+        <v>97734</v>
+      </c>
+      <c r="KF2" t="n">
+        <v>1147489</v>
+      </c>
+      <c r="KG2" t="n">
+        <v>387895</v>
+      </c>
+      <c r="KH2" t="n">
+        <v>236916</v>
+      </c>
+      <c r="KI2" t="n">
+        <v>850674</v>
+      </c>
+      <c r="KJ2" t="n">
+        <v>823273</v>
+      </c>
+      <c r="KK2" t="n">
+        <v>1044860</v>
+      </c>
+      <c r="KL2" t="n">
+        <v>561643</v>
+      </c>
+      <c r="KM2" t="n">
+        <v>383278</v>
+      </c>
+      <c r="KN2" t="n">
+        <v>326409</v>
+      </c>
+      <c r="KO2" t="n">
+        <v>1038918</v>
+      </c>
+      <c r="KP2" t="n">
+        <v>973068</v>
+      </c>
+      <c r="KQ2" t="n">
+        <v>431223</v>
+      </c>
+      <c r="KR2" t="n">
+        <v>873880</v>
+      </c>
+      <c r="KS2" t="n">
+        <v>182208</v>
+      </c>
+      <c r="KT2" t="n">
+        <v>676882</v>
+      </c>
+      <c r="KU2" t="n">
+        <v>135770</v>
+      </c>
+      <c r="KV2" t="n">
+        <v>60008</v>
+      </c>
+      <c r="KW2" t="n">
+        <v>487836</v>
+      </c>
+      <c r="KX2" t="n">
+        <v>896546</v>
+      </c>
+      <c r="KY2" t="n">
+        <v>330219</v>
+      </c>
+      <c r="KZ2" t="n">
+        <v>975023</v>
+      </c>
+      <c r="LA2" t="n">
+        <v>205044</v>
+      </c>
+      <c r="LB2" t="n">
+        <v>250593</v>
+      </c>
+      <c r="LC2" t="n">
+        <v>365332</v>
+      </c>
+      <c r="LD2" t="n">
+        <v>677884</v>
+      </c>
+      <c r="LE2" t="n">
+        <v>814973</v>
+      </c>
+      <c r="LF2" t="n">
+        <v>470540</v>
+      </c>
+      <c r="LG2" t="n">
+        <v>505122</v>
+      </c>
+      <c r="LH2" t="n">
+        <v>21625</v>
+      </c>
+      <c r="LI2" t="n">
+        <v>1113881</v>
+      </c>
+      <c r="LJ2" t="n">
+        <v>973673</v>
+      </c>
+      <c r="LK2" t="n">
+        <v>933750</v>
+      </c>
+      <c r="LL2" t="n">
+        <v>296756</v>
+      </c>
+      <c r="LM2" t="n">
+        <v>242020</v>
+      </c>
+      <c r="LN2" t="n">
+        <v>716774</v>
+      </c>
+      <c r="LO2" t="n">
+        <v>174267</v>
+      </c>
+      <c r="LP2" t="n">
+        <v>363538</v>
+      </c>
+      <c r="LQ2" t="n">
+        <v>571457</v>
+      </c>
+      <c r="LR2" t="n">
+        <v>558358</v>
+      </c>
+      <c r="LS2" t="n">
+        <v>553784</v>
+      </c>
+      <c r="LT2" t="n">
+        <v>787966</v>
+      </c>
+      <c r="LU2" t="n">
+        <v>287757</v>
+      </c>
+      <c r="LV2" t="n">
+        <v>184995</v>
+      </c>
+      <c r="LW2" t="n">
+        <v>443256</v>
+      </c>
+      <c r="LX2" t="n">
+        <v>748319</v>
+      </c>
+      <c r="LY2" t="n">
+        <v>27713</v>
+      </c>
+      <c r="LZ2" t="n">
+        <v>667146</v>
+      </c>
+      <c r="MA2" t="n">
+        <v>540496</v>
+      </c>
+      <c r="MB2" t="n">
+        <v>776584</v>
+      </c>
+      <c r="MC2" t="n">
+        <v>805280</v>
+      </c>
+      <c r="MD2" t="n">
+        <v>383032</v>
+      </c>
+      <c r="ME2" t="n">
+        <v>201394</v>
+      </c>
+      <c r="MF2" t="n">
+        <v>142986</v>
+      </c>
+      <c r="MG2" t="n">
+        <v>569197</v>
+      </c>
+      <c r="MH2" t="n">
+        <v>1153127</v>
+      </c>
+      <c r="MI2" t="n">
+        <v>313710</v>
+      </c>
+      <c r="MJ2" t="n">
+        <v>511830</v>
+      </c>
+      <c r="MK2" t="n">
+        <v>674767</v>
+      </c>
+      <c r="ML2" t="n">
+        <v>854265</v>
+      </c>
+      <c r="MM2" t="n">
+        <v>523533</v>
+      </c>
+      <c r="MN2" t="n">
+        <v>956584</v>
+      </c>
+      <c r="MO2" t="n">
+        <v>75515</v>
+      </c>
+      <c r="MP2" t="n">
+        <v>740148</v>
+      </c>
+      <c r="MQ2" t="n">
+        <v>1171647</v>
+      </c>
+      <c r="MR2" t="n">
+        <v>953145</v>
+      </c>
+      <c r="MS2" t="n">
+        <v>1090891</v>
+      </c>
+      <c r="MT2" t="n">
+        <v>209903</v>
+      </c>
+      <c r="MU2" t="n">
+        <v>183981</v>
+      </c>
+      <c r="MV2" t="n">
+        <v>252892</v>
+      </c>
+      <c r="MW2" t="n">
+        <v>919483</v>
+      </c>
+      <c r="MX2" t="n">
+        <v>237144</v>
+      </c>
+      <c r="MY2" t="n">
+        <v>601718</v>
+      </c>
+      <c r="MZ2" t="n">
+        <v>1075300</v>
+      </c>
+      <c r="NA2" t="n">
+        <v>241003</v>
+      </c>
+      <c r="NB2" t="n">
+        <v>935697</v>
+      </c>
+      <c r="NC2" t="n">
+        <v>34698</v>
+      </c>
+      <c r="ND2" t="n">
+        <v>539460</v>
+      </c>
+      <c r="NE2" t="n">
+        <v>215024</v>
+      </c>
+      <c r="NF2" t="n">
+        <v>599150</v>
+      </c>
+      <c r="NG2" t="n">
+        <v>269731</v>
+      </c>
+      <c r="NH2" t="n">
+        <v>264966</v>
+      </c>
+      <c r="NI2" t="n">
+        <v>343819</v>
+      </c>
+      <c r="NJ2" t="n">
+        <v>140112</v>
+      </c>
+      <c r="NK2" t="n">
+        <v>773232</v>
+      </c>
+      <c r="NL2" t="n">
+        <v>448432</v>
+      </c>
+      <c r="NM2" t="n">
+        <v>392922</v>
+      </c>
+      <c r="NN2" t="n">
+        <v>1236715</v>
+      </c>
+      <c r="NO2" t="n">
+        <v>147214</v>
+      </c>
+      <c r="NP2" t="n">
+        <v>948384</v>
+      </c>
+      <c r="NQ2" t="n">
+        <v>188001</v>
+      </c>
+      <c r="NR2" t="n">
+        <v>1134671</v>
+      </c>
+      <c r="NS2" t="n">
+        <v>407394</v>
+      </c>
+      <c r="NT2" t="n">
+        <v>1180524</v>
+      </c>
+      <c r="NU2" t="n">
+        <v>298675</v>
+      </c>
+      <c r="NV2" t="n">
+        <v>851739</v>
+      </c>
+      <c r="NW2" t="n">
+        <v>167105</v>
+      </c>
+      <c r="NX2" t="n">
+        <v>4309</v>
+      </c>
+      <c r="NY2" t="n">
+        <v>576767</v>
+      </c>
+      <c r="NZ2" t="n">
+        <v>708106</v>
+      </c>
+      <c r="OA2" t="n">
+        <v>545303</v>
+      </c>
+      <c r="OB2" t="n">
+        <v>843302</v>
+      </c>
+      <c r="OC2" t="n">
+        <v>468928</v>
+      </c>
+      <c r="OD2" t="n">
+        <v>507747</v>
+      </c>
+      <c r="OE2" t="n">
+        <v>1227931</v>
+      </c>
+      <c r="OF2" t="n">
+        <v>1019078</v>
+      </c>
+      <c r="OG2" t="n">
+        <v>419203</v>
+      </c>
+      <c r="OH2" t="n">
+        <v>376082</v>
+      </c>
+      <c r="OI2" t="n">
+        <v>425095</v>
+      </c>
+      <c r="OJ2" t="n">
+        <v>212017</v>
+      </c>
+      <c r="OK2" t="n">
+        <v>46861</v>
+      </c>
+      <c r="OL2" t="n">
+        <v>507306</v>
+      </c>
+      <c r="OM2" t="n">
+        <v>1067507</v>
+      </c>
+      <c r="ON2" t="n">
+        <v>533660</v>
+      </c>
+      <c r="OO2" t="n">
+        <v>125455</v>
+      </c>
+      <c r="OP2" t="n">
+        <v>491968</v>
+      </c>
+      <c r="OQ2" t="n">
+        <v>28433</v>
+      </c>
+      <c r="OR2" t="n">
+        <v>1157168</v>
+      </c>
+      <c r="OS2" t="n">
+        <v>540395</v>
+      </c>
+      <c r="OT2" t="n">
+        <v>728220</v>
+      </c>
+      <c r="OU2" t="n">
+        <v>757642</v>
+      </c>
+      <c r="OV2" t="n">
+        <v>705014</v>
+      </c>
+      <c r="OW2" t="n">
+        <v>298842</v>
+      </c>
+      <c r="OX2" t="n">
+        <v>1106403</v>
+      </c>
+      <c r="OY2" t="n">
+        <v>634361</v>
+      </c>
+      <c r="OZ2" t="n">
+        <v>571221</v>
+      </c>
+      <c r="PA2" t="n">
+        <v>1200064</v>
+      </c>
+      <c r="PB2" t="n">
+        <v>1129810</v>
+      </c>
+      <c r="PC2" t="n">
+        <v>516057</v>
+      </c>
+      <c r="PD2" t="n">
+        <v>1119580</v>
+      </c>
+      <c r="PE2" t="n">
+        <v>455415</v>
+      </c>
+      <c r="PF2" t="n">
+        <v>503266</v>
+      </c>
+      <c r="PG2" t="n">
+        <v>414188</v>
+      </c>
+      <c r="PH2" t="n">
+        <v>574801</v>
+      </c>
+      <c r="PI2" t="n">
+        <v>732207</v>
+      </c>
+      <c r="PJ2" t="n">
+        <v>396782</v>
+      </c>
+      <c r="PK2" t="n">
+        <v>1033774</v>
+      </c>
+      <c r="PL2" t="n">
+        <v>318478</v>
+      </c>
+      <c r="PM2" t="n">
+        <v>219987</v>
+      </c>
+      <c r="PN2" t="n">
+        <v>82215</v>
+      </c>
+      <c r="PO2" t="n">
+        <v>1121028</v>
+      </c>
+      <c r="PP2" t="n">
+        <v>586313</v>
+      </c>
+      <c r="PQ2" t="n">
+        <v>529547</v>
+      </c>
+      <c r="PR2" t="n">
+        <v>1210442</v>
+      </c>
+      <c r="PS2" t="n">
+        <v>1016379</v>
+      </c>
+      <c r="PT2" t="n">
+        <v>565629</v>
+      </c>
+      <c r="PU2" t="n">
+        <v>138177</v>
+      </c>
+      <c r="PV2" t="n">
+        <v>978314</v>
+      </c>
+      <c r="PW2" t="n">
+        <v>956557</v>
+      </c>
+      <c r="PX2" t="n">
+        <v>197798</v>
+      </c>
+      <c r="PY2" t="n">
+        <v>350478</v>
+      </c>
+      <c r="PZ2" t="n">
+        <v>462679</v>
+      </c>
+      <c r="QA2" t="n">
+        <v>294604</v>
+      </c>
+      <c r="QB2" t="n">
+        <v>967133</v>
+      </c>
+      <c r="QC2" t="n">
+        <v>464358</v>
+      </c>
+      <c r="QD2" t="n">
+        <v>374485</v>
+      </c>
+      <c r="QE2" t="n">
+        <v>1093868</v>
+      </c>
+      <c r="QF2" t="n">
+        <v>487807</v>
+      </c>
+      <c r="QG2" t="n">
+        <v>875530</v>
+      </c>
+      <c r="QH2" t="n">
+        <v>613434</v>
+      </c>
+      <c r="QI2" t="n">
+        <v>340626</v>
+      </c>
+      <c r="QJ2" t="n">
+        <v>1048008</v>
+      </c>
+      <c r="QK2" t="n">
+        <v>143056</v>
+      </c>
+      <c r="QL2" t="n">
+        <v>652723</v>
+      </c>
+      <c r="QM2" t="n">
+        <v>764706</v>
+      </c>
+      <c r="QN2" t="n">
+        <v>76421</v>
+      </c>
+      <c r="QO2" t="n">
+        <v>54308</v>
+      </c>
+      <c r="QP2" t="n">
+        <v>418726</v>
+      </c>
+      <c r="QQ2" t="n">
+        <v>824217</v>
+      </c>
+      <c r="QR2" t="n">
+        <v>111566</v>
+      </c>
+      <c r="QS2" t="n">
+        <v>841070</v>
+      </c>
+      <c r="QT2" t="n">
+        <v>898798</v>
+      </c>
+      <c r="QU2" t="n">
+        <v>148112</v>
+      </c>
+      <c r="QV2" t="n">
+        <v>49578</v>
+      </c>
+      <c r="QW2" t="n">
+        <v>42183</v>
+      </c>
+      <c r="QX2" t="n">
+        <v>964658</v>
+      </c>
+      <c r="QY2" t="n">
+        <v>85085</v>
+      </c>
+      <c r="QZ2" t="n">
+        <v>646291</v>
+      </c>
+      <c r="RA2" t="n">
+        <v>272123</v>
+      </c>
+      <c r="RB2" t="n">
+        <v>1078690</v>
+      </c>
+      <c r="RC2" t="n">
+        <v>347305</v>
+      </c>
+      <c r="RD2" t="n">
+        <v>1020388</v>
+      </c>
+      <c r="RE2" t="n">
+        <v>229010</v>
+      </c>
+      <c r="RF2" t="n">
+        <v>357928</v>
+      </c>
+      <c r="RG2" t="n">
+        <v>472619</v>
+      </c>
+      <c r="RH2" t="n">
+        <v>602815</v>
+      </c>
+      <c r="RI2" t="n">
+        <v>645561</v>
+      </c>
+      <c r="RJ2" t="n">
+        <v>312689</v>
+      </c>
+      <c r="RK2" t="n">
+        <v>887910</v>
+      </c>
+      <c r="RL2" t="n">
+        <v>996889</v>
+      </c>
+      <c r="RM2" t="n">
+        <v>995367</v>
+      </c>
+      <c r="RN2" t="n">
+        <v>814943</v>
+      </c>
+      <c r="RO2" t="n">
+        <v>290884</v>
+      </c>
+      <c r="RP2" t="n">
+        <v>94782</v>
+      </c>
+      <c r="RQ2" t="n">
+        <v>220911</v>
+      </c>
+      <c r="RR2" t="n">
+        <v>1076101</v>
+      </c>
+      <c r="RS2" t="n">
+        <v>1147569</v>
+      </c>
+      <c r="RT2" t="n">
+        <v>999922</v>
+      </c>
+      <c r="RU2" t="n">
+        <v>391551</v>
+      </c>
+      <c r="RV2" t="n">
+        <v>662793</v>
+      </c>
+      <c r="RW2" t="n">
+        <v>801858</v>
+      </c>
+      <c r="RX2" t="n">
+        <v>436068</v>
+      </c>
+      <c r="RY2" t="n">
+        <v>1070572</v>
+      </c>
+      <c r="RZ2" t="n">
+        <v>1178148</v>
+      </c>
+      <c r="SA2" t="n">
+        <v>687417</v>
+      </c>
+      <c r="SB2" t="n">
+        <v>64293</v>
+      </c>
+      <c r="SC2" t="n">
+        <v>1025759</v>
+      </c>
+      <c r="SD2" t="n">
+        <v>421488</v>
+      </c>
+      <c r="SE2" t="n">
+        <v>31308</v>
+      </c>
+      <c r="SF2" t="n">
+        <v>191845</v>
+      </c>
+      <c r="SG2" t="n">
+        <v>885653</v>
+      </c>
+      <c r="SH2" t="n">
+        <v>398748</v>
+      </c>
+      <c r="SI2" t="n">
+        <v>128301</v>
+      </c>
+      <c r="SJ2" t="n">
+        <v>868526</v>
+      </c>
+      <c r="SK2" t="n">
+        <v>948018</v>
+      </c>
+      <c r="SL2" t="n">
+        <v>1194176</v>
+      </c>
+      <c r="SM2" t="n">
+        <v>1196321</v>
+      </c>
+      <c r="SN2" t="n">
+        <v>913537</v>
+      </c>
+      <c r="SO2" t="n">
+        <v>474437</v>
+      </c>
+      <c r="SP2" t="n">
+        <v>79595</v>
+      </c>
+      <c r="SQ2" t="n">
+        <v>1100439</v>
+      </c>
+      <c r="SR2" t="n">
+        <v>322670</v>
+      </c>
+      <c r="SS2" t="n">
+        <v>172000</v>
+      </c>
+      <c r="ST2" t="n">
+        <v>701434</v>
+      </c>
+      <c r="SU2" t="n">
+        <v>258362</v>
+      </c>
+      <c r="SV2" t="n">
+        <v>262434</v>
+      </c>
+      <c r="SW2" t="n">
+        <v>175497</v>
+      </c>
+      <c r="SX2" t="n">
+        <v>595396</v>
+      </c>
+      <c r="SY2" t="n">
+        <v>484167</v>
+      </c>
+      <c r="SZ2" t="n">
+        <v>351777</v>
+      </c>
+      <c r="TA2" t="n">
+        <v>89031</v>
+      </c>
+      <c r="TB2" t="n">
+        <v>865454</v>
+      </c>
+      <c r="TC2" t="n">
+        <v>249500</v>
+      </c>
+      <c r="TD2" t="n">
+        <v>177246</v>
+      </c>
+      <c r="TE2" t="n">
+        <v>782752</v>
+      </c>
+      <c r="TF2" t="n">
+        <v>913436</v>
+      </c>
+      <c r="TG2" t="n">
+        <v>255233</v>
+      </c>
+      <c r="TH2" t="n">
+        <v>781387</v>
+      </c>
+      <c r="TI2" t="n">
+        <v>1087824</v>
+      </c>
+      <c r="TJ2" t="n">
+        <v>152680</v>
+      </c>
+      <c r="TK2" t="n">
+        <v>832463</v>
+      </c>
+      <c r="TL2" t="n">
+        <v>253771</v>
+      </c>
+      <c r="TM2" t="n">
+        <v>170668</v>
+      </c>
+      <c r="TN2" t="n">
+        <v>413496</v>
+      </c>
+      <c r="TO2" t="n">
+        <v>924532</v>
+      </c>
+      <c r="TP2" t="n">
+        <v>845436</v>
+      </c>
+      <c r="TQ2" t="n">
+        <v>924724</v>
+      </c>
+      <c r="TR2" t="n">
+        <v>3215</v>
+      </c>
+      <c r="TS2" t="n">
+        <v>335118</v>
+      </c>
+      <c r="TT2" t="n">
+        <v>64373</v>
+      </c>
+      <c r="TU2" t="n">
+        <v>439199</v>
+      </c>
+      <c r="TV2" t="n">
+        <v>725599</v>
+      </c>
+      <c r="TW2" t="n">
+        <v>1134903</v>
+      </c>
+      <c r="TX2" t="n">
+        <v>484951</v>
+      </c>
+      <c r="TY2" t="n">
+        <v>473612</v>
+      </c>
+      <c r="TZ2" t="n">
+        <v>337625</v>
+      </c>
+      <c r="UA2" t="n">
+        <v>946728</v>
+      </c>
+      <c r="UB2" t="n">
+        <v>808542</v>
+      </c>
+      <c r="UC2" t="n">
+        <v>409481</v>
+      </c>
+      <c r="UD2" t="n">
+        <v>25969</v>
+      </c>
+      <c r="UE2" t="n">
+        <v>105968</v>
+      </c>
+      <c r="UF2" t="n">
+        <v>370705</v>
+      </c>
+      <c r="UG2" t="n">
+        <v>883915</v>
+      </c>
+      <c r="UH2" t="n">
+        <v>423276</v>
+      </c>
+      <c r="UI2" t="n">
+        <v>1085887</v>
+      </c>
+      <c r="UJ2" t="n">
+        <v>57805</v>
+      </c>
+      <c r="UK2" t="n">
+        <v>40777</v>
+      </c>
+      <c r="UL2" t="n">
+        <v>375222</v>
+      </c>
+      <c r="UM2" t="n">
+        <v>847226</v>
+      </c>
+      <c r="UN2" t="n">
+        <v>54174</v>
+      </c>
+      <c r="UO2" t="n">
+        <v>474227</v>
+      </c>
+      <c r="UP2" t="n">
+        <v>1016322</v>
+      </c>
+      <c r="UQ2" t="n">
+        <v>843731</v>
+      </c>
+      <c r="UR2" t="n">
+        <v>688262</v>
+      </c>
+      <c r="US2" t="n">
+        <v>501261</v>
+      </c>
+      <c r="UT2" t="n">
+        <v>426639</v>
+      </c>
+      <c r="UU2" t="n">
+        <v>206809</v>
+      </c>
+      <c r="UV2" t="n">
+        <v>1107446</v>
+      </c>
+      <c r="UW2" t="n">
+        <v>447578</v>
+      </c>
+      <c r="UX2" t="n">
+        <v>556390</v>
+      </c>
+      <c r="UY2" t="n">
+        <v>512952</v>
+      </c>
+      <c r="UZ2" t="n">
+        <v>412734</v>
+      </c>
+      <c r="VA2" t="n">
+        <v>594612</v>
+      </c>
+      <c r="VB2" t="n">
+        <v>1045593</v>
+      </c>
+      <c r="VC2" t="n">
+        <v>539053</v>
+      </c>
+      <c r="VD2" t="n">
+        <v>849876</v>
+      </c>
+      <c r="VE2" t="n">
+        <v>1049603</v>
+      </c>
+      <c r="VF2" t="n">
+        <v>249082</v>
+      </c>
+      <c r="VG2" t="n">
+        <v>301637</v>
+      </c>
+      <c r="VH2" t="n">
+        <v>690060</v>
+      </c>
+      <c r="VI2" t="n">
+        <v>606768</v>
+      </c>
+      <c r="VJ2" t="n">
+        <v>1031321</v>
+      </c>
+      <c r="VK2" t="n">
+        <v>281729</v>
+      </c>
+      <c r="VL2" t="n">
+        <v>712829</v>
+      </c>
+      <c r="VM2" t="n">
+        <v>971477</v>
+      </c>
+      <c r="VN2" t="n">
+        <v>191132</v>
+      </c>
+      <c r="VO2" t="n">
+        <v>510486</v>
+      </c>
+      <c r="VP2" t="n">
+        <v>200499</v>
+      </c>
+      <c r="VQ2" t="n">
+        <v>444644</v>
+      </c>
+      <c r="VR2" t="n">
+        <v>1163012</v>
+      </c>
+      <c r="VS2" t="n">
+        <v>98958</v>
+      </c>
+      <c r="VT2" t="n">
+        <v>235275</v>
+      </c>
+      <c r="VU2" t="n">
+        <v>118909</v>
+      </c>
+      <c r="VV2" t="n">
+        <v>1163001</v>
+      </c>
+      <c r="VW2" t="n">
+        <v>953485</v>
+      </c>
+      <c r="VX2" t="n">
+        <v>940923</v>
+      </c>
+      <c r="VY2" t="n">
+        <v>417124</v>
+      </c>
+      <c r="VZ2" t="n">
+        <v>1010652</v>
+      </c>
+      <c r="WA2" t="n">
+        <v>700765</v>
+      </c>
+      <c r="WB2" t="n">
+        <v>316297</v>
+      </c>
+      <c r="WC2" t="n">
+        <v>548135</v>
+      </c>
+      <c r="WD2" t="n">
+        <v>622056</v>
+      </c>
+      <c r="WE2" t="n">
+        <v>1235871</v>
+      </c>
+      <c r="WF2" t="n">
+        <v>729399</v>
+      </c>
+      <c r="WG2" t="n">
+        <v>38107</v>
+      </c>
+      <c r="WH2" t="n">
+        <v>493122</v>
+      </c>
+      <c r="WI2" t="n">
+        <v>268013</v>
+      </c>
+      <c r="WJ2" t="n">
+        <v>37767</v>
+      </c>
+      <c r="WK2" t="n">
+        <v>523985</v>
+      </c>
+      <c r="WL2" t="n">
+        <v>11594</v>
+      </c>
+      <c r="WM2" t="n">
+        <v>140860</v>
+      </c>
+      <c r="WN2" t="n">
+        <v>568119</v>
+      </c>
+      <c r="WO2" t="n">
+        <v>1126169</v>
+      </c>
+      <c r="WP2" t="n">
+        <v>1206</v>
+      </c>
+      <c r="WQ2" t="n">
+        <v>853792</v>
+      </c>
+      <c r="WR2" t="n">
+        <v>656036</v>
+      </c>
+      <c r="WS2" t="n">
+        <v>962095</v>
+      </c>
+      <c r="WT2" t="n">
+        <v>6698</v>
+      </c>
+      <c r="WU2" t="n">
+        <v>714791</v>
+      </c>
+      <c r="WV2" t="n">
+        <v>3755</v>
+      </c>
+      <c r="WW2" t="n">
+        <v>1083386</v>
+      </c>
+      <c r="WX2" t="n">
+        <v>1091172</v>
+      </c>
+      <c r="WY2" t="n">
+        <v>885379</v>
+      </c>
+      <c r="WZ2" t="n">
+        <v>718966</v>
+      </c>
+      <c r="XA2" t="n">
+        <v>170870</v>
+      </c>
+      <c r="XB2" t="n">
+        <v>148436</v>
+      </c>
+      <c r="XC2" t="n">
+        <v>807275</v>
+      </c>
+      <c r="XD2" t="n">
+        <v>812881</v>
+      </c>
+      <c r="XE2" t="n">
+        <v>247969</v>
+      </c>
+      <c r="XF2" t="n">
+        <v>1149337</v>
+      </c>
+      <c r="XG2" t="n">
+        <v>1238092</v>
+      </c>
+      <c r="XH2" t="n">
+        <v>499776</v>
+      </c>
+      <c r="XI2" t="n">
+        <v>307013</v>
+      </c>
+      <c r="XJ2" t="n">
+        <v>564195</v>
+      </c>
+      <c r="XK2" t="n">
+        <v>790290</v>
+      </c>
+      <c r="XL2" t="n">
+        <v>99726</v>
+      </c>
+      <c r="XM2" t="n">
+        <v>1233338</v>
+      </c>
+      <c r="XN2" t="n">
+        <v>587415</v>
+      </c>
+      <c r="XO2" t="n">
+        <v>870674</v>
+      </c>
+      <c r="XP2" t="n">
+        <v>116166</v>
+      </c>
+      <c r="XQ2" t="n">
+        <v>674651</v>
+      </c>
+      <c r="XR2" t="n">
+        <v>356399</v>
+      </c>
+      <c r="XS2" t="n">
+        <v>933647</v>
+      </c>
+      <c r="XT2" t="n">
+        <v>1027438</v>
+      </c>
+      <c r="XU2" t="n">
+        <v>62059</v>
+      </c>
+      <c r="XV2" t="n">
+        <v>303333</v>
+      </c>
+      <c r="XW2" t="n">
+        <v>656815</v>
+      </c>
+      <c r="XX2" t="n">
+        <v>503124</v>
+      </c>
+      <c r="XY2" t="n">
+        <v>733816</v>
+      </c>
+      <c r="XZ2" t="n">
+        <v>77729</v>
+      </c>
+      <c r="YA2" t="n">
+        <v>47564</v>
+      </c>
+      <c r="YB2" t="n">
+        <v>412205</v>
+      </c>
+      <c r="YC2" t="n">
+        <v>691721</v>
+      </c>
+      <c r="YD2" t="n">
+        <v>402889</v>
+      </c>
+      <c r="YE2" t="n">
+        <v>7422</v>
+      </c>
+      <c r="YF2" t="n">
+        <v>944345</v>
+      </c>
+      <c r="YG2" t="n">
+        <v>621812</v>
+      </c>
+      <c r="YH2" t="n">
+        <v>637276</v>
+      </c>
+      <c r="YI2" t="n">
+        <v>259117</v>
+      </c>
+      <c r="YJ2" t="n">
+        <v>172968</v>
+      </c>
+      <c r="YK2" t="n">
+        <v>467166</v>
+      </c>
+      <c r="YL2" t="n">
+        <v>1198203</v>
+      </c>
+      <c r="YM2" t="n">
+        <v>1132226</v>
+      </c>
+      <c r="YN2" t="n">
+        <v>1038579</v>
+      </c>
+      <c r="YO2" t="n">
+        <v>132176</v>
+      </c>
+      <c r="YP2" t="n">
+        <v>287949</v>
+      </c>
+      <c r="YQ2" t="n">
+        <v>19282</v>
+      </c>
+      <c r="YR2" t="n">
+        <v>70343</v>
+      </c>
+      <c r="YS2" t="n">
+        <v>1134444</v>
+      </c>
+      <c r="YT2" t="n">
+        <v>1206494</v>
+      </c>
+      <c r="YU2" t="n">
+        <v>495995</v>
+      </c>
+      <c r="YV2" t="n">
+        <v>597267</v>
+      </c>
+      <c r="YW2" t="n">
+        <v>518929</v>
+      </c>
+      <c r="YX2" t="n">
+        <v>437625</v>
+      </c>
+      <c r="YY2" t="n">
+        <v>765137</v>
+      </c>
+      <c r="YZ2" t="n">
+        <v>672123</v>
+      </c>
+      <c r="ZA2" t="n">
+        <v>1225622</v>
+      </c>
+      <c r="ZB2" t="n">
+        <v>493680</v>
+      </c>
+      <c r="ZC2" t="n">
+        <v>419372</v>
+      </c>
+      <c r="ZD2" t="n">
+        <v>657497</v>
+      </c>
+      <c r="ZE2" t="n">
+        <v>16767</v>
+      </c>
+      <c r="ZF2" t="n">
+        <v>583430</v>
+      </c>
+      <c r="ZG2" t="n">
+        <v>578023</v>
+      </c>
+      <c r="ZH2" t="n">
+        <v>1031429</v>
+      </c>
+      <c r="ZI2" t="n">
+        <v>554384</v>
+      </c>
+      <c r="ZJ2" t="n">
+        <v>168804</v>
+      </c>
+      <c r="ZK2" t="n">
+        <v>619151</v>
+      </c>
+      <c r="ZL2" t="n">
+        <v>341014</v>
+      </c>
+      <c r="ZM2" t="n">
+        <v>461948</v>
+      </c>
+      <c r="ZN2" t="n">
+        <v>278771</v>
+      </c>
+      <c r="ZO2" t="n">
+        <v>65781</v>
+      </c>
+      <c r="ZP2" t="n">
+        <v>662975</v>
+      </c>
+      <c r="ZQ2" t="n">
+        <v>109618</v>
+      </c>
+      <c r="ZR2" t="n">
+        <v>115916</v>
+      </c>
+      <c r="ZS2" t="n">
+        <v>966414</v>
+      </c>
+      <c r="ZT2" t="n">
+        <v>1220561</v>
+      </c>
+      <c r="ZU2" t="n">
+        <v>92474</v>
+      </c>
+      <c r="ZV2" t="n">
+        <v>210421</v>
+      </c>
+      <c r="ZW2" t="n">
+        <v>438937</v>
+      </c>
+      <c r="ZX2" t="n">
+        <v>177138</v>
+      </c>
+      <c r="ZY2" t="n">
+        <v>1063551</v>
+      </c>
+      <c r="ZZ2" t="n">
+        <v>154682</v>
+      </c>
+      <c r="AAA2" t="n">
+        <v>1027229</v>
+      </c>
+      <c r="AAB2" t="n">
+        <v>771354</v>
+      </c>
+      <c r="AAC2" t="n">
+        <v>629952</v>
+      </c>
+      <c r="AAD2" t="n">
+        <v>52227</v>
+      </c>
+      <c r="AAE2" t="n">
+        <v>30330</v>
+      </c>
+      <c r="AAF2" t="n">
+        <v>1057741</v>
+      </c>
+      <c r="AAG2" t="n">
+        <v>988332</v>
+      </c>
+      <c r="AAH2" t="n">
+        <v>740294</v>
+      </c>
+      <c r="AAI2" t="n">
+        <v>752694</v>
+      </c>
+      <c r="AAJ2" t="n">
+        <v>1024581</v>
+      </c>
+      <c r="AAK2" t="n">
+        <v>802394</v>
+      </c>
+      <c r="AAL2" t="n">
+        <v>883635</v>
+      </c>
+      <c r="AAM2" t="n">
+        <v>51642</v>
+      </c>
+      <c r="AAN2" t="n">
+        <v>541805</v>
+      </c>
+      <c r="AAO2" t="n">
+        <v>679326</v>
+      </c>
+      <c r="AAP2" t="n">
+        <v>381313</v>
+      </c>
+      <c r="AAQ2" t="n">
+        <v>1056076</v>
+      </c>
+      <c r="AAR2" t="n">
+        <v>558377</v>
+      </c>
+      <c r="AAS2" t="n">
+        <v>134104</v>
+      </c>
+      <c r="AAT2" t="n">
+        <v>739026</v>
+      </c>
+      <c r="AAU2" t="n">
+        <v>818699</v>
+      </c>
+      <c r="AAV2" t="n">
+        <v>90366</v>
+      </c>
+      <c r="AAW2" t="n">
+        <v>342467</v>
+      </c>
+      <c r="AAX2" t="n">
+        <v>229737</v>
+      </c>
+      <c r="AAY2" t="n">
+        <v>428895</v>
+      </c>
+      <c r="AAZ2" t="n">
+        <v>405441</v>
+      </c>
+      <c r="ABA2" t="n">
+        <v>247880</v>
+      </c>
+      <c r="ABB2" t="n">
+        <v>395861</v>
+      </c>
+      <c r="ABC2" t="n">
+        <v>505222</v>
+      </c>
+      <c r="ABD2" t="n">
+        <v>440942</v>
+      </c>
+      <c r="ABE2" t="n">
+        <v>95647</v>
+      </c>
+      <c r="ABF2" t="n">
+        <v>535613</v>
+      </c>
+      <c r="ABG2" t="n">
+        <v>612560</v>
+      </c>
+      <c r="ABH2" t="n">
+        <v>441560</v>
+      </c>
+      <c r="ABI2" t="n">
+        <v>19055</v>
+      </c>
+      <c r="ABJ2" t="n">
+        <v>314511</v>
+      </c>
+      <c r="ABK2" t="n">
+        <v>627404</v>
+      </c>
+      <c r="ABL2" t="n">
+        <v>591104</v>
+      </c>
+      <c r="ABM2" t="n">
+        <v>708296</v>
+      </c>
+      <c r="ABN2" t="n">
+        <v>159997</v>
+      </c>
+      <c r="ABO2" t="n">
+        <v>73377</v>
+      </c>
+      <c r="ABP2" t="n">
+        <v>968522</v>
+      </c>
+      <c r="ABQ2" t="n">
+        <v>80604</v>
+      </c>
+      <c r="ABR2" t="n">
+        <v>614289</v>
+      </c>
+      <c r="ABS2" t="n">
+        <v>225126</v>
+      </c>
+      <c r="ABT2" t="n">
+        <v>647156</v>
+      </c>
+      <c r="ABU2" t="n">
+        <v>1062525</v>
+      </c>
+      <c r="ABV2" t="n">
+        <v>410283</v>
+      </c>
+      <c r="ABW2" t="n">
+        <v>991965</v>
+      </c>
+      <c r="ABX2" t="n">
+        <v>145553</v>
+      </c>
+      <c r="ABY2" t="n">
+        <v>619211</v>
+      </c>
+      <c r="ABZ2" t="n">
+        <v>586025</v>
+      </c>
+      <c r="ACA2" t="n">
+        <v>809575</v>
+      </c>
+      <c r="ACB2" t="n">
+        <v>21083</v>
+      </c>
+      <c r="ACC2" t="n">
+        <v>995178</v>
+      </c>
+      <c r="ACD2" t="n">
+        <v>349975</v>
+      </c>
+      <c r="ACE2" t="n">
+        <v>469040</v>
+      </c>
+      <c r="ACF2" t="n">
+        <v>1175422</v>
+      </c>
+      <c r="ACG2" t="n">
+        <v>849624</v>
+      </c>
+      <c r="ACH2" t="n">
+        <v>361717</v>
+      </c>
+      <c r="ACI2" t="n">
+        <v>421708</v>
+      </c>
+      <c r="ACJ2" t="n">
+        <v>796232</v>
+      </c>
+      <c r="ACK2" t="n">
+        <v>771922</v>
+      </c>
+      <c r="ACL2" t="n">
+        <v>1202926</v>
+      </c>
+      <c r="ACM2" t="n">
+        <v>635261</v>
+      </c>
+      <c r="ACN2" t="n">
+        <v>291032</v>
+      </c>
+      <c r="ACO2" t="n">
+        <v>952339</v>
+      </c>
+      <c r="ACP2" t="n">
+        <v>92769</v>
+      </c>
+      <c r="ACQ2" t="n">
+        <v>191445</v>
+      </c>
+      <c r="ACR2" t="n">
+        <v>458541</v>
+      </c>
+      <c r="ACS2" t="n">
+        <v>163798</v>
+      </c>
+      <c r="ACT2" t="n">
+        <v>1193235</v>
+      </c>
+      <c r="ACU2" t="n">
+        <v>825367</v>
+      </c>
+      <c r="ACV2" t="n">
+        <v>981583</v>
+      </c>
+      <c r="ACW2" t="n">
+        <v>239618</v>
+      </c>
+      <c r="ACX2" t="n">
+        <v>385026</v>
+      </c>
+      <c r="ACY2" t="n">
+        <v>877954</v>
+      </c>
+      <c r="ACZ2" t="n">
+        <v>984863</v>
+      </c>
+      <c r="ADA2" t="n">
+        <v>82050</v>
+      </c>
+      <c r="ADB2" t="n">
+        <v>467213</v>
+      </c>
+      <c r="ADC2" t="n">
+        <v>562977</v>
+      </c>
+      <c r="ADD2" t="n">
+        <v>1143416</v>
+      </c>
+      <c r="ADE2" t="n">
+        <v>267212</v>
+      </c>
+      <c r="ADF2" t="n">
+        <v>750110</v>
+      </c>
+      <c r="ADG2" t="n">
+        <v>305340</v>
+      </c>
+      <c r="ADH2" t="n">
+        <v>41640</v>
+      </c>
+      <c r="ADI2" t="n">
+        <v>70531</v>
+      </c>
+      <c r="ADJ2" t="n">
+        <v>784883</v>
+      </c>
+      <c r="ADK2" t="n">
+        <v>87424</v>
+      </c>
+      <c r="ADL2" t="n">
+        <v>359350</v>
+      </c>
+      <c r="ADM2" t="n">
+        <v>915032</v>
+      </c>
+      <c r="ADN2" t="n">
+        <v>181292</v>
+      </c>
+      <c r="ADO2" t="n">
+        <v>756417</v>
+      </c>
+      <c r="ADP2" t="n">
+        <v>835560</v>
+      </c>
+      <c r="ADQ2" t="n">
+        <v>163407</v>
+      </c>
+      <c r="ADR2" t="n">
+        <v>1157488</v>
+      </c>
+      <c r="ADS2" t="n">
+        <v>223200</v>
+      </c>
+      <c r="ADT2" t="n">
+        <v>400324</v>
+      </c>
+      <c r="ADU2" t="n">
+        <v>891655</v>
+      </c>
+      <c r="ADV2" t="n">
+        <v>446506</v>
+      </c>
+      <c r="ADW2" t="n">
+        <v>299292</v>
+      </c>
+      <c r="ADX2" t="n">
+        <v>769627</v>
+      </c>
+      <c r="ADY2" t="n">
+        <v>353618</v>
+      </c>
+      <c r="ADZ2" t="n">
+        <v>702979</v>
+      </c>
+      <c r="AEA2" t="n">
+        <v>1208191</v>
+      </c>
+      <c r="AEB2" t="n">
+        <v>284819</v>
+      </c>
+      <c r="AEC2" t="n">
+        <v>579329</v>
+      </c>
+      <c r="AED2" t="n">
+        <v>276400</v>
+      </c>
+      <c r="AEE2" t="n">
+        <v>307666</v>
+      </c>
+      <c r="AEF2" t="n">
+        <v>633173</v>
+      </c>
+      <c r="AEG2" t="n">
+        <v>982275</v>
+      </c>
+      <c r="AEH2" t="n">
+        <v>218358</v>
+      </c>
+      <c r="AEI2" t="n">
+        <v>461153</v>
+      </c>
+      <c r="AEJ2" t="n">
+        <v>224485</v>
+      </c>
+      <c r="AEK2" t="n">
+        <v>222602</v>
+      </c>
+      <c r="AEL2" t="n">
+        <v>790541</v>
+      </c>
+      <c r="AEM2" t="n">
+        <v>204649</v>
+      </c>
+      <c r="AEN2" t="n">
+        <v>902394</v>
+      </c>
+      <c r="AEO2" t="n">
+        <v>721011</v>
+      </c>
+      <c r="AEP2" t="n">
+        <v>86063</v>
+      </c>
+      <c r="AEQ2" t="n">
+        <v>228215</v>
+      </c>
+      <c r="AER2" t="n">
+        <v>746907</v>
+      </c>
+      <c r="AES2" t="n">
+        <v>288995</v>
+      </c>
+      <c r="AET2" t="n">
+        <v>344394</v>
+      </c>
+      <c r="AEU2" t="n">
+        <v>706139</v>
+      </c>
+      <c r="AEV2" t="n">
+        <v>376246</v>
+      </c>
+      <c r="AEW2" t="n">
+        <v>797387</v>
+      </c>
+      <c r="AEX2" t="n">
+        <v>1099450</v>
+      </c>
+      <c r="AEY2" t="n">
+        <v>582372</v>
+      </c>
+      <c r="AEZ2" t="n">
+        <v>841747</v>
+      </c>
+      <c r="AFA2" t="n">
+        <v>275188</v>
+      </c>
+      <c r="AFB2" t="n">
+        <v>1151204</v>
+      </c>
+      <c r="AFC2" t="n">
+        <v>860403</v>
+      </c>
+      <c r="AFD2" t="n">
+        <v>180691</v>
+      </c>
+      <c r="AFE2" t="n">
+        <v>865602</v>
+      </c>
+      <c r="AFF2" t="n">
+        <v>1074525</v>
+      </c>
+      <c r="AFG2" t="n">
+        <v>123385</v>
+      </c>
+      <c r="AFH2" t="n">
+        <v>634859</v>
+      </c>
+      <c r="AFI2" t="n">
+        <v>277343</v>
+      </c>
+      <c r="AFJ2" t="n">
+        <v>905020</v>
+      </c>
+      <c r="AFK2" t="n">
+        <v>259549</v>
+      </c>
+      <c r="AFL2" t="n">
+        <v>1219631</v>
+      </c>
+      <c r="AFM2" t="n">
+        <v>872218</v>
+      </c>
+      <c r="AFN2" t="n">
+        <v>834084</v>
+      </c>
+      <c r="AFO2" t="n">
+        <v>559414</v>
+      </c>
+      <c r="AFP2" t="n">
+        <v>427343</v>
+      </c>
+      <c r="AFQ2" t="n">
+        <v>120288</v>
+      </c>
+      <c r="AFR2" t="n">
+        <v>843866</v>
+      </c>
+      <c r="AFS2" t="n">
+        <v>138355</v>
+      </c>
+      <c r="AFT2" t="n">
+        <v>421335</v>
+      </c>
+      <c r="AFU2" t="n">
+        <v>435721</v>
+      </c>
+      <c r="AFV2" t="n">
+        <v>1079906</v>
+      </c>
+      <c r="AFW2" t="n">
+        <v>909593</v>
+      </c>
+      <c r="AFX2" t="n">
+        <v>777115</v>
+      </c>
+      <c r="AFY2" t="n">
+        <v>640414</v>
+      </c>
+      <c r="AFZ2" t="n">
+        <v>107047</v>
+      </c>
+      <c r="AGA2" t="n">
+        <v>145499</v>
+      </c>
+      <c r="AGB2" t="n">
+        <v>927360</v>
+      </c>
+      <c r="AGC2" t="n">
+        <v>127459</v>
+      </c>
+      <c r="AGD2" t="n">
+        <v>545000</v>
+      </c>
+      <c r="AGE2" t="n">
+        <v>762495</v>
+      </c>
+      <c r="AGF2" t="n">
+        <v>640709</v>
+      </c>
+      <c r="AGG2" t="n">
+        <v>769598</v>
+      </c>
+      <c r="AGH2" t="n">
+        <v>146816</v>
+      </c>
+      <c r="AGI2" t="n">
+        <v>156086</v>
+      </c>
+      <c r="AGJ2" t="n">
+        <v>489406</v>
+      </c>
+      <c r="AGK2" t="n">
+        <v>124651</v>
+      </c>
+      <c r="AGL2" t="n">
+        <v>283451</v>
+      </c>
+      <c r="AGM2" t="n">
+        <v>445554</v>
+      </c>
+      <c r="AGN2" t="n">
+        <v>1083753</v>
+      </c>
+      <c r="AGO2" t="n">
+        <v>435063</v>
+      </c>
+      <c r="AGP2" t="n">
+        <v>644399</v>
+      </c>
+      <c r="AGQ2" t="n">
+        <v>603906</v>
+      </c>
+      <c r="AGR2" t="n">
+        <v>1061964</v>
+      </c>
+      <c r="AGS2" t="n">
+        <v>202736</v>
+      </c>
+      <c r="AGT2" t="n">
+        <v>112750</v>
+      </c>
+      <c r="AGU2" t="n">
+        <v>161614</v>
+      </c>
+      <c r="AGV2" t="n">
+        <v>720070</v>
+      </c>
+      <c r="AGW2" t="n">
+        <v>746221</v>
+      </c>
+      <c r="AGX2" t="n">
+        <v>1023512</v>
+      </c>
+      <c r="AGY2" t="n">
+        <v>989350</v>
+      </c>
+      <c r="AGZ2" t="n">
+        <v>158434</v>
+      </c>
+      <c r="AHA2" t="n">
+        <v>245440</v>
+      </c>
+      <c r="AHB2" t="n">
+        <v>61776</v>
+      </c>
+      <c r="AHC2" t="n">
+        <v>230816</v>
+      </c>
+      <c r="AHD2" t="n">
+        <v>186759</v>
+      </c>
+      <c r="AHE2" t="n">
+        <v>166587</v>
+      </c>
+      <c r="AHF2" t="n">
+        <v>938462</v>
+      </c>
+      <c r="AHG2" t="n">
+        <v>195648</v>
+      </c>
+      <c r="AHH2" t="n">
+        <v>1000828</v>
+      </c>
+      <c r="AHI2" t="n">
+        <v>1138811</v>
+      </c>
+      <c r="AHJ2" t="n">
+        <v>486102</v>
+      </c>
+      <c r="AHK2" t="n">
+        <v>1190831</v>
+      </c>
+      <c r="AHL2" t="n">
+        <v>118349</v>
+      </c>
+      <c r="AHM2" t="n">
+        <v>481401</v>
+      </c>
+      <c r="AHN2" t="n">
+        <v>475924</v>
+      </c>
+      <c r="AHO2" t="n">
+        <v>257238</v>
+      </c>
+      <c r="AHP2" t="n">
+        <v>950995</v>
+      </c>
+      <c r="AHQ2" t="n">
+        <v>911523</v>
+      </c>
+      <c r="AHR2" t="n">
+        <v>44306</v>
+      </c>
+      <c r="AHS2" t="n">
+        <v>641856</v>
+      </c>
+      <c r="AHT2" t="n">
+        <v>22799</v>
+      </c>
+      <c r="AHU2" t="n">
+        <v>337674</v>
+      </c>
+      <c r="AHV2" t="n">
+        <v>207407</v>
+      </c>
+      <c r="AHW2" t="n">
+        <v>792252</v>
+      </c>
+      <c r="AHX2" t="n">
+        <v>7468</v>
+      </c>
+      <c r="AHY2" t="n">
+        <v>68055</v>
+      </c>
+      <c r="AHZ2" t="n">
+        <v>456091</v>
+      </c>
+      <c r="AIA2" t="n">
+        <v>1005773</v>
+      </c>
+      <c r="AIB2" t="n">
+        <v>404953</v>
+      </c>
+      <c r="AIC2" t="n">
+        <v>1195875</v>
+      </c>
+      <c r="AID2" t="n">
+        <v>919269</v>
+      </c>
+      <c r="AIE2" t="n">
+        <v>752516</v>
+      </c>
+      <c r="AIF2" t="n">
+        <v>390434</v>
+      </c>
+      <c r="AIG2" t="n">
+        <v>160114</v>
+      </c>
+      <c r="AIH2" t="n">
+        <v>931107</v>
+      </c>
+      <c r="AII2" t="n">
+        <v>364689</v>
+      </c>
+      <c r="AIJ2" t="n">
+        <v>517151</v>
+      </c>
+      <c r="AIK2" t="n">
+        <v>337067</v>
+      </c>
+      <c r="AIL2" t="n">
+        <v>106945</v>
+      </c>
+      <c r="AIM2" t="n">
+        <v>1097816</v>
+      </c>
+      <c r="AIN2" t="n">
+        <v>1158891</v>
+      </c>
+      <c r="AIO2" t="n">
+        <v>588996</v>
+      </c>
+      <c r="AIP2" t="n">
+        <v>749301</v>
+      </c>
+      <c r="AIQ2" t="n">
+        <v>728407</v>
+      </c>
+      <c r="AIR2" t="n">
+        <v>1110431</v>
+      </c>
+      <c r="AIS2" t="n">
+        <v>551082</v>
+      </c>
+      <c r="AIT2" t="n">
+        <v>858279</v>
+      </c>
+      <c r="AIU2" t="n">
+        <v>1041532</v>
+      </c>
+      <c r="AIV2" t="n">
+        <v>497855</v>
+      </c>
+      <c r="AIW2" t="n">
+        <v>18199</v>
+      </c>
+      <c r="AIX2" t="n">
+        <v>547788</v>
+      </c>
+      <c r="AIY2" t="n">
+        <v>1188530</v>
+      </c>
+      <c r="AIZ2" t="n">
+        <v>760830</v>
+      </c>
+      <c r="AJA2" t="n">
+        <v>575153</v>
+      </c>
+      <c r="AJB2" t="n">
+        <v>897015</v>
+      </c>
+      <c r="AJC2" t="n">
+        <v>56385</v>
+      </c>
+      <c r="AJD2" t="n">
+        <v>513652</v>
+      </c>
+      <c r="AJE2" t="n">
+        <v>698697</v>
+      </c>
+      <c r="AJF2" t="n">
+        <v>1115410</v>
+      </c>
+      <c r="AJG2" t="n">
+        <v>1204032</v>
+      </c>
+      <c r="AJH2" t="n">
+        <v>855738</v>
+      </c>
+      <c r="AJI2" t="n">
+        <v>389586</v>
+      </c>
+      <c r="AJJ2" t="n">
+        <v>1188023</v>
+      </c>
+      <c r="AJK2" t="n">
+        <v>743732</v>
+      </c>
+      <c r="AJL2" t="n">
+        <v>8247</v>
+      </c>
+      <c r="AJM2" t="n">
+        <v>862483</v>
+      </c>
+      <c r="AJN2" t="n">
+        <v>34950</v>
+      </c>
+      <c r="AJO2" t="n">
+        <v>443212</v>
+      </c>
+      <c r="AJP2" t="n">
+        <v>309355</v>
+      </c>
+      <c r="AJQ2" t="n">
+        <v>1013283</v>
+      </c>
+      <c r="AJR2" t="n">
+        <v>270924</v>
+      </c>
+      <c r="AJS2" t="n">
+        <v>945260</v>
+      </c>
+      <c r="AJT2" t="n">
+        <v>369638</v>
+      </c>
+      <c r="AJU2" t="n">
+        <v>684077</v>
+      </c>
+      <c r="AJV2" t="n">
+        <v>1201990</v>
+      </c>
+      <c r="AJW2" t="n">
+        <v>1189328</v>
+      </c>
+      <c r="AJX2" t="n">
+        <v>723431</v>
+      </c>
+      <c r="AJY2" t="n">
+        <v>393030</v>
+      </c>
+      <c r="AJZ2" t="n">
+        <v>196046</v>
+      </c>
+      <c r="AKA2" t="n">
+        <v>24602</v>
+      </c>
+      <c r="AKB2" t="n">
+        <v>289166</v>
+      </c>
+      <c r="AKC2" t="n">
+        <v>1118720</v>
+      </c>
+      <c r="AKD2" t="n">
+        <v>33218</v>
+      </c>
+      <c r="AKE2" t="n">
+        <v>103251</v>
+      </c>
+      <c r="AKF2" t="n">
+        <v>556814</v>
+      </c>
+      <c r="AKG2" t="n">
+        <v>526485</v>
+      </c>
+      <c r="AKH2" t="n">
+        <v>642919</v>
+      </c>
+      <c r="AKI2" t="n">
+        <v>600968</v>
+      </c>
+      <c r="AKJ2" t="n">
+        <v>683985</v>
+      </c>
+      <c r="AKK2" t="n">
+        <v>926475</v>
+      </c>
+      <c r="AKL2" t="n">
+        <v>1127414</v>
+      </c>
+      <c r="AKM2" t="n">
+        <v>1110319</v>
+      </c>
+      <c r="AKN2" t="n">
+        <v>650076</v>
+      </c>
+      <c r="AKO2" t="n">
+        <v>325953</v>
+      </c>
+      <c r="AKP2" t="n">
+        <v>744675</v>
+      </c>
+      <c r="AKQ2" t="n">
+        <v>1010636</v>
+      </c>
+      <c r="AKR2" t="n">
+        <v>478437</v>
+      </c>
+      <c r="AKS2" t="n">
+        <v>907172</v>
+      </c>
+      <c r="AKT2" t="n">
+        <v>1003958</v>
+      </c>
+      <c r="AKU2" t="n">
         <v>0</v>
       </c>
-      <c r="BY2" t="n">
-        <v>110269</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>48010</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>122752</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>62176</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>65275</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>24971</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>32372</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>90234</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>15166</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>75812</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>12136</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>9256</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>119970</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>115007</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>101168</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>2142</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>5212</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>56071</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>28358</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>86651</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>116638</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>16327</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>102388</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>21675</v>
+      <c r="AKV2" t="n">
+        <v>198740</v>
+      </c>
+      <c r="AKW2" t="n">
+        <v>10942</v>
+      </c>
+      <c r="AKX2" t="n">
+        <v>218010</v>
+      </c>
+      <c r="AKY2" t="n">
+        <v>1137232</v>
+      </c>
+      <c r="AKZ2" t="n">
+        <v>1043739</v>
+      </c>
+      <c r="ALA2" t="n">
+        <v>1143137</v>
+      </c>
+      <c r="ALB2" t="n">
+        <v>788320</v>
+      </c>
+      <c r="ALC2" t="n">
+        <v>665265</v>
+      </c>
+      <c r="ALD2" t="n">
+        <v>333007</v>
+      </c>
+      <c r="ALE2" t="n">
+        <v>937467</v>
+      </c>
+      <c r="ALF2" t="n">
+        <v>699952</v>
+      </c>
+      <c r="ALG2" t="n">
+        <v>213231</v>
+      </c>
+      <c r="ALH2" t="n">
+        <v>626721</v>
+      </c>
+      <c r="ALI2" t="n">
+        <v>529156</v>
+      </c>
+      <c r="ALJ2" t="n">
+        <v>890588</v>
+      </c>
+      <c r="ALK2" t="n">
+        <v>396211</v>
+      </c>
+      <c r="ALL2" t="n">
+        <v>330999</v>
       </c>
     </row>
   </sheetData>
@@ -894,7 +8494,7 @@
         <v>324</v>
       </c>
       <c r="B1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
@@ -936,7 +8536,7 @@
         <v>10384</v>
       </c>
       <c r="B1" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
@@ -990,7 +8590,7 @@
         <v>11692</v>
       </c>
       <c r="B1" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
@@ -1044,7 +8644,7 @@
         <v>19770</v>
       </c>
       <c r="B1" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2">
@@ -1128,7 +8728,7 @@
         <v>20507</v>
       </c>
       <c r="B1" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2">
@@ -1266,7 +8866,7 @@
         <v>114471</v>
       </c>
       <c r="B1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2">
@@ -1317,312 +8917,312 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>6889525</v>
+        <v>6911414</v>
       </c>
       <c r="B1" t="n">
-        <v>120469</v>
+        <v>113953</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>59396</v>
+        <v>58932</v>
       </c>
       <c r="B2" t="n">
-        <v>101737</v>
+        <v>102752</v>
       </c>
       <c r="C2" t="n">
-        <v>48000</v>
+        <v>49389</v>
       </c>
       <c r="D2" t="n">
-        <v>31892</v>
+        <v>31371</v>
       </c>
       <c r="E2" t="n">
-        <v>45510</v>
+        <v>12498</v>
       </c>
       <c r="F2" t="n">
         <v>12217</v>
       </c>
       <c r="G2" t="n">
-        <v>51898</v>
+        <v>53276</v>
       </c>
       <c r="H2" t="n">
-        <v>127748</v>
+        <v>126779</v>
       </c>
       <c r="I2" t="n">
-        <v>133184</v>
+        <v>131684</v>
       </c>
       <c r="J2" t="n">
-        <v>70050</v>
+        <v>28930</v>
       </c>
       <c r="K2" t="n">
-        <v>17104</v>
+        <v>12110</v>
       </c>
       <c r="L2" t="n">
-        <v>112784</v>
+        <v>95378</v>
       </c>
       <c r="M2" t="n">
-        <v>93245</v>
+        <v>91463</v>
       </c>
       <c r="N2" t="n">
         <v>5971</v>
       </c>
       <c r="O2" t="n">
-        <v>72134</v>
+        <v>75114</v>
       </c>
       <c r="P2" t="n">
-        <v>40942</v>
+        <v>43596</v>
       </c>
       <c r="Q2" t="n">
-        <v>100652</v>
+        <v>87833</v>
       </c>
       <c r="R2" t="n">
-        <v>84846</v>
+        <v>85013</v>
       </c>
       <c r="S2" t="n">
-        <v>59210</v>
+        <v>58777</v>
       </c>
       <c r="T2" t="n">
-        <v>16856</v>
+        <v>24869</v>
       </c>
       <c r="U2" t="n">
-        <v>108359</v>
+        <v>113076</v>
       </c>
       <c r="V2" t="n">
-        <v>80635</v>
+        <v>95520</v>
       </c>
       <c r="W2" t="n">
         <v>5207</v>
       </c>
       <c r="X2" t="n">
-        <v>129097</v>
+        <v>103314</v>
       </c>
       <c r="Y2" t="n">
-        <v>119538</v>
+        <v>116653</v>
       </c>
       <c r="Z2" t="n">
-        <v>70081</v>
+        <v>94312</v>
       </c>
       <c r="AA2" t="n">
-        <v>74415</v>
+        <v>73215</v>
       </c>
       <c r="AB2" t="n">
-        <v>80420</v>
+        <v>80587</v>
       </c>
       <c r="AC2" t="n">
-        <v>30959</v>
+        <v>30438</v>
       </c>
       <c r="AD2" t="n">
-        <v>27835</v>
+        <v>33436</v>
       </c>
       <c r="AE2" t="n">
         <v>9492</v>
       </c>
       <c r="AF2" t="n">
-        <v>82637</v>
+        <v>57194</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>57075</v>
+        <v>64925</v>
       </c>
       <c r="AI2" t="n">
-        <v>106103</v>
+        <v>106749</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19805</v>
+        <v>17672</v>
       </c>
       <c r="AK2" t="n">
-        <v>77682</v>
+        <v>77849</v>
       </c>
       <c r="AL2" t="n">
         <v>933</v>
       </c>
       <c r="AM2" t="n">
-        <v>63874</v>
+        <v>62722</v>
       </c>
       <c r="AN2" t="n">
-        <v>55599</v>
+        <v>49982</v>
       </c>
       <c r="AO2" t="n">
-        <v>90663</v>
+        <v>90094</v>
       </c>
       <c r="AP2" t="n">
-        <v>86089</v>
+        <v>51735</v>
       </c>
       <c r="AQ2" t="n">
-        <v>54819</v>
+        <v>56197</v>
       </c>
       <c r="AR2" t="n">
-        <v>41807</v>
+        <v>44461</v>
       </c>
       <c r="AS2" t="n">
-        <v>48504</v>
+        <v>98443</v>
       </c>
       <c r="AT2" t="n">
         <v>6699</v>
       </c>
       <c r="AU2" t="n">
-        <v>90631</v>
+        <v>86338</v>
       </c>
       <c r="AV2" t="n">
-        <v>79823</v>
+        <v>79990</v>
       </c>
       <c r="AW2" t="n">
-        <v>126001</v>
+        <v>125032</v>
       </c>
       <c r="AX2" t="n">
-        <v>70986</v>
+        <v>69786</v>
       </c>
       <c r="AY2" t="n">
-        <v>35498</v>
+        <v>22673</v>
       </c>
       <c r="AZ2" t="n">
-        <v>122138</v>
+        <v>120673</v>
       </c>
       <c r="BA2" t="n">
-        <v>136370</v>
+        <v>137280</v>
       </c>
       <c r="BB2" t="n">
-        <v>95107</v>
+        <v>140002</v>
       </c>
       <c r="BC2" t="n">
-        <v>23258</v>
+        <v>27005</v>
       </c>
       <c r="BD2" t="n">
-        <v>92150</v>
+        <v>105259</v>
       </c>
       <c r="BE2" t="n">
-        <v>49860</v>
+        <v>38780</v>
       </c>
       <c r="BF2" t="n">
-        <v>115950</v>
+        <v>59629</v>
       </c>
       <c r="BG2" t="n">
         <v>21</v>
       </c>
       <c r="BH2" t="n">
-        <v>63382</v>
+        <v>38775</v>
       </c>
       <c r="BI2" t="n">
-        <v>99489</v>
+        <v>108862</v>
       </c>
       <c r="BJ2" t="n">
-        <v>74146</v>
+        <v>131701</v>
       </c>
       <c r="BK2" t="n">
-        <v>112503</v>
+        <v>52770</v>
       </c>
       <c r="BL2" t="n">
         <v>2057</v>
       </c>
       <c r="BM2" t="n">
-        <v>21735</v>
+        <v>110862</v>
       </c>
       <c r="BN2" t="n">
-        <v>97053</v>
+        <v>89199</v>
       </c>
       <c r="BO2" t="n">
-        <v>41859</v>
+        <v>44513</v>
       </c>
       <c r="BP2" t="n">
-        <v>66961</v>
+        <v>119864</v>
       </c>
       <c r="BQ2" t="n">
-        <v>132319</v>
+        <v>127686</v>
       </c>
       <c r="BR2" t="n">
         <v>9787</v>
       </c>
       <c r="BS2" t="n">
-        <v>115237</v>
+        <v>116281</v>
       </c>
       <c r="BT2" t="n">
-        <v>30562</v>
+        <v>20703</v>
       </c>
       <c r="BU2" t="n">
         <v>4476</v>
       </c>
       <c r="BV2" t="n">
-        <v>51574</v>
+        <v>114677</v>
       </c>
       <c r="BW2" t="n">
-        <v>66527</v>
+        <v>67637</v>
       </c>
       <c r="BX2" t="n">
-        <v>13055</v>
+        <v>19810</v>
       </c>
       <c r="BY2" t="n">
-        <v>98602</v>
+        <v>100909</v>
       </c>
       <c r="BZ2" t="n">
-        <v>124444</v>
+        <v>120812</v>
       </c>
       <c r="CA2" t="n">
-        <v>44489</v>
+        <v>47143</v>
       </c>
       <c r="CB2" t="n">
-        <v>16158</v>
+        <v>40528</v>
       </c>
       <c r="CC2" t="n">
-        <v>36669</v>
+        <v>37807</v>
       </c>
       <c r="CD2" t="n">
-        <v>104029</v>
+        <v>83187</v>
       </c>
       <c r="CE2" t="n">
-        <v>109074</v>
+        <v>110322</v>
       </c>
       <c r="CF2" t="n">
-        <v>116840</v>
+        <v>100053</v>
       </c>
       <c r="CG2" t="n">
-        <v>27844</v>
+        <v>25224</v>
       </c>
       <c r="CH2" t="n">
-        <v>88549</v>
+        <v>135195</v>
       </c>
       <c r="CI2" t="n">
-        <v>24814</v>
+        <v>22194</v>
       </c>
       <c r="CJ2" t="n">
-        <v>38177</v>
+        <v>34948</v>
       </c>
       <c r="CK2" t="n">
-        <v>73114</v>
+        <v>71914</v>
       </c>
       <c r="CL2" t="n">
-        <v>53264</v>
+        <v>63141</v>
       </c>
       <c r="CM2" t="n">
-        <v>22469</v>
+        <v>21300</v>
       </c>
       <c r="CN2" t="n">
-        <v>104580</v>
+        <v>65725</v>
       </c>
       <c r="CO2" t="n">
-        <v>87260</v>
+        <v>79956</v>
       </c>
       <c r="CP2" t="n">
-        <v>78921</v>
+        <v>16929</v>
       </c>
       <c r="CQ2" t="n">
-        <v>46433</v>
+        <v>50421</v>
       </c>
       <c r="CR2" t="n">
-        <v>62831</v>
+        <v>85171</v>
       </c>
       <c r="CS2" t="n">
-        <v>123214</v>
+        <v>122654</v>
       </c>
       <c r="CT2" t="n">
         <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>34772</v>
+        <v>35910</v>
       </c>
       <c r="CV2" t="n">
-        <v>13934</v>
+        <v>14160</v>
       </c>
     </row>
   </sheetData>
